--- a/tests/workbooktests/workbooks/test_bonds.xlsx
+++ b/tests/workbooktests/workbooks/test_bonds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED47D65-5269-434E-B33E-8578ED008772}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F7C303-12C7-40E2-B231-BB6B8BA4FB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="32370" windowHeight="9360" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
+    <workbookView xWindow="3645" yWindow="-19185" windowWidth="30690" windowHeight="16530" firstSheet="7" activeTab="12" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
@@ -33,12 +33,26 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="154">
   <si>
     <t>Bond</t>
   </si>
@@ -757,7 +771,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -773,9 +787,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -813,7 +827,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -919,7 +933,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1061,7 +1075,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1070,17 +1084,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F1B31AC-6B78-4845-B599-86FA814CB2D7}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="15"/>
-    <col min="2" max="2" width="36.140625" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="33.85546875" customWidth="1"/>
-    <col min="5" max="5" width="32.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="15"/>
+    <col min="2" max="2" width="36.109375" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="4" max="4" width="33.88671875" customWidth="1"/>
+    <col min="5" max="5" width="32.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="16" t="s">
         <v>113</v>
       </c>
@@ -1090,7 +1104,7 @@
       <c r="D2" s="34"/>
       <c r="E2" s="35"/>
     </row>
-    <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="17"/>
       <c r="C3" s="18" t="s">
         <v>51</v>
@@ -1102,7 +1116,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="29" t="s">
         <v>116</v>
       </c>
@@ -1110,7 +1124,7 @@
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="20" t="s">
         <v>0</v>
       </c>
@@ -1120,7 +1134,7 @@
       <c r="D5" s="21"/>
       <c r="E5" s="22"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="20" t="s">
         <v>1</v>
       </c>
@@ -1130,7 +1144,7 @@
       <c r="D6" s="21"/>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="20" t="s">
         <v>2</v>
       </c>
@@ -1140,7 +1154,7 @@
       <c r="D7" s="21"/>
       <c r="E7" s="22"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="20" t="s">
         <v>3</v>
       </c>
@@ -1150,7 +1164,7 @@
       <c r="D8" s="21"/>
       <c r="E8" s="22"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="20" t="s">
         <v>4</v>
       </c>
@@ -1160,7 +1174,7 @@
       <c r="D9" s="21"/>
       <c r="E9" s="22"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="20" t="s">
         <v>5</v>
       </c>
@@ -1170,7 +1184,7 @@
       <c r="D10" s="21"/>
       <c r="E10" s="22"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="20" t="s">
         <v>6</v>
       </c>
@@ -1180,7 +1194,7 @@
       <c r="D11" s="21"/>
       <c r="E11" s="22"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="26" t="s">
         <v>7</v>
       </c>
@@ -1190,7 +1204,7 @@
       <c r="D12" s="21"/>
       <c r="E12" s="22"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="26" t="s">
         <v>124</v>
       </c>
@@ -1198,7 +1212,7 @@
       <c r="D13" s="21"/>
       <c r="E13" s="22"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="26" t="s">
         <v>8</v>
       </c>
@@ -1208,7 +1222,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="26" t="s">
         <v>9</v>
       </c>
@@ -1218,7 +1232,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="25" t="s">
         <v>11</v>
       </c>
@@ -1238,14 +1252,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ABD84F-1436-4AE1-BC17-091C65B56114}">
   <dimension ref="A1:C68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.5703125" customWidth="1"/>
-    <col min="2" max="2" width="73.85546875" customWidth="1"/>
-    <col min="3" max="3" width="71.140625" customWidth="1"/>
+    <col min="1" max="1" width="48.5546875" customWidth="1"/>
+    <col min="2" max="2" width="73.88671875" customWidth="1"/>
+    <col min="3" max="3" width="71.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1253,7 +1267,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1262,10 +1276,10 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1276,7 +1290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="36" t="s">
         <v>82</v>
       </c>
@@ -1287,7 +1301,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="36"/>
       <c r="B6" s="3">
         <v>102</v>
@@ -1296,7 +1310,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="36"/>
       <c r="B7" s="3">
         <v>101</v>
@@ -1305,7 +1319,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>73</v>
       </c>
@@ -1316,7 +1330,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
@@ -1327,7 +1341,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
@@ -1338,7 +1352,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>60</v>
       </c>
@@ -1351,7 +1365,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
@@ -1362,7 +1376,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>75</v>
       </c>
@@ -1373,7 +1387,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>77</v>
       </c>
@@ -1384,7 +1398,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>78</v>
       </c>
@@ -1395,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -1408,7 +1422,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R16C3Schedule,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>101</v>
       </c>
@@ -1419,7 +1433,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>46</v>
       </c>
@@ -1430,7 +1444,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>14</v>
       </c>
@@ -1441,7 +1455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>103</v>
       </c>
@@ -1452,7 +1466,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>60</v>
       </c>
@@ -1465,7 +1479,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>105</v>
       </c>
@@ -1476,7 +1490,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>106</v>
       </c>
@@ -1487,7 +1501,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>107</v>
       </c>
@@ -1498,7 +1512,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>109</v>
       </c>
@@ -1511,20 +1525,20 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R25C3Euribor,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>110</v>
       </c>
       <c r="B26" s="6" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C26" s="6" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>100</v>
       </c>
@@ -1537,7 +1551,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R27C3SwapIndex,A</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1548,7 +1562,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -1557,7 +1571,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>90</v>
       </c>
@@ -1566,7 +1580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>91</v>
       </c>
@@ -1575,7 +1589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>92</v>
       </c>
@@ -1584,7 +1598,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>93</v>
       </c>
@@ -1593,7 +1607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>94</v>
       </c>
@@ -1602,7 +1616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>95</v>
       </c>
@@ -1611,7 +1625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1620,7 +1634,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>111</v>
       </c>
@@ -1633,7 +1647,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R37C3AmortizingCmsRateBond,A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>20</v>
       </c>
@@ -1646,7 +1660,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>21</v>
       </c>
@@ -1659,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>22</v>
       </c>
@@ -1672,7 +1686,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>23</v>
       </c>
@@ -1685,7 +1699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>24</v>
       </c>
@@ -1698,7 +1712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>25</v>
       </c>
@@ -1711,7 +1725,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>26</v>
       </c>
@@ -1724,7 +1738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>27</v>
       </c>
@@ -1737,7 +1751,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>28</v>
       </c>
@@ -1750,7 +1764,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>29</v>
       </c>
@@ -1763,7 +1777,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>30</v>
       </c>
@@ -1776,38 +1790,20 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R48C3CashFlow,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="3" t="str">
-        <f>_xll.qlBondRedemption(B37)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
-    return bond.redemption()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
-    return _QuantLib.Bond_redemption(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: multiple redemption cash flows given
-</v>
-      </c>
-      <c r="C49" s="3" t="str">
-        <f>_xll.qlBondRedemption(C37)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
-    return bond.redemption()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
-    return _QuantLib.Bond_redemption(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: multiple redemption cash flows given
-</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="3">
+        <f>FIND("RuntimeError: RuntimeError: multiple redemption cash flows given",_xll.qlBondRedemption(B37))</f>
+        <v>1</v>
+      </c>
+      <c r="C49" s="3">
+        <f>FIND("RuntimeError: RuntimeError: multiple redemption cash flows given",_xll.qlBondRedemption(C37))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>58</v>
       </c>
@@ -1820,7 +1816,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R50C3CashFlow,A</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>31</v>
       </c>
@@ -1833,7 +1829,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>32</v>
       </c>
@@ -1846,7 +1842,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>59</v>
       </c>
@@ -1859,20 +1855,20 @@
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B54" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C54" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>152</v>
       </c>
@@ -1885,7 +1881,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R55C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>153</v>
       </c>
@@ -1898,20 +1894,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B57" s="9">
-        <f>_xll.qlBondCleanPrice(B37)</f>
-        <v>72.117682106498307</v>
+        <f>_xll.qlBondCleanPrice(B37,B56)</f>
+        <v>72.117682106498322</v>
       </c>
       <c r="C57" s="9">
-        <f>_xll.qlBondCleanPrice(C37)</f>
+        <f>_xll.qlBondCleanPrice(C37,C56)</f>
         <v>74.834890455035776</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>56</v>
       </c>
@@ -1922,7 +1918,7 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>34</v>
       </c>
@@ -1935,20 +1931,20 @@
         <v>74.834886535610039</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B60" s="9">
-        <f>_xll.qlBondDirtyPrice(B37)</f>
-        <v>72.117682106498307</v>
+        <f>_xll.qlBondDirtyPrice(B37,B56)</f>
+        <v>72.117682106498322</v>
       </c>
       <c r="C60" s="9">
-        <f>_xll.qlBondDirtyPrice(C37)</f>
+        <f>_xll.qlBondDirtyPrice(C37,C56)</f>
         <v>74.836557121702455</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>36</v>
       </c>
@@ -1961,20 +1957,20 @@
         <v>74.836553202276718</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B62" s="9">
-        <f>_xll.qlBondYield(B37,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(B37,"actual360","CONTINUOUS","annual",,,B56)</f>
         <v>2.9888064241409308E-2</v>
       </c>
       <c r="C62" s="9">
-        <f>_xll.qlBondYield(C37,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(C37,"actual360","CONTINUOUS","annual",,,C56)</f>
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>120</v>
       </c>
@@ -1987,7 +1983,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R63C3BondPrice,A</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>38</v>
       </c>
@@ -2000,7 +1996,7 @@
         <v>2.9890143346786503E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>54</v>
       </c>
@@ -2011,7 +2007,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>39</v>
       </c>
@@ -2024,26 +2020,26 @@
         <v>1.6666666666775853E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B67" s="9">
-        <f>_xll.qlBondSettlementValue(B37)</f>
-        <v>74.281212569693253</v>
+        <f>_xll.qlBondSettlementValue(B37,B56)</f>
+        <v>74.281212569693267</v>
       </c>
       <c r="C67" s="9">
-        <f>_xll.qlBondSettlementValue(C37)</f>
+        <f>_xll.qlBondSettlementValue(C37,C56)</f>
         <v>77.081653835353535</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B68" s="9">
         <f>_xll.qlBondSettlementValue2(B37,B57)</f>
-        <v>74.281212569693253</v>
+        <v>74.281212569693281</v>
       </c>
       <c r="C68" s="9">
         <f>_xll.qlBondSettlementValue2(C37,C57)</f>
@@ -2061,14 +2057,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F09BC366-53EA-43EA-8BCB-0489C1B271E0}">
   <dimension ref="A3:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="45.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="45.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>125</v>
       </c>
@@ -2077,7 +2073,7 @@
         <v>欣[test_bonds.xlsx]Callability!R3C2BondPrice,A</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -2085,7 +2081,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -2093,7 +2089,7 @@
         <v>46357</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>129</v>
       </c>
@@ -2102,7 +2098,7 @@
         <v>欣[test_bonds.xlsx]Callability!R6C2Callability,A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>130</v>
       </c>
@@ -2111,7 +2107,7 @@
         <v>欣[test_bonds.xlsx]Callability!R7C2BondPrice,A</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>131</v>
       </c>
@@ -2120,7 +2116,7 @@
         <v>46357</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>132</v>
       </c>
@@ -2129,7 +2125,7 @@
         <v>PUT</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
     </row>
   </sheetData>
@@ -2140,14 +2136,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0A1FE9-B1FE-4762-AEA9-E4B3F6C519F7}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.7109375" customWidth="1"/>
-    <col min="2" max="2" width="93.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="75.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="47.6640625" customWidth="1"/>
+    <col min="2" max="2" width="93.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="75.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -2155,7 +2151,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2164,7 +2160,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2175,7 +2171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -2186,7 +2182,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
@@ -2197,7 +2193,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -2208,7 +2204,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
@@ -2219,7 +2215,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -2232,7 +2228,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -2243,7 +2239,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>75</v>
       </c>
@@ -2254,7 +2250,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
@@ -2265,7 +2261,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -2276,7 +2272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -2289,7 +2285,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R14C3Schedule,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>66</v>
       </c>
@@ -2300,7 +2296,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="36"/>
       <c r="B16" s="3">
         <v>0.03</v>
@@ -2309,7 +2305,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="36"/>
       <c r="B17" s="3">
         <v>0.03</v>
@@ -2318,7 +2314,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>83</v>
       </c>
@@ -2329,7 +2325,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -2340,7 +2336,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -2351,7 +2347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -2362,7 +2358,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>120</v>
       </c>
@@ -2375,7 +2371,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R22C3BondPrice,A</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>126</v>
       </c>
@@ -2386,7 +2382,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>136</v>
       </c>
@@ -2397,7 +2393,7 @@
         <v>47664</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>133</v>
       </c>
@@ -2410,7 +2406,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R25C3Callability,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -2421,7 +2417,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -2434,7 +2430,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -2442,7 +2438,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -2450,7 +2446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>137</v>
       </c>
@@ -2463,7 +2459,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R30C3CallableFixedRateBond,A</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>20</v>
       </c>
@@ -2476,7 +2472,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>21</v>
       </c>
@@ -2489,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>22</v>
       </c>
@@ -2502,7 +2498,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>23</v>
       </c>
@@ -2515,7 +2511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
@@ -2528,7 +2524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>25</v>
       </c>
@@ -2541,7 +2537,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>26</v>
       </c>
@@ -2554,7 +2550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>27</v>
       </c>
@@ -2567,7 +2563,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>28</v>
       </c>
@@ -2580,7 +2576,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>29</v>
       </c>
@@ -2593,7 +2589,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>30</v>
       </c>
@@ -2606,7 +2602,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R41C3CashFlow,A</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>57</v>
       </c>
@@ -2619,7 +2615,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R42C3CashFlow,A</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>58</v>
       </c>
@@ -2632,7 +2628,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R43C3CashFlow,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>31</v>
       </c>
@@ -2645,7 +2641,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>32</v>
       </c>
@@ -2658,7 +2654,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>59</v>
       </c>
@@ -2671,7 +2667,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="30" t="s">
         <v>139</v>
       </c>
@@ -2682,20 +2678,20 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="30" t="s">
         <v>110</v>
       </c>
       <c r="B48" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.025,"actual360")</f>
+        <f>_xll.qlFlatForward(B2,0.025,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C48" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.025,"actual360")</f>
+        <f>_xll.qlFlatForward(B2,0.025,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>138</v>
       </c>
@@ -2708,7 +2704,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R49C3BlackCallableFixedRateBondEngine,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="30" t="s">
         <v>151</v>
       </c>
@@ -2721,20 +2717,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B51" s="33">
-        <f>_xll.qlBondCleanPrice(B30)</f>
-        <v>104.08408808408915</v>
-      </c>
-      <c r="C51" s="9">
-        <f>_xll.qlBondCleanPrice(C30)</f>
-        <v>104.49668091130677</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondCleanPrice(B30,B50)</f>
+        <v>104.56552586351701</v>
+      </c>
+      <c r="C51" s="33">
+        <f>_xll.qlBondCleanPrice(C30,C50)</f>
+        <v>104.93923846207524</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>56</v>
       </c>
@@ -2742,10 +2738,10 @@
         <v>2.8928264971926201E-2</v>
       </c>
       <c r="C52" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.8928264971926201E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>34</v>
       </c>
@@ -2755,23 +2751,23 @@
       </c>
       <c r="C53" s="9">
         <f>_xll.qlBondCleanPrice2(C30,C52,"actual360","continuous")</f>
-        <v>12.534456719148118</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100.60282643461134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B54" s="9">
-        <f>_xll.qlBondDirtyPrice(B30)</f>
-        <v>104.12575475075582</v>
+        <f>_xll.qlBondDirtyPrice(B30,B50)</f>
+        <v>104.60719253018368</v>
       </c>
       <c r="C54" s="9">
-        <f>_xll.qlBondDirtyPrice(C30)</f>
-        <v>104.51334757797343</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondDirtyPrice(C30,C50)</f>
+        <v>104.9559051287419</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>36</v>
       </c>
@@ -2781,23 +2777,23 @@
       </c>
       <c r="C55" s="9">
         <f>_xll.qlBondDirtyPrice2(C30,C52,"actual360","CONTINUOUS","annual")</f>
-        <v>12.551123385814783</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100.61949310127801</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B56" s="9">
-        <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual")</f>
-        <v>2.5000006914138798E-2</v>
+        <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual",,,B50)</f>
+        <v>2.4524004602432259E-2</v>
       </c>
       <c r="C56" s="9">
-        <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual")</f>
-        <v>2.5000006914138798E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual",,,C50)</f>
+        <v>2.4563668775558482E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>120</v>
       </c>
@@ -2810,20 +2806,20 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R57C3BondPrice,A</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B58" s="9">
         <f>_xll.qlBondYield2(B30,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>2.5041315031051642E-2</v>
+        <v>2.4565103197097787E-2</v>
       </c>
       <c r="C58" s="9">
         <f>_xll.qlBondYield2(C30,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>2.5016478586196905E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.458006670921447E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>54</v>
       </c>
@@ -2834,7 +2830,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>39</v>
       </c>
@@ -2847,33 +2843,33 @@
         <v>1.6666666666664831E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B61" s="9">
-        <f>_xll.qlBondSettlementValue(B30)</f>
-        <v>104.12575475075583</v>
+        <f>_xll.qlBondSettlementValue(B30,B50)</f>
+        <v>104.60719253018367</v>
       </c>
       <c r="C61" s="9">
-        <f>_xll.qlBondSettlementValue(C30)</f>
-        <v>104.51334757797343</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondSettlementValue(C30,C50)</f>
+        <v>104.9559051287419</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B62" s="9">
         <f>_xll.qlBondSettlementValue2(B30,B51)</f>
-        <v>104.12575475075583</v>
+        <v>104.6071925301837</v>
       </c>
       <c r="C62" s="9">
         <f>_xll.qlBondSettlementValue2(C30,C51)</f>
-        <v>104.51334757797343</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>104.9559051287419</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>140</v>
       </c>
@@ -2886,7 +2882,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R63C3Callability,A</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>120</v>
       </c>
@@ -2899,92 +2895,60 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R64C3BondPrice,A</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="B66" s="3" t="str">
-        <f>_xll.qlCallableBondOAS(B30,43.82,B48,"Actual/360","Simple","Annual",,,1000)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-60.2279,-60.2279])
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1105, in qlCallableBondOAS
-    return callable_bond.OAS(
-           ~~~~~~~~~~~~~~~~~^
-        clean_price,
-        ^^^^^^^^^^^^
-    ...&lt;7 lines&gt;...
-        guess,
-        ^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
-    return _QuantLib.CallableBond_OAS(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-60.2279,-60.2279])
-</v>
-      </c>
-      <c r="C66" s="3" t="str">
-        <f>_xll.qlCallableBondOAS(C30,43.82,C48,"Actual/360","Simple","Annual",,,1000)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-60.6622,-60.6622])
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1105, in qlCallableBondOAS
-    return callable_bond.OAS(
-           ~~~~~~~~~~~~~~~~~^
-        clean_price,
-        ^^^^^^^^^^^^
-    ...&lt;7 lines&gt;...
-        guess,
-        ^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
-    return _QuantLib.CallableBond_OAS(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-60.6622,-60.6622])
-</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="3">
+        <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(B30,105,B48,"Actual/360","Simple","Annual",,,1000,,B50))</f>
+        <v>1</v>
+      </c>
+      <c r="C66" s="3">
+        <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(C30,105,C48,"Actual/360","Simple","Annual",,,1000,,C50))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>143</v>
       </c>
       <c r="B67" s="3">
-        <f>_xll.qlCallableBondCleanPriceOAS(B30,0.3,B48,"actual/360","simple","annual")</f>
-        <v>104.04793958427845</v>
+        <f>_xll.qlCallableBondCleanPriceOAS(B30,0.3,B48,"actual/360","simple","annual",,B50)</f>
+        <v>104.52921022682914</v>
       </c>
       <c r="C67" s="3">
-        <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual")</f>
-        <v>104.48216617657867</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual",,C50)</f>
+        <v>104.92466226528889</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>144</v>
       </c>
       <c r="B68" s="3">
-        <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","compounded","annual")</f>
+        <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
         <v>0</v>
       </c>
       <c r="C68" s="3">
-        <f>_xll.qlCallableBondEffectiveDuration(C30,0.3,C48,"actual/360","compounded","annual")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlCallableBondEffectiveDuration(C30,0.3,C48,"actual/360","compounded","annual",,C50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>145</v>
       </c>
       <c r="B69" s="3">
-        <f>_xll.qlCallableBondEffectiveConvexity(B30,0.3,B48,"actual/360","compounded","annual")</f>
+        <f>_xll.qlCallableBondEffectiveConvexity(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
         <v>0</v>
       </c>
       <c r="C69" s="3">
-        <f>_xll.qlCallableBondEffectiveConvexity(C30,0.3,C48,"actual/360","compounded","annual")</f>
+        <f>_xll.qlCallableBondEffectiveConvexity(C30,0.3,C48,"actual/360","compounded","annual",,C50)</f>
         <v>0</v>
       </c>
     </row>
@@ -3000,14 +2964,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4EF9C2-FD4D-4E7F-8154-C8E782972C6B}">
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.140625" customWidth="1"/>
-    <col min="2" max="2" width="89.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="73.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="44.109375" customWidth="1"/>
+    <col min="2" max="2" width="89.5546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="73.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -3015,7 +2979,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3024,7 +2988,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -3035,7 +2999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3046,7 +3010,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -3059,7 +3023,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3070,7 +3034,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>146</v>
       </c>
@@ -3081,7 +3045,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -3089,7 +3053,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -3097,7 +3061,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -3105,49 +3069,60 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2" t="str">
+        <f>_xll.qlBondPrice(100,"CLEAN")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C2BondPrice,A</v>
+      </c>
       <c r="C12" s="2" t="str">
         <f>_xll.qlBondPrice(100,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C3BondPrice,A</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="C13" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2">
+        <v>47664</v>
+      </c>
       <c r="C14" s="2">
         <v>47664</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>133</v>
+      </c>
+      <c r="B15" s="3" t="str">
+        <f>_xll.qlCallability(B12,B13,B14)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C2Callability,A</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>_xll.qlCallability(C12,C13,C14)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C3Callability,A</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>147</v>
       </c>
       <c r="B16" s="3" t="str">
-        <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8)</f>
+        <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C2CallableZeroCouponBond,A</v>
       </c>
       <c r="C16" s="3" t="str">
@@ -3155,38 +3130,20 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C3CallableZeroCouponBond,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3" t="str">
-        <f>_xll.qlBondNextCouponRate(B16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 216, in qlBondNextCouponRate
-    return bond.nextCouponRate(date)
-           ~~~~~~~~~~~~~~~~~~~^^^^^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
-    return _QuantLib.Bond_nextCouponRate(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: no coupon paid at cashflow date January 8th, 2036
-</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>_xll.qlBondNextCouponRate(C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 216, in qlBondNextCouponRate
-    return bond.nextCouponRate(date)
-           ~~~~~~~~~~~~~~~~~~~^^^^^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
-    return _QuantLib.Bond_nextCouponRate(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: no coupon paid at cashflow date January 8th, 2036
-</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="3">
+        <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036",_xll.qlBondNextCouponRate(B16))</f>
+        <v>1</v>
+      </c>
+      <c r="C17" s="3">
+        <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036",_xll.qlBondNextCouponRate(C16))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>21</v>
       </c>
@@ -3199,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>22</v>
       </c>
@@ -3212,7 +3169,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
@@ -3225,7 +3182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>24</v>
       </c>
@@ -3238,7 +3195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
@@ -3251,7 +3208,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>26</v>
       </c>
@@ -3264,7 +3221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>27</v>
       </c>
@@ -3277,7 +3234,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>28</v>
       </c>
@@ -3290,7 +3247,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
@@ -3303,7 +3260,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>30</v>
       </c>
@@ -3316,7 +3273,7 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C3CashFlow,A</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>57</v>
       </c>
@@ -3329,7 +3286,7 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C3CashFlow,A</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>58</v>
       </c>
@@ -3342,7 +3299,7 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C3CashFlow,A</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
@@ -3355,7 +3312,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>32</v>
       </c>
@@ -3368,7 +3325,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>59</v>
       </c>
@@ -3381,7 +3338,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
         <v>139</v>
       </c>
@@ -3392,20 +3349,20 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="30" t="s">
         <v>110</v>
       </c>
       <c r="B34" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C34" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>138</v>
       </c>
@@ -3418,7 +3375,7 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R35C3BlackCallableFixedRateBondEngine,A</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="30" t="s">
         <v>151</v>
       </c>
@@ -3431,29 +3388,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="9" t="str">
-        <f>_xll.qlBondCleanPrice(B16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 407, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
+      <c r="B37" s="9">
+        <f>_xll.qlBondCleanPrice(B16,B36)</f>
+        <v>84.712567119963055</v>
       </c>
       <c r="C37" s="9">
-        <f>_xll.qlBondCleanPrice(C16)</f>
-        <v>71.653019933502407</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondCleanPrice(C16,C36)</f>
+        <v>84.712567119963055</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>56</v>
       </c>
@@ -3464,7 +3412,7 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>34</v>
       </c>
@@ -3477,29 +3425,20 @@
         <v>71.65301602846877</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="9" t="str">
-        <f>_xll.qlBondDirtyPrice(B16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 442, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
+      <c r="B40" s="9">
+        <f>_xll.qlBondDirtyPrice(B16,B36)</f>
+        <v>84.712567119963055</v>
       </c>
       <c r="C40" s="9">
-        <f>_xll.qlBondDirtyPrice(C16)</f>
-        <v>71.653019933502407</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondDirtyPrice(C16,C36)</f>
+        <v>84.712567119963055</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>36</v>
       </c>
@@ -3512,73 +3451,46 @@
         <v>71.65301602846877</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="9" t="str">
-        <f>_xll.qlBondYield(B16,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 490, in qlBondYield
-    return bond.bondYield(dc, compounding, freq, accuracy, max_evaluations)
-           ~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
+      <c r="B42" s="9">
+        <f>_xll.qlBondYield(B16,"actual360","CONTINUOUS","annual",,,B36)</f>
+        <v>1.4875779507160188E-2</v>
       </c>
       <c r="C42" s="9">
-        <f>_xll.qlBondYield(C16,"actual360","CONTINUOUS","annual")</f>
-        <v>2.9888064241409308E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondYield(C16,"actual360","CONTINUOUS","annual",,,C36)</f>
+        <v>1.4875779507160188E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>120</v>
       </c>
       <c r="B43" s="9" t="str">
         <f>_xll.qlBondPrice(B37,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 407, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-': Expected float</v>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C2BondPrice,A</v>
       </c>
       <c r="C43" s="9" t="str">
         <f>_xll.qlBondPrice(C37,"clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C3BondPrice,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="9" t="str">
+      <c r="B44" s="9">
         <f>_xll.qlBondYield2(B16,B43,"actual360","CONTINUOUS","annual")</f>
-        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 407, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-': Expected float': Expected cache string</v>
+        <v>1.4875779507160188E-2</v>
       </c>
       <c r="C44" s="9">
         <f>_xll.qlBondYield2(C16,C43,"actual360","CONTINUOUS","annual")</f>
-        <v>2.9888064241409308E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1.4875779507160188E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>54</v>
       </c>
@@ -3589,7 +3501,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>39</v>
       </c>
@@ -3602,197 +3514,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="9" t="str">
-        <f>_xll.qlBondSettlementValue(B16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 547, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
+      <c r="B47" s="9">
+        <f>_xll.qlBondSettlementValue(B16,B36)</f>
+        <v>84.712567119963055</v>
       </c>
       <c r="C47" s="9">
-        <f>_xll.qlBondSettlementValue(C16)</f>
-        <v>71.653019933502407</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondSettlementValue(C16,C36)</f>
+        <v>84.712567119963055</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="9" t="str">
+      <c r="B48" s="9">
         <f>_xll.qlBondSettlementValue2(B16,B37)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 407, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-': Expected float</v>
+        <v>84.712567119963055</v>
       </c>
       <c r="C48" s="9">
         <f>_xll.qlBondSettlementValue2(C16,C37)</f>
-        <v>71.653019933502407</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84.712567119963055</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="3" t="str">
         <f>_xll.qlCallableBondCallability(B16)</f>
-        <v>0</v>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C2Callability,A</v>
       </c>
       <c r="C49" s="3" t="str">
         <f>_xll.qlCallableBondCallability(C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C3Callability,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="B51" s="3" t="str">
-        <f>_xll.qlCallableBondOAS(B16,43.82,B34,"Actual/360","Simple","Annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1105, in qlCallableBondOAS
-    return callable_bond.OAS(
-           ~~~~~~~~~~~~~~~~~^
-        clean_price,
-        ^^^^^^^^^^^^
-    ...&lt;7 lines&gt;...
-        guess,
-        ^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
-    return _QuantLib.CallableBond_OAS(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
-      </c>
-      <c r="C51" s="3" t="str">
-        <f>_xll.qlCallableBondOAS(C16,43.82,C34,"Actual/360","Simple","Annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 100 function evaluations (last bracket attempt: f[-6.79107e+23,1.76568e+24] -&gt; [-27.8211,-27.8211])
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1105, in qlCallableBondOAS
-    return callable_bond.OAS(
-           ~~~~~~~~~~~~~~~~~^
-        clean_price,
-        ^^^^^^^^^^^^
-    ...&lt;7 lines&gt;...
-        guess,
-        ^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
-    return _QuantLib.CallableBond_OAS(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: unable to bracket root in 100 function evaluations (last bracket attempt: f[-6.79107e+23,1.76568e+24] -&gt; [-27.8211,-27.8211])
-</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="3">
+        <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(B16,105,B34,"Actual/360","Simple","Annual",,,1000,,B36))</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="3">
+        <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(C16,105,C34,"Actual/360","Simple","Annual",,,1000,,C36))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="B52" s="3" t="str">
-        <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Boost assertion failed: px != 0
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1140, in qlCallableBondCleanPriceOAS
-    return callable_bond.cleanPriceOAS(
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~^
-        oas,
-        ^^^^
-    ...&lt;4 lines&gt;...
-        settlement_date,
-        ^^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26308, in cleanPriceOAS
-    return _QuantLib.CallableBond_cleanPriceOAS(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Boost assertion failed: px != 0
-</v>
+      <c r="B52" s="3">
+        <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual",,B36)</f>
+        <v>84.698502208619104</v>
       </c>
       <c r="C52" s="3">
-        <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual")</f>
-        <v>71.641123311700554</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual",,C36)</f>
+        <v>84.698502208619104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="3" t="str">
-        <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Boost assertion failed: px != 0
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1172, in qlCallableBondEffectiveDuration
-    return callable_bond.effectiveDuration(
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
-        oas,
-        ^^^^
-    ...&lt;4 lines&gt;...
-        bump,
-        ^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26312, in effectiveDuration
-    return _QuantLib.CallableBond_effectiveDuration(self, oas, engineTS, dayCounter, compounding, frequency, bump)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-RuntimeError: Boost assertion failed: px != 0
-</v>
+      <c r="B53" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
+        <v>0</v>
       </c>
       <c r="C53" s="3">
-        <f>_xll.qlCallableBondEffectiveDuration(C16,0.3,C34,"actual/360","simple","quarterly")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlCallableBondEffectiveDuration(C16,0.3,C34,"actual/360","simple","quarterly",,C36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B54" s="3" t="str">
-        <f>_xll.qlCallableBondEffectiveConvexity(B16,0.3,B34,"actual/360","simple","quarterly")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1204, in qlCallableBondEffectiveConvexity
-    return callable_bond.effectiveConvexity(
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
-        oas,
-        ^^^^
-    ...&lt;4 lines&gt;...
-        bump,
-        ^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26316, in effectiveConvexity
-    return _QuantLib.CallableBond_effectiveConvexity(self, oas, engineTS, dayCounter, compounding, frequency, bump)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
+      <c r="B54" s="3">
+        <f>_xll.qlCallableBondEffectiveConvexity(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
+        <v>0</v>
       </c>
       <c r="C54" s="3">
-        <f>_xll.qlCallableBondEffectiveConvexity(C16,0.3,C34,"actual/360","simple","quarterly")</f>
+        <f>_xll.qlCallableBondEffectiveConvexity(C16,0.3,C34,"actual/360","simple","quarterly",,C36)</f>
         <v>0</v>
       </c>
     </row>
@@ -3805,7 +3619,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE8D14D-DD7E-4024-86F3-1C5FBF784E5F}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3814,13 +3628,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B77307-DD7A-406E-AD93-A17357F921C0}">
   <dimension ref="A3:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" customWidth="1"/>
     <col min="2" max="2" width="46" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>117</v>
       </c>
@@ -3828,7 +3642,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>118</v>
       </c>
@@ -3836,7 +3650,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>120</v>
       </c>
@@ -3845,7 +3659,7 @@
         <v>欣[test_bonds.xlsx]BondPrice!R5C2BondPrice,A</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>121</v>
       </c>
@@ -3854,7 +3668,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>122</v>
       </c>
@@ -3863,7 +3677,7 @@
         <v>CLEAN</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>123</v>
       </c>
@@ -3881,15 +3695,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8683113-FD1C-4D88-8D42-F7763B404E4F}">
   <dimension ref="A1:E56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.5703125" customWidth="1"/>
+    <col min="1" max="1" width="43.5546875" customWidth="1"/>
     <col min="2" max="2" width="65" style="3" customWidth="1"/>
-    <col min="3" max="3" width="49.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="49.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -3898,7 +3712,7 @@
       </c>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3907,10 +3721,10 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
@@ -3919,7 +3733,7 @@
       </c>
       <c r="C4" s="6"/>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
@@ -3928,7 +3742,7 @@
       </c>
       <c r="C5" s="6"/>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
@@ -3938,7 +3752,7 @@
       </c>
       <c r="C6" s="6"/>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
@@ -3947,7 +3761,7 @@
       </c>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>47</v>
       </c>
@@ -3956,7 +3770,7 @@
       </c>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>48</v>
       </c>
@@ -3965,7 +3779,7 @@
       </c>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>49</v>
       </c>
@@ -3975,7 +3789,7 @@
       </c>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="6">
         <v>103</v>
@@ -3984,7 +3798,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="6">
         <v>103</v>
@@ -3993,49 +3807,49 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6">
         <v>103</v>
       </c>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="6">
         <v>103</v>
       </c>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6">
         <v>102</v>
       </c>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="6">
         <v>102</v>
       </c>
       <c r="C16" s="6"/>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="6">
         <v>102</v>
       </c>
       <c r="C17" s="6"/>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="6">
         <v>102</v>
       </c>
       <c r="C18" s="6"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -4046,7 +3860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -4059,7 +3873,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -4070,7 +3884,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -4081,7 +3895,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -4094,7 +3908,7 @@
         <v>欣[test_bonds.xlsx]Bond!R23C3CashFlow,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -4102,7 +3916,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>19</v>
       </c>
@@ -4115,7 +3929,7 @@
         <v>欣[test_bonds.xlsx]Bond!R25C3Bond,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>20</v>
       </c>
@@ -4128,7 +3942,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>21</v>
       </c>
@@ -4141,7 +3955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>22</v>
       </c>
@@ -4154,7 +3968,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>23</v>
       </c>
@@ -4167,7 +3981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>24</v>
       </c>
@@ -4180,7 +3994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>25</v>
       </c>
@@ -4193,20 +4007,20 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="3" t="e">
-        <f ca="1">qlBondIsTradable(B25)</f>
-        <v>#NAME?</v>
+      <c r="B32" s="3" t="b">
+        <f>_xll.qlBondIsTradable(B25)</f>
+        <v>1</v>
       </c>
       <c r="C32" s="3" t="b">
         <f>_xll.qlBondIsTradable(C25)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -4219,7 +4033,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -4232,7 +4046,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -4245,7 +4059,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>30</v>
       </c>
@@ -4258,7 +4072,7 @@
         <v>欣[test_bonds.xlsx]Bond!R36C3CashFlow,A</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>57</v>
       </c>
@@ -4271,7 +4085,7 @@
         <v>欣[test_bonds.xlsx]Bond!R37C3CashFlow,A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>58</v>
       </c>
@@ -4284,7 +4098,7 @@
         <v>欣[test_bonds.xlsx]Bond!R38C3CashFlow,A</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>31</v>
       </c>
@@ -4297,7 +4111,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>32</v>
       </c>
@@ -4310,7 +4124,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>59</v>
       </c>
@@ -4323,20 +4137,20 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B42" s="3" t="str">
-        <f>_xll.qlFlatForward(B1,0.03,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]Bond!R42C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C42" s="3" t="str">
-        <f>_xll.qlFlatForward(B1,0.03,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]Bond!R42C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>152</v>
       </c>
@@ -4349,7 +4163,7 @@
         <v>欣[test_bonds.xlsx]Bond!R43C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>153</v>
       </c>
@@ -4362,20 +4176,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B45" s="9">
-        <f>_xll.qlBondCleanPrice(B25)</f>
+        <f>_xll.qlBondCleanPrice(B25,B44)</f>
         <v>2.9820944542826178</v>
       </c>
       <c r="C45" s="9">
-        <f>_xll.qlBondCleanPrice(C25)</f>
+        <f>_xll.qlBondCleanPrice(C25,C44)</f>
         <v>2.9820944542826178</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>56</v>
       </c>
@@ -4386,7 +4200,7 @@
         <v>2.9558800538580478E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>34</v>
       </c>
@@ -4399,20 +4213,20 @@
         <v>2.9820944594328145</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B48" s="9">
-        <f>_xll.qlBondDirtyPrice(B25)</f>
+        <f>_xll.qlBondDirtyPrice(B25,B44)</f>
         <v>2.9992611209492823</v>
       </c>
       <c r="C48" s="9">
-        <f>_xll.qlBondDirtyPrice(C25)</f>
+        <f>_xll.qlBondDirtyPrice(C25,C44)</f>
         <v>2.9992611209492823</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>36</v>
       </c>
@@ -4425,20 +4239,20 @@
         <v>2.999261126099479</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B50" s="9">
-        <f>_xll.qlBondYield(B25,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(B25,"actual360","CONTINUOUS","annual",,,B44)</f>
         <v>2.9558799446356546E-2</v>
       </c>
       <c r="C50" s="9">
-        <f>_xll.qlBondYield(C25,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(C25,"actual360","CONTINUOUS","annual",,,C44)</f>
         <v>2.9558799446356546E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>120</v>
       </c>
@@ -4451,7 +4265,7 @@
         <v>欣[test_bonds.xlsx]Bond!R51C3BondPrice,A</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>38</v>
       </c>
@@ -4464,7 +4278,7 @@
         <v>3.5251441098982664E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>54</v>
       </c>
@@ -4475,7 +4289,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>39</v>
       </c>
@@ -4488,20 +4302,20 @@
         <v>1.7166666666664776E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B55" s="9">
-        <f>_xll.qlBondSettlementValue(B25)</f>
+        <f>_xll.qlBondSettlementValue(B25,B44)</f>
         <v>2.9992611209492819</v>
       </c>
       <c r="C55" s="9">
-        <f>_xll.qlBondSettlementValue(C25)</f>
+        <f>_xll.qlBondSettlementValue(C25,C44)</f>
         <v>2.9992611209492819</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>41</v>
       </c>
@@ -4523,15 +4337,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0BDDB4-6035-4089-86B1-6246F3228CBC}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.85546875" customWidth="1"/>
-    <col min="2" max="2" width="88.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="59.28515625" style="3" customWidth="1"/>
-    <col min="4" max="7" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="42.88671875" customWidth="1"/>
+    <col min="2" max="2" width="88.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="59.33203125" style="3" customWidth="1"/>
+    <col min="4" max="7" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -4539,7 +4353,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4548,7 +4362,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4559,7 +4373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -4572,7 +4386,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4583,7 +4397,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4594,7 +4408,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -4602,7 +4416,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -4610,7 +4424,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -4618,7 +4432,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>62</v>
       </c>
@@ -4631,38 +4445,20 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R11C3ZeroCouponBond,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="3" t="str">
-        <f>_xll.qlBondNextCouponRate(B11)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 216, in qlBondNextCouponRate
-    return bond.nextCouponRate(date)
-           ~~~~~~~~~~~~~~~~~~~^^^^^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
-    return _QuantLib.Bond_nextCouponRate(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: no coupon paid at cashflow date January 8th, 2036
-</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>_xll.qlBondNextCouponRate(C11)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 216, in qlBondNextCouponRate
-    return bond.nextCouponRate(date)
-           ~~~~~~~~~~~~~~~~~~~^^^^^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
-    return _QuantLib.Bond_nextCouponRate(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: no coupon paid at cashflow date January 8th, 2036
-</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
+        <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036",_xll.qlBondNextCouponRate(B11))</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036",_xll.qlBondNextCouponRate(C11))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -4675,7 +4471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>22</v>
       </c>
@@ -4688,7 +4484,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -4701,7 +4497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -4714,7 +4510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -4727,7 +4523,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>26</v>
       </c>
@@ -4740,7 +4536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
@@ -4753,7 +4549,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>28</v>
       </c>
@@ -4766,7 +4562,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>29</v>
       </c>
@@ -4779,7 +4575,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>30</v>
       </c>
@@ -4792,7 +4588,7 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R22C3CashFlow,A</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>57</v>
       </c>
@@ -4805,7 +4601,7 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R23C3CashFlow,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>58</v>
       </c>
@@ -4818,7 +4614,7 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R24C3CashFlow,A</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
@@ -4831,7 +4627,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>32</v>
       </c>
@@ -4844,7 +4640,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>59</v>
       </c>
@@ -4857,20 +4653,20 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B28" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R28C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C28" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R28C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>152</v>
       </c>
@@ -4883,7 +4679,7 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R29C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>153</v>
       </c>
@@ -4896,20 +4692,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="9">
-        <f>_xll.qlBondCleanPrice(B11)</f>
+        <f>_xll.qlBondCleanPrice(B11,B30)</f>
         <v>71.916622935265281</v>
       </c>
       <c r="C31" s="9">
-        <f>_xll.qlBondCleanPrice(C11)</f>
-        <v>86.29994752231832</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondCleanPrice(C11,C30)</f>
+        <v>86.299947522318348</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>56</v>
       </c>
@@ -4920,7 +4716,7 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>34</v>
       </c>
@@ -4933,20 +4729,20 @@
         <v>86.299941894906539</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B34" s="9">
-        <f>_xll.qlBondDirtyPrice(B11)</f>
+        <f>_xll.qlBondDirtyPrice(B11,B30)</f>
         <v>71.916622935265281</v>
       </c>
       <c r="C34" s="9">
-        <f>_xll.qlBondDirtyPrice(C11)</f>
-        <v>86.29994752231832</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondDirtyPrice(C11,C30)</f>
+        <v>86.299947522318348</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>36</v>
       </c>
@@ -4959,20 +4755,20 @@
         <v>86.299941894906539</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B36" s="9">
-        <f>_xll.qlBondYield(B11,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(B11,"actual360","CONTINUOUS","annual",,,B30)</f>
         <v>2.9558808088302614E-2</v>
       </c>
       <c r="C36" s="9">
-        <f>_xll.qlBondYield(C11,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(C11,"actual360","CONTINUOUS","annual",,,C30)</f>
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>120</v>
       </c>
@@ -4985,20 +4781,20 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R37C3BondPrice,A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B38" s="9">
-        <f>_xll.qlBondYield2(B11,B37,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield2(B11,B37,"actual360","CONTINUOUS","annual",,,,,B30)</f>
         <v>2.9558808088302614E-2</v>
       </c>
       <c r="C38" s="9">
-        <f>_xll.qlBondYield2(C11,C37,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield2(C11,C37,"actual360","CONTINUOUS","annual",,,,,C30)</f>
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>54</v>
       </c>
@@ -5009,7 +4805,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>39</v>
       </c>
@@ -5022,20 +4818,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="9">
-        <f>_xll.qlBondSettlementValue(B11)</f>
+        <f>_xll.qlBondSettlementValue(B11,B30)</f>
         <v>71.916622935265281</v>
       </c>
       <c r="C41" s="9">
-        <f>_xll.qlBondSettlementValue(C11)</f>
-        <v>86.299947522318334</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondSettlementValue(C11,C30)</f>
+        <v>86.299947522318348</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>41</v>
       </c>
@@ -5045,7 +4841,7 @@
       </c>
       <c r="C42" s="9">
         <f>_xll.qlBondSettlementValue2(C11,C31)</f>
-        <v>86.29994752231832</v>
+        <v>86.299947522318348</v>
       </c>
     </row>
   </sheetData>
@@ -5056,14 +4852,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00EB77E5-949B-439C-BFA2-575F2A710E3C}">
   <dimension ref="A1:C58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="59.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="126.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="59.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="126.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -5071,7 +4867,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5080,7 +4876,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -5091,7 +4887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -5102,7 +4898,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
@@ -5113,7 +4909,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -5124,7 +4920,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
@@ -5135,7 +4931,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -5148,7 +4944,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -5159,7 +4955,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>75</v>
       </c>
@@ -5170,7 +4966,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
@@ -5181,7 +4977,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -5192,7 +4988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -5205,7 +5001,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R14C3Schedule,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>66</v>
       </c>
@@ -5216,7 +5012,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="36"/>
       <c r="B16" s="3">
         <v>0.05</v>
@@ -5225,7 +5021,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="36"/>
       <c r="B17" s="3">
         <v>0.06</v>
@@ -5234,7 +5030,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -5245,7 +5041,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -5253,7 +5049,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -5261,7 +5057,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -5269,7 +5065,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -5278,7 +5074,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -5286,7 +5082,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -5295,7 +5091,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -5303,7 +5099,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -5311,7 +5107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>80</v>
       </c>
@@ -5324,7 +5120,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R27C3FixedRateBond,A</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>20</v>
       </c>
@@ -5337,7 +5133,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>21</v>
       </c>
@@ -5350,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>22</v>
       </c>
@@ -5363,7 +5159,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>23</v>
       </c>
@@ -5376,7 +5172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -5389,7 +5185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>25</v>
       </c>
@@ -5402,7 +5198,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>26</v>
       </c>
@@ -5415,7 +5211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>27</v>
       </c>
@@ -5428,7 +5224,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>28</v>
       </c>
@@ -5441,7 +5237,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>29</v>
       </c>
@@ -5454,7 +5250,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>30</v>
       </c>
@@ -5467,7 +5263,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R38C3CashFlow,A</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>57</v>
       </c>
@@ -5480,7 +5276,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R39C3CashFlow,A</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>58</v>
       </c>
@@ -5493,7 +5289,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R40C3CashFlow,A</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>31</v>
       </c>
@@ -5506,7 +5302,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>32</v>
       </c>
@@ -5519,7 +5315,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>59</v>
       </c>
@@ -5532,20 +5328,20 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B44" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R44C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R44C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>152</v>
       </c>
@@ -5558,7 +5354,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R45C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>153</v>
       </c>
@@ -5571,20 +5367,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B47" s="9">
-        <f>_xll.qlBondCleanPrice(B27)</f>
-        <v>124.40332304252406</v>
+        <f>_xll.qlBondCleanPrice(B27,B46)</f>
+        <v>124.40332304252402</v>
       </c>
       <c r="C47" s="9">
-        <f>_xll.qlBondCleanPrice(C27)</f>
-        <v>124.40127138186649</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondCleanPrice(C27,C46)</f>
+        <v>124.40127138186648</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>56</v>
       </c>
@@ -5595,7 +5391,7 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>34</v>
       </c>
@@ -5608,20 +5404,20 @@
         <v>124.40126484069721</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B50" s="9">
-        <f>_xll.qlBondDirtyPrice(B27)</f>
-        <v>124.40332304252406</v>
+        <f>_xll.qlBondDirtyPrice(B27,B46)</f>
+        <v>124.40332304252402</v>
       </c>
       <c r="C50" s="9">
-        <f>_xll.qlBondDirtyPrice(C27)</f>
-        <v>124.40127138186649</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondDirtyPrice(C27,C46)</f>
+        <v>124.40127138186648</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>36</v>
       </c>
@@ -5634,20 +5430,20 @@
         <v>124.40126484069721</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B52" s="9">
-        <f>_xll.qlBondYield(B27,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(B27,"actual360","CONTINUOUS","annual",,,B46)</f>
         <v>2.9558808088302614E-2</v>
       </c>
       <c r="C52" s="9">
-        <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual",,,C46)</f>
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>120</v>
       </c>
@@ -5660,7 +5456,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R53C3BondPrice,A</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>38</v>
       </c>
@@ -5673,7 +5469,7 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>54</v>
       </c>
@@ -5684,7 +5480,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>39</v>
       </c>
@@ -5697,30 +5493,30 @@
         <v>2.2222222222212373E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B57" s="9">
-        <f>_xll.qlBondSettlementValue(B27)</f>
-        <v>124.40332304252406</v>
+        <f>_xll.qlBondSettlementValue(B27,B46)</f>
+        <v>124.40332304252402</v>
       </c>
       <c r="C57" s="9">
-        <f>_xll.qlBondSettlementValue(C27)</f>
-        <v>124.40127138186649</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondSettlementValue(C27,C46)</f>
+        <v>124.40127138186648</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B58" s="9">
         <f>_xll.qlBondSettlementValue2(B27,B47)</f>
-        <v>124.40332304252406</v>
+        <v>124.40332304252402</v>
       </c>
       <c r="C58" s="9">
         <f>_xll.qlBondSettlementValue2(C27,C47)</f>
-        <v>124.40127138186649</v>
+        <v>124.40127138186648</v>
       </c>
     </row>
   </sheetData>
@@ -5734,14 +5530,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303A5445-988F-4FD7-9234-8C10A40DEB2F}">
   <dimension ref="A1:C61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.42578125" customWidth="1"/>
-    <col min="2" max="2" width="69.42578125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="71.140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="44.44140625" customWidth="1"/>
+    <col min="2" max="2" width="69.44140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="71.109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -5749,7 +5545,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5758,7 +5554,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -5769,7 +5565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="36" t="s">
         <v>82</v>
       </c>
@@ -5780,7 +5576,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="36"/>
       <c r="B6" s="3">
         <v>125</v>
@@ -5789,7 +5585,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="36"/>
       <c r="B7" s="3">
         <v>100</v>
@@ -5798,7 +5594,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>73</v>
       </c>
@@ -5809,7 +5605,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
@@ -5820,7 +5616,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
@@ -5831,7 +5627,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>60</v>
       </c>
@@ -5844,7 +5640,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
@@ -5855,7 +5651,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>75</v>
       </c>
@@ -5866,7 +5662,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>77</v>
       </c>
@@ -5877,7 +5673,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>78</v>
       </c>
@@ -5888,7 +5684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -5901,7 +5697,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R16C3Schedule,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="36" t="s">
         <v>66</v>
       </c>
@@ -5912,7 +5708,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="36"/>
       <c r="B18" s="3">
         <v>0.05</v>
@@ -5921,7 +5717,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="36"/>
       <c r="B19" s="3">
         <v>0.06</v>
@@ -5930,7 +5726,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -5941,7 +5737,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -5949,7 +5745,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -5957,7 +5753,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -5965,7 +5761,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -5974,7 +5770,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -5982,7 +5778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -5990,7 +5786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="36" t="s">
         <v>87</v>
       </c>
@@ -5998,19 +5794,19 @@
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="36"/>
       <c r="C28" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="36"/>
       <c r="C29" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>85</v>
       </c>
@@ -6023,7 +5819,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R30C3AmortizingFixedRateBond,A</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>20</v>
       </c>
@@ -6036,7 +5832,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>21</v>
       </c>
@@ -6049,7 +5845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>22</v>
       </c>
@@ -6062,7 +5858,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>23</v>
       </c>
@@ -6075,7 +5871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
@@ -6088,7 +5884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>25</v>
       </c>
@@ -6101,7 +5897,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>26</v>
       </c>
@@ -6114,7 +5910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>27</v>
       </c>
@@ -6127,7 +5923,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>28</v>
       </c>
@@ -6140,7 +5936,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>29</v>
       </c>
@@ -6153,7 +5949,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>30</v>
       </c>
@@ -6166,38 +5962,20 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R41C3CashFlow,A</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="3" t="str">
-        <f>_xll.qlBondRedemption(B30)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
-    return bond.redemption()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
-    return _QuantLib.Bond_redemption(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: multiple redemption cash flows given
-</v>
-      </c>
-      <c r="C42" s="3" t="str">
-        <f>_xll.qlBondRedemption(C30)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
-    return bond.redemption()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
-    return _QuantLib.Bond_redemption(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: multiple redemption cash flows given
-</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="3">
+        <f>FIND("RuntimeError: RuntimeError: multiple redemption cash flows given",_xll.qlBondRedemption(B30))</f>
+        <v>1</v>
+      </c>
+      <c r="C42" s="3">
+        <f>FIND("RuntimeError: RuntimeError: multiple redemption cash flows given",_xll.qlBondRedemption(C30))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>58</v>
       </c>
@@ -6210,7 +5988,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R43C3CashFlow,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>31</v>
       </c>
@@ -6223,7 +6001,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>32</v>
       </c>
@@ -6236,7 +6014,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>59</v>
       </c>
@@ -6249,20 +6027,20 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B47" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R47C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C47" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R47C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>152</v>
       </c>
@@ -6275,7 +6053,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R48C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>153</v>
       </c>
@@ -6288,20 +6066,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B50" s="9">
-        <f>_xll.qlBondCleanPrice(B30)</f>
-        <v>116.88159964957646</v>
+        <f>_xll.qlBondCleanPrice(B30,B49)</f>
+        <v>116.8815996495765</v>
       </c>
       <c r="C50" s="9">
-        <f>_xll.qlBondCleanPrice(C30)</f>
-        <v>124.8650952165318</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondCleanPrice(C30,C49)</f>
+        <v>124.86509521653187</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>56</v>
       </c>
@@ -6312,7 +6090,7 @@
         <v>2.9586706781387334E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>34</v>
       </c>
@@ -6325,20 +6103,20 @@
         <v>124.84124844017744</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B53" s="9">
-        <f>_xll.qlBondDirtyPrice(B30)</f>
-        <v>116.90382187179867</v>
+        <f>_xll.qlBondDirtyPrice(B30,B49)</f>
+        <v>116.90382187179871</v>
       </c>
       <c r="C53" s="9">
-        <f>_xll.qlBondDirtyPrice(C30)</f>
-        <v>124.88731743875401</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondDirtyPrice(C30,C49)</f>
+        <v>124.88731743875408</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>36</v>
       </c>
@@ -6351,20 +6129,20 @@
         <v>124.86347066239965</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B55" s="9">
-        <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual",,,B49)</f>
         <v>2.9558808088302614E-2</v>
       </c>
       <c r="C55" s="9">
-        <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual",,,C49)</f>
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>120</v>
       </c>
@@ -6377,7 +6155,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R56C3BondPrice,A</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>38</v>
       </c>
@@ -6390,7 +6168,7 @@
         <v>2.9584804964065556E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>54</v>
       </c>
@@ -6401,7 +6179,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>39</v>
       </c>
@@ -6414,30 +6192,30 @@
         <v>2.2222222222212373E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B60" s="9">
-        <f>_xll.qlBondSettlementValue(B30)</f>
-        <v>175.35573280769802</v>
+        <f>_xll.qlBondSettlementValue(B30,B49)</f>
+        <v>175.35573280769808</v>
       </c>
       <c r="C60" s="9">
-        <f>_xll.qlBondSettlementValue(C30)</f>
-        <v>187.33097615813102</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondSettlementValue(C30,C49)</f>
+        <v>187.33097615813111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B61" s="9">
         <f>_xll.qlBondSettlementValue2(B30,B50)</f>
-        <v>175.35573280769799</v>
+        <v>175.35573280769808</v>
       </c>
       <c r="C61" s="9">
         <f>_xll.qlBondSettlementValue2(C30,C50)</f>
-        <v>187.33097615813102</v>
+        <v>187.33097615813111</v>
       </c>
     </row>
   </sheetData>
@@ -6453,14 +6231,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76F30CA-2F79-453E-B116-2A48310E361D}">
   <dimension ref="A1:E65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.42578125" customWidth="1"/>
-    <col min="2" max="2" width="72.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="73.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="45.44140625" customWidth="1"/>
+    <col min="2" max="2" width="72.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="73.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -6468,7 +6246,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6477,7 +6255,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -6488,7 +6266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="36" t="s">
         <v>88</v>
       </c>
@@ -6499,7 +6277,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="36"/>
       <c r="B6" s="3">
         <v>125</v>
@@ -6508,7 +6286,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="36"/>
       <c r="B7" s="3">
         <v>100</v>
@@ -6517,7 +6295,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>73</v>
       </c>
@@ -6528,7 +6306,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
@@ -6539,7 +6317,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
@@ -6550,7 +6328,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>60</v>
       </c>
@@ -6563,7 +6341,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
@@ -6574,7 +6352,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>75</v>
       </c>
@@ -6585,7 +6363,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>77</v>
       </c>
@@ -6596,7 +6374,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>78</v>
       </c>
@@ -6607,7 +6385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -6620,20 +6398,20 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R16C3Schedule,A</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>55</v>
       </c>
       <c r="B17" s="14" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C17" s="14" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -6646,7 +6424,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R18C3Euribor,A</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>83</v>
       </c>
@@ -6657,7 +6435,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -6665,7 +6443,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -6673,7 +6451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>91</v>
       </c>
@@ -6681,7 +6459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>92</v>
       </c>
@@ -6689,18 +6467,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>93</v>
       </c>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>95</v>
       </c>
@@ -6708,7 +6486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>17</v>
       </c>
@@ -6716,7 +6494,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -6724,7 +6502,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -6733,7 +6511,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -6741,7 +6519,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -6749,7 +6527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -6757,7 +6535,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -6765,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>97</v>
       </c>
@@ -6778,20 +6556,20 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R34C3AmortizingFloatingRateBond,A</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B35" s="3">
         <f>_xll.qlBondNextCouponRate(B34)</f>
-        <v>3.0348052211435581E-2</v>
+        <v>3.03480522114358E-2</v>
       </c>
       <c r="C35" s="3">
         <f>_xll.qlBondNextCouponRate(C34)</f>
-        <v>3.0348052211435581E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.03480522114358E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>21</v>
       </c>
@@ -6804,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>22</v>
       </c>
@@ -6817,7 +6595,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>23</v>
       </c>
@@ -6830,7 +6608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>24</v>
       </c>
@@ -6843,7 +6621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>25</v>
       </c>
@@ -6856,7 +6634,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>26</v>
       </c>
@@ -6869,7 +6647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>27</v>
       </c>
@@ -6882,7 +6660,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>28</v>
       </c>
@@ -6895,7 +6673,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>29</v>
       </c>
@@ -6908,7 +6686,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>30</v>
       </c>
@@ -6921,38 +6699,20 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R45C3CashFlow,A</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="3" t="str">
-        <f>_xll.qlBondRedemption(B34)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
-    return bond.redemption()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
-    return _QuantLib.Bond_redemption(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: multiple redemption cash flows given
-</v>
-      </c>
-      <c r="C46" s="3" t="str">
-        <f>_xll.qlBondRedemption(C34)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
-    return bond.redemption()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
-    return _QuantLib.Bond_redemption(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: multiple redemption cash flows given
-</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="3">
+        <f>FIND("RuntimeError: RuntimeError: multiple redemption cash flows given",_xll.qlBondRedemption(B34))</f>
+        <v>1</v>
+      </c>
+      <c r="C46" s="3">
+        <f>FIND("RuntimeError: RuntimeError: multiple redemption cash flows given",_xll.qlBondRedemption(C34))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>58</v>
       </c>
@@ -6965,7 +6725,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R47C3CashFlow,A</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>31</v>
       </c>
@@ -6978,7 +6738,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>32</v>
       </c>
@@ -6991,7 +6751,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>59</v>
       </c>
@@ -7004,20 +6764,20 @@
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B51" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R51C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C51" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R51C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>152</v>
       </c>
@@ -7030,7 +6790,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R52C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>153</v>
       </c>
@@ -7043,20 +6803,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B54" s="9">
-        <f>_xll.qlBondCleanPrice(B34)</f>
-        <v>99.710822698691373</v>
+        <f>_xll.qlBondCleanPrice(B34,B53)</f>
+        <v>99.710822698691345</v>
       </c>
       <c r="C54" s="9">
-        <f>_xll.qlBondCleanPrice(C34)</f>
-        <v>99.710822698691373</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondCleanPrice(C34,C53)</f>
+        <v>99.710822698691345</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>56</v>
       </c>
@@ -7067,59 +6827,59 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B56" s="9">
         <f>_xll.qlBondCleanPrice2(B34,B55,"actual360","continuous")</f>
-        <v>99.710819325044909</v>
+        <v>99.710819325044866</v>
       </c>
       <c r="C56" s="9">
         <f>_xll.qlBondCleanPrice2(C34,C55,"actual360","continuous")</f>
-        <v>99.710819325044909</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99.710819325044866</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B57" s="9">
-        <f>_xll.qlBondDirtyPrice(B34)</f>
-        <v>99.727682727697726</v>
+        <f>_xll.qlBondDirtyPrice(B34,B53)</f>
+        <v>99.727682727697697</v>
       </c>
       <c r="C57" s="9">
-        <f>_xll.qlBondDirtyPrice(C34)</f>
-        <v>99.727682727697726</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondDirtyPrice(C34,C53)</f>
+        <v>99.727682727697697</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B58" s="9">
         <f>_xll.qlBondDirtyPrice2(B34,B55,"actual360","CONTINUOUS","annual")</f>
-        <v>99.727679354051261</v>
+        <v>99.727679354051219</v>
       </c>
       <c r="C58" s="9">
         <f>_xll.qlBondDirtyPrice2(C34,C55,"actual360","CONTINUOUS","annual")</f>
-        <v>99.727679354051261</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99.727679354051219</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B59" s="9">
-        <f>_xll.qlBondYield(B34,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(B34,"actual360","CONTINUOUS","annual",,,B53)</f>
         <v>2.9888064241409308E-2</v>
       </c>
       <c r="C59" s="9">
-        <f>_xll.qlBondYield(C34,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(C34,"actual360","CONTINUOUS","annual",,,C53)</f>
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>120</v>
       </c>
@@ -7132,7 +6892,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R60C3BondPrice,A</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>38</v>
       </c>
@@ -7145,7 +6905,7 @@
         <v>2.991248164176942E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>54</v>
       </c>
@@ -7156,43 +6916,43 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B63" s="9">
         <f>_xll.qlBondAccruedAmount(B34,B62)</f>
-        <v>1.6860029006353104E-2</v>
+        <v>1.6860029006353222E-2</v>
       </c>
       <c r="C63" s="9">
         <f>_xll.qlBondAccruedAmount(C34,C62)</f>
-        <v>1.6860029006353104E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1.6860029006353222E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B64" s="9">
-        <f>_xll.qlBondSettlementValue(B34)</f>
-        <v>149.59152409154657</v>
+        <f>_xll.qlBondSettlementValue(B34,B53)</f>
+        <v>149.59152409154655</v>
       </c>
       <c r="C64" s="9">
-        <f>_xll.qlBondSettlementValue(C34)</f>
-        <v>149.59152409154657</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondSettlementValue(C34,C53)</f>
+        <v>149.59152409154655</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B65" s="9">
         <f>_xll.qlBondSettlementValue2(B34,B54)</f>
-        <v>149.5915240915466</v>
+        <v>149.59152409154655</v>
       </c>
       <c r="C65" s="9">
         <f>_xll.qlBondSettlementValue2(C34,C54)</f>
-        <v>149.5915240915466</v>
+        <v>149.59152409154655</v>
       </c>
     </row>
   </sheetData>
@@ -7207,14 +6967,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05025377-E5EA-48F0-BE68-1C47A2C5C8E6}">
   <dimension ref="A1:C62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.28515625" customWidth="1"/>
-    <col min="2" max="2" width="67.28515625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="73.140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="44.33203125" customWidth="1"/>
+    <col min="2" max="2" width="67.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="73.109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -7222,7 +6982,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -7231,7 +6991,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -7242,7 +7002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -7253,7 +7013,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
@@ -7264,7 +7024,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -7275,7 +7035,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
@@ -7286,7 +7046,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -7299,7 +7059,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -7310,7 +7070,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>75</v>
       </c>
@@ -7321,7 +7081,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
@@ -7332,7 +7092,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -7343,7 +7103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -7356,20 +7116,20 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R14C3Schedule,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>55</v>
       </c>
       <c r="B15" s="14" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R15C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C15" s="14" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R15C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>89</v>
       </c>
@@ -7382,7 +7142,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R16C3Euribor,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -7393,7 +7153,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -7401,7 +7161,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -7409,7 +7169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -7417,7 +7177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -7425,17 +7185,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>95</v>
       </c>
@@ -7443,7 +7203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -7451,7 +7211,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -7459,7 +7219,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -7467,7 +7227,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -7476,7 +7236,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -7484,7 +7244,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -7492,7 +7252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>98</v>
       </c>
@@ -7505,20 +7265,20 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R31C3FloatingRateBond,A</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B32" s="3">
         <f>_xll.qlBondNextCouponRate(B31)</f>
-        <v>3.0348052211435581E-2</v>
+        <v>3.03480522114358E-2</v>
       </c>
       <c r="C32" s="3">
         <f>_xll.qlBondNextCouponRate(C31)</f>
-        <v>3.0348052211435581E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3.03480522114358E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>21</v>
       </c>
@@ -7531,7 +7291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>22</v>
       </c>
@@ -7544,7 +7304,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>23</v>
       </c>
@@ -7557,7 +7317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>24</v>
       </c>
@@ -7570,7 +7330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>25</v>
       </c>
@@ -7583,7 +7343,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>26</v>
       </c>
@@ -7596,7 +7356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>27</v>
       </c>
@@ -7609,7 +7369,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>28</v>
       </c>
@@ -7622,7 +7382,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>29</v>
       </c>
@@ -7635,7 +7395,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>30</v>
       </c>
@@ -7648,7 +7408,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R42C3CashFlow,A</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>57</v>
       </c>
@@ -7661,7 +7421,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R43C3CashFlow,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>58</v>
       </c>
@@ -7674,7 +7434,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R44C3CashFlow,A</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>31</v>
       </c>
@@ -7687,7 +7447,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>32</v>
       </c>
@@ -7700,7 +7460,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>59</v>
       </c>
@@ -7713,20 +7473,20 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B48" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R48C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C48" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R48C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>152</v>
       </c>
@@ -7739,7 +7499,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R49C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>153</v>
       </c>
@@ -7752,20 +7512,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B51" s="9">
-        <f>_xll.qlBondCleanPrice(B31)</f>
-        <v>99.596604611054204</v>
+        <f>_xll.qlBondCleanPrice(B31,B50)</f>
+        <v>99.596604611054161</v>
       </c>
       <c r="C51" s="9">
-        <f>_xll.qlBondCleanPrice(C31)</f>
-        <v>99.596604611054204</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondCleanPrice(C31,C50)</f>
+        <v>99.596604611054161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>56</v>
       </c>
@@ -7776,59 +7536,59 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B53" s="9">
         <f>_xll.qlBondCleanPrice2(B31,B52,"actual360","continuous")</f>
-        <v>99.596599916978278</v>
+        <v>99.596599916978249</v>
       </c>
       <c r="C53" s="9">
         <f>_xll.qlBondCleanPrice2(C31,C52,"actual360","continuous")</f>
-        <v>99.596599916978278</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99.596599916978249</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B54" s="9">
-        <f>_xll.qlBondDirtyPrice(B31)</f>
-        <v>99.613464640060556</v>
+        <f>_xll.qlBondDirtyPrice(B31,B50)</f>
+        <v>99.613464640060513</v>
       </c>
       <c r="C54" s="9">
-        <f>_xll.qlBondDirtyPrice(C31)</f>
-        <v>99.613464640060556</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondDirtyPrice(C31,C50)</f>
+        <v>99.613464640060513</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B55" s="9">
         <f>_xll.qlBondDirtyPrice2(B31,B52,"actual360","CONTINUOUS","annual")</f>
-        <v>99.61345994598463</v>
+        <v>99.613459945984602</v>
       </c>
       <c r="C55" s="9">
         <f>_xll.qlBondDirtyPrice2(C31,C52,"actual360","CONTINUOUS","annual")</f>
-        <v>99.61345994598463</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99.613459945984602</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B56" s="9">
-        <f>_xll.qlBondYield(B31,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(B31,"actual360","CONTINUOUS","annual",,,B50)</f>
         <v>2.9888064241409308E-2</v>
       </c>
       <c r="C56" s="9">
-        <f>_xll.qlBondYield(C31,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(C31,"actual360","CONTINUOUS","annual",,,C50)</f>
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>120</v>
       </c>
@@ -7841,7 +7601,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R57C3BondPrice,A</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>38</v>
       </c>
@@ -7854,7 +7614,7 @@
         <v>2.990561575889588E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>54</v>
       </c>
@@ -7865,43 +7625,43 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B60" s="9">
         <f>_xll.qlBondAccruedAmount(B31,B59)</f>
-        <v>1.6860029006353101E-2</v>
+        <v>1.6860029006353222E-2</v>
       </c>
       <c r="C60" s="9">
         <f>_xll.qlBondAccruedAmount(C31,C59)</f>
-        <v>1.6860029006353101E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1.6860029006353222E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B61" s="9">
-        <f>_xll.qlBondSettlementValue(B31)</f>
-        <v>99.613464640060556</v>
+        <f>_xll.qlBondSettlementValue(B31,B50)</f>
+        <v>99.613464640060513</v>
       </c>
       <c r="C61" s="9">
-        <f>_xll.qlBondSettlementValue(C31)</f>
-        <v>99.613464640060556</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondSettlementValue(C31,C50)</f>
+        <v>99.613464640060513</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B62" s="9">
         <f>_xll.qlBondSettlementValue2(B31,B51)</f>
-        <v>99.613464640060556</v>
+        <v>99.613464640060513</v>
       </c>
       <c r="C62" s="9">
         <f>_xll.qlBondSettlementValue2(C31,C51)</f>
-        <v>99.613464640060556</v>
+        <v>99.613464640060513</v>
       </c>
     </row>
   </sheetData>
@@ -7912,14 +7672,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27515A30-3B44-433D-8DBF-ACC4ED7765FD}">
   <dimension ref="A1:C67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.140625" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="46.109375" customWidth="1"/>
+    <col min="2" max="2" width="58.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="46.5546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -7927,7 +7687,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -7936,7 +7696,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -7947,7 +7707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -7958,7 +7718,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
@@ -7969,7 +7729,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -7980,7 +7740,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
@@ -7991,7 +7751,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -8004,7 +7764,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -8015,7 +7775,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>75</v>
       </c>
@@ -8026,7 +7786,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
@@ -8037,7 +7797,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -8048,7 +7808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -8061,7 +7821,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R14C3Schedule,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>101</v>
       </c>
@@ -8072,7 +7832,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>46</v>
       </c>
@@ -8083,7 +7843,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>14</v>
       </c>
@@ -8094,7 +7854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>103</v>
       </c>
@@ -8105,7 +7865,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>60</v>
       </c>
@@ -8118,7 +7878,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>105</v>
       </c>
@@ -8129,7 +7889,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>106</v>
       </c>
@@ -8140,7 +7900,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>107</v>
       </c>
@@ -8151,7 +7911,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>109</v>
       </c>
@@ -8164,20 +7924,20 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R23C3Euribor,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>110</v>
       </c>
       <c r="B24" s="6" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R24C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C24" s="6" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R24C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>100</v>
       </c>
@@ -8190,7 +7950,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R25C3SwapIndex,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -8201,7 +7961,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -8212,7 +7972,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>90</v>
       </c>
@@ -8223,7 +7983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>91</v>
       </c>
@@ -8234,7 +7994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -8245,7 +8005,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>93</v>
       </c>
@@ -8256,7 +8016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>94</v>
       </c>
@@ -8267,7 +8027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -8275,7 +8035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>63</v>
       </c>
@@ -8283,7 +8043,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -8291,7 +8051,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>99</v>
       </c>
@@ -8304,7 +8064,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R36C3CmsRateBond,A</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>20</v>
       </c>
@@ -8317,7 +8077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>21</v>
       </c>
@@ -8330,7 +8090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>22</v>
       </c>
@@ -8343,7 +8103,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>23</v>
       </c>
@@ -8356,7 +8116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>24</v>
       </c>
@@ -8369,7 +8129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>25</v>
       </c>
@@ -8382,7 +8142,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>26</v>
       </c>
@@ -8395,7 +8155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>27</v>
       </c>
@@ -8408,7 +8168,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>28</v>
       </c>
@@ -8421,7 +8181,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>29</v>
       </c>
@@ -8434,7 +8194,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>30</v>
       </c>
@@ -8447,7 +8207,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R47C3CashFlow,A</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>57</v>
       </c>
@@ -8460,7 +8220,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R48C3CashFlow,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>58</v>
       </c>
@@ -8473,7 +8233,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R49C3CashFlow,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
@@ -8486,7 +8246,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>32</v>
       </c>
@@ -8499,7 +8259,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>59</v>
       </c>
@@ -8512,20 +8272,20 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B53" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R53C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C53" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R53C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>152</v>
       </c>
@@ -8538,7 +8298,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R54C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>153</v>
       </c>
@@ -8551,83 +8311,83 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B56" s="9">
-        <f>_xll.qlBondCleanPrice(B36)</f>
+        <f>_xll.qlBondCleanPrice(B36,B55)</f>
         <v>71.653019933502407</v>
       </c>
       <c r="C56" s="9">
-        <f>_xll.qlBondCleanPrice(C36)</f>
+        <f>_xll.qlBondCleanPrice(C36,C55)</f>
         <v>85.983623920202888</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B57" s="9">
-        <v>2.9888064241409308E-2</v>
+        <v>2.9888064241409301E-2</v>
       </c>
       <c r="C57" s="9">
-        <v>2.9888064241409308E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2.9888064241409301E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B58" s="9">
         <f>_xll.qlBondCleanPrice2(B36,B57,"actual360","continuous")</f>
-        <v>71.653016028468727</v>
+        <v>71.653016028468784</v>
       </c>
       <c r="C58" s="9">
         <f>_xll.qlBondCleanPrice2(C36,C57,"actual360","continuous")</f>
-        <v>85.983619234162475</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>85.983619234162546</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B59" s="9">
-        <f>_xll.qlBondDirtyPrice(B36)</f>
+        <f>_xll.qlBondDirtyPrice(B36,B55)</f>
         <v>71.653019933502407</v>
       </c>
       <c r="C59" s="9">
-        <f>_xll.qlBondDirtyPrice(C36)</f>
+        <f>_xll.qlBondDirtyPrice(C36,C55)</f>
         <v>85.983623920202888</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B60" s="9">
         <f>_xll.qlBondDirtyPrice2(B36,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>71.653016028468727</v>
+        <v>71.653016028468784</v>
       </c>
       <c r="C60" s="9">
         <f>_xll.qlBondDirtyPrice2(C36,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>85.983619234162475</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>85.983619234162546</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B61" s="9">
-        <f>_xll.qlBondYield(B36,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(B36,"actual360","CONTINUOUS","annual",,,B55)</f>
         <v>2.9888064241409308E-2</v>
       </c>
       <c r="C61" s="9">
-        <f>_xll.qlBondYield(C36,"actual360","CONTINUOUS","annual")</f>
+        <f>_xll.qlBondYield(C36,"actual360","CONTINUOUS","annual",,,C55)</f>
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>120</v>
       </c>
@@ -8640,7 +8400,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R62C3BondPrice,A</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>38</v>
       </c>
@@ -8653,7 +8413,7 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>54</v>
       </c>
@@ -8664,7 +8424,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>39</v>
       </c>
@@ -8677,20 +8437,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B66" s="9">
-        <f>_xll.qlBondSettlementValue(B36)</f>
+        <f>_xll.qlBondSettlementValue(B36,B55)</f>
         <v>71.653019933502407</v>
       </c>
       <c r="C66" s="9">
-        <f>_xll.qlBondSettlementValue(C36)</f>
-        <v>85.983623920202874</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <f>_xll.qlBondSettlementValue(C36,C55)</f>
+        <v>85.983623920202888</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>41</v>
       </c>

--- a/tests/workbooktests/workbooks/test_bonds.xlsx
+++ b/tests/workbooktests/workbooks/test_bonds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F7C303-12C7-40E2-B231-BB6B8BA4FB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67234E4C-50B7-4352-B9FD-9916C18D493D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3645" yWindow="-19185" windowWidth="30690" windowHeight="16530" firstSheet="7" activeTab="12" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
@@ -3724,7 +3724,7 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C4" s="6"/>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
@@ -3742,17 +3742,17 @@
       </c>
       <c r="C5" s="6"/>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B6" s="11">
-        <f>_xll.qlCalendarAdvance2(B4,B5,"10y","following")</f>
+        <f>_xll.qlCalendarAdvance(B4,B5,"10y","following")</f>
         <v>49317</v>
       </c>
       <c r="C6" s="6"/>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>47</v>
       </c>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>48</v>
       </c>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>49</v>
       </c>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="6">
         <v>103</v>
@@ -3798,7 +3798,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="6">
         <v>103</v>
@@ -3807,42 +3807,42 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6">
         <v>103</v>
       </c>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="6">
         <v>103</v>
       </c>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6">
         <v>102</v>
       </c>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="6">
         <v>102</v>
       </c>
       <c r="C16" s="6"/>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="6">
         <v>102</v>
       </c>
       <c r="C17" s="6"/>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="6">
         <v>102</v>

--- a/tests/workbooktests/workbooks/test_bonds.xlsx
+++ b/tests/workbooktests/workbooks/test_bonds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67234E4C-50B7-4352-B9FD-9916C18D493D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210FD972-46B1-4CAB-9F2D-C79A32D0F197}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
@@ -33,17 +33,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -52,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="171">
   <si>
     <t>Bond</t>
   </si>
@@ -459,9 +448,6 @@
     <t>act/360</t>
   </si>
   <si>
-    <t>Put</t>
-  </si>
-  <si>
     <t xml:space="preserve">date </t>
   </si>
   <si>
@@ -514,6 +500,60 @@
   </si>
   <si>
     <t>qlInstrumentPricingEngine</t>
+  </si>
+  <si>
+    <t>target_price</t>
+  </si>
+  <si>
+    <t>discounting_curve</t>
+  </si>
+  <si>
+    <t>accuracy</t>
+  </si>
+  <si>
+    <t>max_evaluations</t>
+  </si>
+  <si>
+    <t>min_vol</t>
+  </si>
+  <si>
+    <t>max_vol</t>
+  </si>
+  <si>
+    <t>6M</t>
+  </si>
+  <si>
+    <t>Backward</t>
+  </si>
+  <si>
+    <t>Call</t>
+  </si>
+  <si>
+    <t>qlBondCleanPriceFromZSpread</t>
+  </si>
+  <si>
+    <t>z_spread</t>
+  </si>
+  <si>
+    <t>compounding</t>
+  </si>
+  <si>
+    <t>dc</t>
+  </si>
+  <si>
+    <t>freq</t>
+  </si>
+  <si>
+    <t>settlement_date</t>
+  </si>
+  <si>
+    <t>actual365fixed</t>
+  </si>
+  <si>
+    <t>Compounded</t>
+  </si>
+  <si>
+    <t>Annual</t>
   </si>
 </sst>
 </file>
@@ -703,7 +743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -760,6 +800,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -771,7 +821,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -787,9 +837,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -827,7 +877,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -933,7 +983,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1075,7 +1125,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1084,27 +1134,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F1B31AC-6B78-4845-B599-86FA814CB2D7}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="15"/>
-    <col min="2" max="2" width="36.109375" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" customWidth="1"/>
-    <col min="4" max="4" width="33.88671875" customWidth="1"/>
-    <col min="5" max="5" width="32.109375" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="15"/>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" customWidth="1"/>
+    <col min="5" max="5" width="32.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-    </row>
-    <row r="3" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+    </row>
+    <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="17"/>
       <c r="C3" s="18" t="s">
         <v>51</v>
@@ -1116,7 +1166,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="29" t="s">
         <v>116</v>
       </c>
@@ -1124,7 +1174,7 @@
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>0</v>
       </c>
@@ -1134,7 +1184,7 @@
       <c r="D5" s="21"/>
       <c r="E5" s="22"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
         <v>1</v>
       </c>
@@ -1144,7 +1194,7 @@
       <c r="D6" s="21"/>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>2</v>
       </c>
@@ -1154,7 +1204,7 @@
       <c r="D7" s="21"/>
       <c r="E7" s="22"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="20" t="s">
         <v>3</v>
       </c>
@@ -1164,7 +1214,7 @@
       <c r="D8" s="21"/>
       <c r="E8" s="22"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
         <v>4</v>
       </c>
@@ -1174,7 +1224,7 @@
       <c r="D9" s="21"/>
       <c r="E9" s="22"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
         <v>5</v>
       </c>
@@ -1184,7 +1234,7 @@
       <c r="D10" s="21"/>
       <c r="E10" s="22"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
         <v>6</v>
       </c>
@@ -1194,7 +1244,7 @@
       <c r="D11" s="21"/>
       <c r="E11" s="22"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="26" t="s">
         <v>7</v>
       </c>
@@ -1204,7 +1254,7 @@
       <c r="D12" s="21"/>
       <c r="E12" s="22"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="26" t="s">
         <v>124</v>
       </c>
@@ -1212,7 +1262,7 @@
       <c r="D13" s="21"/>
       <c r="E13" s="22"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
         <v>8</v>
       </c>
@@ -1222,7 +1272,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
         <v>9</v>
       </c>
@@ -1232,7 +1282,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>11</v>
       </c>
@@ -1251,35 +1301,35 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ABD84F-1436-4AE1-BC17-091C65B56114}">
-  <dimension ref="A1:C68"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.5546875" customWidth="1"/>
-    <col min="2" max="2" width="73.88671875" customWidth="1"/>
-    <col min="3" max="3" width="71.109375" customWidth="1"/>
+    <col min="1" max="1" width="48.5703125" customWidth="1"/>
+    <col min="2" max="2" width="73.85546875" customWidth="1"/>
+    <col min="3" max="3" width="71.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1290,8 +1340,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="3">
@@ -1301,8 +1351,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="40"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
@@ -1310,8 +1360,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="40"/>
       <c r="B7" s="3">
         <v>101</v>
       </c>
@@ -1319,7 +1369,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>73</v>
       </c>
@@ -1330,7 +1380,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
@@ -1341,18 +1391,18 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>60</v>
       </c>
@@ -1365,7 +1415,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
@@ -1376,7 +1426,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>75</v>
       </c>
@@ -1387,7 +1437,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>77</v>
       </c>
@@ -1398,7 +1448,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>78</v>
       </c>
@@ -1409,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -1422,7 +1472,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R16C3Schedule,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>101</v>
       </c>
@@ -1433,7 +1483,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>46</v>
       </c>
@@ -1444,7 +1494,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>14</v>
       </c>
@@ -1455,7 +1505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>103</v>
       </c>
@@ -1466,7 +1516,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>60</v>
       </c>
@@ -1479,7 +1529,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>105</v>
       </c>
@@ -1490,7 +1540,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>106</v>
       </c>
@@ -1501,18 +1551,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>107</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>109</v>
       </c>
@@ -1525,7 +1575,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R25C3Euribor,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>110</v>
       </c>
@@ -1538,7 +1588,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>100</v>
       </c>
@@ -1551,18 +1601,18 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R27C3SwapIndex,A</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>67</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -1571,7 +1621,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>90</v>
       </c>
@@ -1580,7 +1630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>91</v>
       </c>
@@ -1589,7 +1639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>92</v>
       </c>
@@ -1598,7 +1648,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>93</v>
       </c>
@@ -1607,7 +1657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>94</v>
       </c>
@@ -1616,7 +1666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>95</v>
       </c>
@@ -1625,7 +1675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1634,7 +1684,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>111</v>
       </c>
@@ -1647,7 +1697,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R37C3AmortizingCmsRateBond,A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>20</v>
       </c>
@@ -1660,7 +1710,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>21</v>
       </c>
@@ -1673,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>22</v>
       </c>
@@ -1686,7 +1736,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>23</v>
       </c>
@@ -1699,7 +1749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>24</v>
       </c>
@@ -1712,20 +1762,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B43" s="2">
         <f>_xll.qlBondSettlementDate(B37)</f>
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C43" s="2">
         <f>_xll.qlBondSettlementDate(C37)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>26</v>
       </c>
@@ -1738,7 +1788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>27</v>
       </c>
@@ -1751,7 +1801,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>28</v>
       </c>
@@ -1764,7 +1814,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>29</v>
       </c>
@@ -1777,7 +1827,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>30</v>
       </c>
@@ -1790,7 +1840,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R48C3CashFlow,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>57</v>
       </c>
@@ -1803,7 +1853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>58</v>
       </c>
@@ -1816,7 +1866,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R50C3CashFlow,A</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>31</v>
       </c>
@@ -1829,7 +1879,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>32</v>
       </c>
@@ -1842,7 +1892,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>59</v>
       </c>
@@ -1855,7 +1905,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>55</v>
       </c>
@@ -1868,9 +1918,9 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B55" s="3" t="str">
         <f>_xll.qlDiscountingBondEngine(B54)</f>
@@ -1881,9 +1931,9 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R55C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B56" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B37,B55)</f>
@@ -1894,20 +1944,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B57" s="9">
         <f>_xll.qlBondCleanPrice(B37,B56)</f>
-        <v>72.117682106498322</v>
+        <v>72.093736554270748</v>
       </c>
       <c r="C57" s="9">
         <f>_xll.qlBondCleanPrice(C37,C56)</f>
-        <v>74.834890455035776</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+        <v>74.811708809405872</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>56</v>
       </c>
@@ -1918,46 +1968,46 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B59" s="9">
         <f>_xll.qlBondCleanPrice2(B37,B58,"actual360","continuous")</f>
-        <v>72.117678263617449</v>
+        <v>72.09373270875146</v>
       </c>
       <c r="C59" s="9">
         <f>_xll.qlBondCleanPrice2(C37,C58,"actual360","continuous")</f>
-        <v>74.834886535610039</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+        <v>74.811704887219548</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B60" s="9">
         <f>_xll.qlBondDirtyPrice(B37,B56)</f>
-        <v>72.117682106498322</v>
+        <v>72.093736554270748</v>
       </c>
       <c r="C60" s="9">
         <f>_xll.qlBondDirtyPrice(C37,C56)</f>
-        <v>74.836557121702455</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+        <v>74.811708809405872</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B61" s="9">
         <f>_xll.qlBondDirtyPrice2(B37,B58,"actual360","CONTINUOUS","annual")</f>
-        <v>72.117678263617449</v>
+        <v>72.09373270875146</v>
       </c>
       <c r="C61" s="9">
         <f>_xll.qlBondDirtyPrice2(C37,C58,"actual360","CONTINUOUS","annual")</f>
-        <v>74.836553202276718</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+        <v>74.811704887219548</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>37</v>
       </c>
@@ -1970,7 +2020,7 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>120</v>
       </c>
@@ -1983,7 +2033,7 @@
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R63C3BondPrice,A</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>38</v>
       </c>
@@ -1993,10 +2043,10 @@
       </c>
       <c r="C64" s="9">
         <f>_xll.qlBondYield2(C37,C63,"actual360","CONTINUOUS","annual")</f>
-        <v>2.9890143346786503E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>54</v>
       </c>
@@ -2007,7 +2057,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>39</v>
       </c>
@@ -2020,30 +2070,107 @@
         <v>1.6666666666775853E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B67" s="9">
         <f>_xll.qlBondSettlementValue(B37,B56)</f>
-        <v>74.281212569693267</v>
+        <v>74.256548650898864</v>
       </c>
       <c r="C67" s="9">
         <f>_xll.qlBondSettlementValue(C37,C56)</f>
-        <v>77.081653835353535</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+        <v>77.056060073688045</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B68" s="9">
         <f>_xll.qlBondSettlementValue2(B37,B57)</f>
-        <v>74.281212569693281</v>
+        <v>74.256548650898864</v>
       </c>
       <c r="C68" s="9">
         <f>_xll.qlBondSettlementValue2(C37,C57)</f>
-        <v>77.081653835353521</v>
+        <v>77.056060073688045</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R69C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C69" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R69C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B70" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C70" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B75" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B37,B69,B70,B71,B72,B73)</f>
+        <v>68.658262971981003</v>
+      </c>
+      <c r="C75" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C37,C69,C70,C71,C72,C73)</f>
+        <v>71.307194575057778</v>
       </c>
     </row>
   </sheetData>
@@ -2057,14 +2184,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F09BC366-53EA-43EA-8BCB-0489C1B271E0}">
   <dimension ref="A3:B12"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="45.44140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="45.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>125</v>
       </c>
@@ -2073,7 +2200,7 @@
         <v>欣[test_bonds.xlsx]Callability!R3C2BondPrice,A</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -2081,7 +2208,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -2089,7 +2216,7 @@
         <v>46357</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>129</v>
       </c>
@@ -2098,7 +2225,7 @@
         <v>欣[test_bonds.xlsx]Callability!R6C2Callability,A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>130</v>
       </c>
@@ -2107,7 +2234,7 @@
         <v>欣[test_bonds.xlsx]Callability!R7C2BondPrice,A</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>131</v>
       </c>
@@ -2116,7 +2243,7 @@
         <v>46357</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>132</v>
       </c>
@@ -2125,7 +2252,7 @@
         <v>PUT</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
     </row>
   </sheetData>
@@ -2135,43 +2262,43 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0A1FE9-B1FE-4762-AEA9-E4B3F6C519F7}">
-  <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C81"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.6640625" customWidth="1"/>
-    <col min="2" max="2" width="93.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="75.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="47.7109375" customWidth="1"/>
+    <col min="2" max="2" width="93.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="75.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -2182,40 +2309,40 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B6" s="11">
-        <v>45665</v>
+        <v>45659</v>
       </c>
       <c r="C6" s="11">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B7" s="11">
-        <v>49682</v>
+        <v>48215</v>
       </c>
       <c r="C7" s="11">
-        <v>49682</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+        <v>48215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -2228,7 +2355,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -2239,7 +2366,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>75</v>
       </c>
@@ -2250,29 +2377,29 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="6">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -2285,47 +2412,47 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R14C3Schedule,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="3">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="C15" s="3">
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="40"/>
       <c r="B16" s="3">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="C16" s="3">
         <v>0.03</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="40"/>
       <c r="B17" s="3">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="C17" s="3">
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>83</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -2336,7 +2463,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -2347,7 +2474,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -2358,42 +2485,42 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>120</v>
       </c>
       <c r="B22" s="2" t="str">
-        <f>_xll.qlBondPrice(100,"CLEAN")</f>
+        <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R22C2BondPrice,A</v>
       </c>
       <c r="C22" s="2" t="str">
-        <f>_xll.qlBondPrice(100,"CLEAN")</f>
+        <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R22C3BondPrice,A</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="B24" s="2">
-        <v>47664</v>
+        <v>46754</v>
       </c>
       <c r="C24" s="2">
-        <v>47664</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>46754</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>133</v>
       </c>
@@ -2406,7 +2533,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R25C3Callability,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -2417,7 +2544,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -2430,7 +2557,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -2438,7 +2565,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -2446,9 +2573,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B30" s="3" t="str">
         <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25)</f>
@@ -2459,20 +2586,20 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R30C3CallableFixedRateBond,A</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B31" s="3">
         <f>_xll.qlBondNextCouponRate(B30)</f>
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="C31" s="3">
         <f>_xll.qlBondNextCouponRate(C30)</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>21</v>
       </c>
@@ -2485,20 +2612,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="2">
         <f>_xll.qlBondNextCashFlowDate(B30)</f>
-        <v>46030</v>
+        <v>45840</v>
       </c>
       <c r="C33" s="2">
         <f>_xll.qlBondNextCashFlowDate(C30)</f>
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45840</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>23</v>
       </c>
@@ -2511,33 +2638,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B35" s="3">
         <f>_xll.qlBondSettlementDays(B30)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" s="3">
         <f>_xll.qlBondSettlementDays(C30)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B36" s="2">
         <f>_xll.qlBondSettlementDate(B30)</f>
-        <v>45670</v>
+        <v>45665</v>
       </c>
       <c r="C36" s="2">
         <f>_xll.qlBondSettlementDate(C30)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>26</v>
       </c>
@@ -2550,33 +2677,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B38" s="2">
         <f>_xll.qlBondStartDate(B30)</f>
-        <v>45665</v>
+        <v>45659</v>
       </c>
       <c r="C38" s="2">
         <f>_xll.qlBondStartDate(C30)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B39" s="2">
         <f>_xll.qlBondMaturityDate(B30)</f>
-        <v>49682</v>
+        <v>48215</v>
       </c>
       <c r="C39" s="2">
         <f>_xll.qlBondMaturityDate(C30)</f>
-        <v>49682</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+        <v>48215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>29</v>
       </c>
@@ -2589,7 +2716,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>30</v>
       </c>
@@ -2602,7 +2729,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R41C3CashFlow,A</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>57</v>
       </c>
@@ -2615,7 +2742,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R42C3CashFlow,A</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>58</v>
       </c>
@@ -2628,7 +2755,7 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R43C3CashFlow,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>31</v>
       </c>
@@ -2641,7 +2768,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>32</v>
       </c>
@@ -2654,7 +2781,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>59</v>
       </c>
@@ -2667,33 +2794,33 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B47" s="3">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C47" s="3">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="30" t="s">
         <v>110</v>
       </c>
       <c r="B48" s="3" t="str">
-        <f>_xll.qlFlatForward(B2,0.025,"actual360")</f>
+        <f>_xll.qlFlatForward($B$2,0.03,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C48" s="3" t="str">
-        <f>_xll.qlFlatForward(B2,0.025,"actual360")</f>
+        <f>_xll.qlFlatForward($B$2,0.03,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(B47,B48)</f>
@@ -2704,9 +2831,9 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R49C3BlackCallableFixedRateBondEngine,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B50" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B30,B49)</f>
@@ -2717,20 +2844,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B51" s="33">
         <f>_xll.qlBondCleanPrice(B30,B50)</f>
-        <v>104.56552586351701</v>
+        <v>110.06392336774921</v>
       </c>
       <c r="C51" s="33">
         <f>_xll.qlBondCleanPrice(C30,C50)</f>
-        <v>104.93923846207524</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.445095445011546</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>56</v>
       </c>
@@ -2741,59 +2868,59 @@
         <v>2.8928264971926201E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B53" s="9">
         <f>_xll.qlBondCleanPrice2(B30,B52,"actual360","continuous")</f>
-        <v>100.20194238732337</v>
+        <v>119.08137817483198</v>
       </c>
       <c r="C53" s="9">
         <f>_xll.qlBondCleanPrice2(C30,C52,"actual360","continuous")</f>
-        <v>100.60282643461134</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+        <v>100.54500989207793</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B54" s="9">
         <f>_xll.qlBondDirtyPrice(B30,B50)</f>
-        <v>104.60719253018368</v>
+        <v>110.16392336774921</v>
       </c>
       <c r="C54" s="9">
         <f>_xll.qlBondDirtyPrice(C30,C50)</f>
-        <v>104.9559051287419</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.495095445011543</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B55" s="9">
         <f>_xll.qlBondDirtyPrice2(B30,B52,"actual360","CONTINUOUS","annual")</f>
-        <v>100.24360905399004</v>
+        <v>119.18137817483198</v>
       </c>
       <c r="C55" s="9">
         <f>_xll.qlBondDirtyPrice2(C30,C52,"actual360","CONTINUOUS","annual")</f>
-        <v>100.61949310127801</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+        <v>100.59500989207793</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B56" s="9">
         <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual",,,B50)</f>
-        <v>2.4524004602432259E-2</v>
+        <v>4.2093677997589118E-2</v>
       </c>
       <c r="C56" s="9">
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual",,,C50)</f>
-        <v>2.4563668775558482E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3.0637670373916633E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>120</v>
       </c>
@@ -2806,20 +2933,20 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R57C3BondPrice,A</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B58" s="9">
         <f>_xll.qlBondYield2(B30,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>2.4565103197097787E-2</v>
+        <v>4.2246308316370287E-2</v>
       </c>
       <c r="C58" s="9">
         <f>_xll.qlBondYield2(C30,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>2.458006670921447E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3.0715854406356817E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>54</v>
       </c>
@@ -2830,48 +2957,48 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B60" s="9">
         <f>_xll.qlBondAccruedAmount(B30,B59)</f>
-        <v>1.6666666666664831E-2</v>
+        <v>0.13333333333334085</v>
       </c>
       <c r="C60" s="9">
         <f>_xll.qlBondAccruedAmount(C30,C59)</f>
-        <v>1.6666666666664831E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+        <v>6.6666666666659324E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B61" s="9">
         <f>_xll.qlBondSettlementValue(B30,B50)</f>
-        <v>104.60719253018367</v>
+        <v>110.16392336774922</v>
       </c>
       <c r="C61" s="9">
         <f>_xll.qlBondSettlementValue(C30,C50)</f>
-        <v>104.9559051287419</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.495095445011543</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B62" s="9">
         <f>_xll.qlBondSettlementValue2(B30,B51)</f>
-        <v>104.6071925301837</v>
+        <v>110.16392336774921</v>
       </c>
       <c r="C62" s="9">
         <f>_xll.qlBondSettlementValue2(C30,C51)</f>
-        <v>104.9559051287419</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.495095445011543</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B63" s="3" t="str">
         <f>_xll.qlCallableBondCallability(B30)</f>
@@ -2882,9 +3009,9 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R63C3Callability,A</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="B64" s="3" t="str">
         <f>_xll.qlBondPrice(B51,"Clean")</f>
@@ -2895,61 +3022,203 @@
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R64C3BondPrice,A</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="32" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" s="3" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R65C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C65" s="3" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R65C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" s="34">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C66" s="34">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B67" s="3">
+        <v>100</v>
+      </c>
+      <c r="C67" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B68" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="C68" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C69" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="36">
+        <f>_xll.qlCallableBondImpliedVolatility(B30,B64,B65,B66,B67,B68,B69)</f>
+        <v>0.3367870577176853</v>
+      </c>
+      <c r="C70" s="36">
+        <f>_xll.qlCallableBondImpliedVolatility(C30,C64,C65,C66,C67,C68,C69)</f>
+        <v>0.25291424428606024</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="32" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="B66" s="3">
+      <c r="B71" s="3">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(B30,105,B48,"Actual/360","Simple","Annual",,,1000,,B50))</f>
         <v>1</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C71" s="3">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(C30,105,C48,"Actual/360","Simple","Annual",,,1000,,C50))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" s="3">
+        <f>_xll.qlCallableBondCleanPriceOAS(B30,0.3,B48,"actual/360","simple","annual",,B50)</f>
+        <v>110.008855174261</v>
+      </c>
+      <c r="C72" s="3">
+        <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual",,C50)</f>
+        <v>99.395360332103436</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B67" s="3">
-        <f>_xll.qlCallableBondCleanPriceOAS(B30,0.3,B48,"actual/360","simple","annual",,B50)</f>
-        <v>104.52921022682914</v>
-      </c>
-      <c r="C67" s="3">
-        <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual",,C50)</f>
-        <v>104.92466226528889</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
+      <c r="B73" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
+        <v>0</v>
+      </c>
+      <c r="C73" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(C30,0.3,C48,"actual/360","compounded","annual",,C50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B68" s="3">
-        <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
-        <v>0</v>
-      </c>
-      <c r="C68" s="3">
-        <f>_xll.qlCallableBondEffectiveDuration(C30,0.3,C48,"actual/360","compounded","annual",,C50)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" s="3">
+      <c r="B74" s="3">
         <f>_xll.qlCallableBondEffectiveConvexity(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
         <v>0</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C74" s="3">
         <f>_xll.qlCallableBondEffectiveConvexity(C30,0.3,C48,"actual/360","compounded","annual",,C50)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R75C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C75" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R75C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B76" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C76" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B30,B75,B76,B77,B78,B79)</f>
+        <v>115.26309756278064</v>
+      </c>
+      <c r="C81" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C30,C75,C76,C77,C78,C79)</f>
+        <v>97.091946053546252</v>
       </c>
     </row>
   </sheetData>
@@ -2963,32 +3232,32 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4EF9C2-FD4D-4E7F-8154-C8E782972C6B}">
-  <dimension ref="A1:C54"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C68"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.109375" customWidth="1"/>
-    <col min="2" max="2" width="89.5546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="73.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="44.140625" customWidth="1"/>
+    <col min="2" max="2" width="89.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="73.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2999,7 +3268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3010,7 +3279,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -3023,7 +3292,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3034,26 +3303,26 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -3061,7 +3330,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -3069,42 +3338,42 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>120</v>
       </c>
       <c r="B12" s="2" t="str">
-        <f>_xll.qlBondPrice(100,"CLEAN")</f>
+        <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C2BondPrice,A</v>
       </c>
       <c r="C12" s="2" t="str">
-        <f>_xll.qlBondPrice(100,"CLEAN")</f>
+        <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C3BondPrice,A</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="B14" s="2">
-        <v>47664</v>
+        <v>46754</v>
       </c>
       <c r="C14" s="2">
-        <v>47664</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>46754</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -3117,9 +3386,9 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C3Callability,A</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B16" s="3" t="str">
         <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15)</f>
@@ -3130,7 +3399,7 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C3CallableZeroCouponBond,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
@@ -3143,7 +3412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>21</v>
       </c>
@@ -3156,7 +3425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>22</v>
       </c>
@@ -3169,7 +3438,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
@@ -3182,7 +3451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>24</v>
       </c>
@@ -3195,20 +3464,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="2">
         <f>_xll.qlBondSettlementDate(B16)</f>
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C22" s="2">
         <f>_xll.qlBondSettlementDate(C16)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>26</v>
       </c>
@@ -3221,7 +3490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>27</v>
       </c>
@@ -3234,7 +3503,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>28</v>
       </c>
@@ -3247,7 +3516,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
@@ -3260,7 +3529,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>30</v>
       </c>
@@ -3273,7 +3542,7 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C3CashFlow,A</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>57</v>
       </c>
@@ -3286,7 +3555,7 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C3CashFlow,A</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>58</v>
       </c>
@@ -3299,7 +3568,7 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C3CashFlow,A</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
@@ -3312,7 +3581,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>32</v>
       </c>
@@ -3325,7 +3594,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>59</v>
       </c>
@@ -3338,9 +3607,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B33" s="3">
         <v>0.15</v>
@@ -3349,7 +3618,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="30" t="s">
         <v>110</v>
       </c>
@@ -3362,9 +3631,9 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B35" s="3" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(B33,B34)</f>
@@ -3375,9 +3644,9 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R35C3BlackCallableFixedRateBondEngine,A</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B36" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B16,B35)</f>
@@ -3388,20 +3657,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B37" s="9">
         <f>_xll.qlBondCleanPrice(B16,B36)</f>
-        <v>84.712567119963055</v>
+        <v>71.629227252608828</v>
       </c>
       <c r="C37" s="9">
         <f>_xll.qlBondCleanPrice(C16,C36)</f>
-        <v>84.712567119963055</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71.641121879613067</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>56</v>
       </c>
@@ -3412,59 +3681,59 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B39" s="9">
         <f>_xll.qlBondCleanPrice2(B16,B38,"actual360","continuous")</f>
-        <v>71.65301602846877</v>
+        <v>71.629224757480401</v>
       </c>
       <c r="C39" s="9">
         <f>_xll.qlBondCleanPrice2(C16,C38,"actual360","continuous")</f>
-        <v>71.65301602846877</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71.641119405370375</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B40" s="9">
         <f>_xll.qlBondDirtyPrice(B16,B36)</f>
-        <v>84.712567119963055</v>
+        <v>71.629227252608828</v>
       </c>
       <c r="C40" s="9">
         <f>_xll.qlBondDirtyPrice(C16,C36)</f>
-        <v>84.712567119963055</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71.641121879613067</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="9">
         <f>_xll.qlBondDirtyPrice2(B16,B38,"actual360","CONTINUOUS","annual")</f>
-        <v>71.65301602846877</v>
+        <v>71.629224757480401</v>
       </c>
       <c r="C41" s="9">
         <f>_xll.qlBondDirtyPrice2(C16,C38,"actual360","CONTINUOUS","annual")</f>
-        <v>71.65301602846877</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71.641119405370375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B42" s="9">
         <f>_xll.qlBondYield(B16,"actual360","CONTINUOUS","annual",,,B36)</f>
-        <v>1.4875779507160188E-2</v>
+        <v>2.9888064241409308E-2</v>
       </c>
       <c r="C42" s="9">
         <f>_xll.qlBondYield(C16,"actual360","CONTINUOUS","annual",,,C36)</f>
-        <v>1.4875779507160188E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>120</v>
       </c>
@@ -3477,20 +3746,20 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C3BondPrice,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B44" s="9">
         <f>_xll.qlBondYield2(B16,B43,"actual360","CONTINUOUS","annual")</f>
-        <v>1.4875779507160188E-2</v>
+        <v>2.9888064241409308E-2</v>
       </c>
       <c r="C44" s="9">
         <f>_xll.qlBondYield2(C16,C43,"actual360","CONTINUOUS","annual")</f>
-        <v>1.4875779507160188E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>54</v>
       </c>
@@ -3501,7 +3770,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>39</v>
       </c>
@@ -3514,35 +3783,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B47" s="9">
         <f>_xll.qlBondSettlementValue(B16,B36)</f>
-        <v>84.712567119963055</v>
+        <v>71.629227252608828</v>
       </c>
       <c r="C47" s="9">
         <f>_xll.qlBondSettlementValue(C16,C36)</f>
-        <v>84.712567119963055</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71.641121879613067</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B48" s="9">
         <f>_xll.qlBondSettlementValue2(B16,B37)</f>
-        <v>84.712567119963055</v>
+        <v>71.629227252608828</v>
       </c>
       <c r="C48" s="9">
         <f>_xll.qlBondSettlementValue2(C16,C37)</f>
-        <v>84.712567119963055</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71.641121879613067</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>_xll.qlCallableBondCallability(B16)</f>
@@ -3553,61 +3822,229 @@
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C3Callability,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" s="3" t="str">
+        <f>_xll.qlBondPrice(B37,"Clean")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R50C2BondPrice,A</v>
+      </c>
+      <c r="C50" s="3" t="str">
+        <f>_xll.qlBondPrice(C37,"Clean")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R50C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="3" t="str">
+        <f>_xll.qlBondPrice(B37,"Clean")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R51C2BondPrice,A</v>
+      </c>
+      <c r="C51" s="3" t="str">
+        <f>_xll.qlBondPrice(C37,"Clean")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R51C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" s="3" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R52C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C52" s="3" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R52C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="34">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C53" s="34">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="3">
+        <v>100</v>
+      </c>
+      <c r="C54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B55" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="C55" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B56" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C56" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="37">
+        <f>_xll.qlCallableBondImpliedVolatility(B16,B51,B52,B53,B54,B55,B56)</f>
+        <v>0.40836303474006003</v>
+      </c>
+      <c r="C57" s="37">
+        <f>_xll.qlCallableBondImpliedVolatility(C16,C51,C52,C53,C54,C55,C56)</f>
+        <v>0.40812981234542117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="32" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="B51" s="3">
+      <c r="B58" s="3">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(B16,105,B34,"Actual/360","Simple","Annual",,,1000,,B36))</f>
         <v>1</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C58" s="3">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(C16,105,C34,"Actual/360","Simple","Annual",,,1000,,C36))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="32" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" s="3">
+        <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual",,B36)</f>
+        <v>71.605443884201833</v>
+      </c>
+      <c r="C59" s="3">
+        <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual",,C36)</f>
+        <v>71.605443864856298</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B52" s="3">
-        <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual",,B36)</f>
-        <v>84.698502208619104</v>
-      </c>
-      <c r="C52" s="3">
-        <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual",,C36)</f>
-        <v>84.698502208619104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
+      <c r="B60" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
+        <v>0</v>
+      </c>
+      <c r="C60" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(C16,0.3,C34,"actual/360","simple","quarterly",,C36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="3">
-        <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
-        <v>0</v>
-      </c>
-      <c r="C53" s="3">
-        <f>_xll.qlCallableBondEffectiveDuration(C16,0.3,C34,"actual/360","simple","quarterly",,C36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B54" s="3">
+      <c r="B61" s="3">
         <f>_xll.qlCallableBondEffectiveConvexity(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
         <v>0</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C61" s="3">
         <f>_xll.qlCallableBondEffectiveConvexity(C16,0.3,C34,"actual/360","simple","quarterly",,C36)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R62C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C62" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R62C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B63" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C63" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B68" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B16,B62,B63,B64,B65,B66)</f>
+        <v>68.138537120691339</v>
+      </c>
+      <c r="C68" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C16,C62,C63,C64,C65,C66)</f>
+        <v>68.151546473470646</v>
       </c>
     </row>
   </sheetData>
@@ -3619,7 +4056,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE8D14D-DD7E-4024-86F3-1C5FBF784E5F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3628,13 +4065,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B77307-DD7A-406E-AD93-A17357F921C0}">
   <dimension ref="A3:B8"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
     <col min="2" max="2" width="46" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>117</v>
       </c>
@@ -3642,7 +4079,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>118</v>
       </c>
@@ -3650,7 +4087,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>120</v>
       </c>
@@ -3659,7 +4096,7 @@
         <v>欣[test_bonds.xlsx]BondPrice!R5C2BondPrice,A</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>121</v>
       </c>
@@ -3668,7 +4105,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>122</v>
       </c>
@@ -3677,7 +4114,7 @@
         <v>CLEAN</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>123</v>
       </c>
@@ -3695,36 +4132,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8683113-FD1C-4D88-8D42-F7763B404E4F}">
   <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.5546875" customWidth="1"/>
+    <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="65" style="3" customWidth="1"/>
-    <col min="3" max="3" width="49.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" customWidth="1"/>
+    <col min="3" max="3" width="49.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
+        <v>45659</v>
       </c>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
@@ -3733,7 +4170,7 @@
       </c>
       <c r="C4" s="6"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
@@ -3742,7 +4179,7 @@
       </c>
       <c r="C5" s="6"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
@@ -3752,7 +4189,7 @@
       </c>
       <c r="C6" s="6"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
@@ -3761,7 +4198,7 @@
       </c>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>47</v>
       </c>
@@ -3770,16 +4207,16 @@
       </c>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>49</v>
       </c>
@@ -3789,7 +4226,7 @@
       </c>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="6">
         <v>103</v>
@@ -3798,7 +4235,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="6">
         <v>103</v>
@@ -3807,49 +4244,49 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="6">
         <v>103</v>
       </c>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="6">
         <v>103</v>
       </c>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="6">
         <v>102</v>
       </c>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="6">
         <v>102</v>
       </c>
       <c r="C16" s="6"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="6">
         <v>102</v>
       </c>
       <c r="C17" s="6"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="6">
         <v>102</v>
       </c>
       <c r="C18" s="6"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -3860,7 +4297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -3873,7 +4310,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -3884,7 +4321,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -3895,7 +4332,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -3908,7 +4345,7 @@
         <v>欣[test_bonds.xlsx]Bond!R23C3CashFlow,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -3916,7 +4353,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>19</v>
       </c>
@@ -3929,7 +4366,7 @@
         <v>欣[test_bonds.xlsx]Bond!R25C3Bond,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>20</v>
       </c>
@@ -3942,7 +4379,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>21</v>
       </c>
@@ -3955,7 +4392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>22</v>
       </c>
@@ -3968,7 +4405,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>23</v>
       </c>
@@ -3981,7 +4418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>24</v>
       </c>
@@ -3994,20 +4431,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="2">
         <f>_xll.qlBondSettlementDate(B25)</f>
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C31" s="2">
         <f>_xll.qlBondSettlementDate(C25)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>26</v>
       </c>
@@ -4020,7 +4457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -4033,7 +4470,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -4046,7 +4483,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -4059,7 +4496,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>30</v>
       </c>
@@ -4072,7 +4509,7 @@
         <v>欣[test_bonds.xlsx]Bond!R36C3CashFlow,A</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>57</v>
       </c>
@@ -4085,7 +4522,7 @@
         <v>欣[test_bonds.xlsx]Bond!R37C3CashFlow,A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>58</v>
       </c>
@@ -4098,7 +4535,7 @@
         <v>欣[test_bonds.xlsx]Bond!R38C3CashFlow,A</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>31</v>
       </c>
@@ -4111,7 +4548,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>32</v>
       </c>
@@ -4124,7 +4561,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>59</v>
       </c>
@@ -4137,7 +4574,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>55</v>
       </c>
@@ -4150,9 +4587,9 @@
         <v>欣[test_bonds.xlsx]Bond!R42C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B43" s="3" t="str">
         <f>_xll.qlDiscountingBondEngine(B42)</f>
@@ -4163,9 +4600,9 @@
         <v>欣[test_bonds.xlsx]Bond!R43C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B44" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B25,B43)</f>
@@ -4176,20 +4613,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B45" s="9">
         <f>_xll.qlBondCleanPrice(B25,B44)</f>
-        <v>2.9820944542826178</v>
+        <v>2.9982762319550749</v>
       </c>
       <c r="C45" s="9">
         <f>_xll.qlBondCleanPrice(C25,C44)</f>
-        <v>2.9820944542826178</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9982762319550749</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>56</v>
       </c>
@@ -4200,59 +4637,59 @@
         <v>2.9558800538580478E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B47" s="9">
         <f>_xll.qlBondCleanPrice2(B25,B46,"actual360","continuous")</f>
-        <v>2.9820944594328145</v>
+        <v>2.9982762371603138</v>
       </c>
       <c r="C47" s="9">
         <f>_xll.qlBondCleanPrice2(C25,C46,"actual360","continuous")</f>
-        <v>2.9820944594328145</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9982762371603138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B48" s="9">
         <f>_xll.qlBondDirtyPrice(B25,B44)</f>
-        <v>2.9992611209492823</v>
+        <v>2.9982762319550749</v>
       </c>
       <c r="C48" s="9">
         <f>_xll.qlBondDirtyPrice(C25,C44)</f>
-        <v>2.9992611209492823</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9982762319550749</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B49" s="9">
         <f>_xll.qlBondDirtyPrice2(B25,B46,"actual360","CONTINUOUS","annual")</f>
-        <v>2.999261126099479</v>
+        <v>2.9982762371603138</v>
       </c>
       <c r="C49" s="9">
         <f>_xll.qlBondDirtyPrice2(C25,C46,"actual360","CONTINUOUS","annual")</f>
-        <v>2.999261126099479</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9982762371603138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B50" s="9">
         <f>_xll.qlBondYield(B25,"actual360","CONTINUOUS","annual",,,B44)</f>
-        <v>2.9558799446356546E-2</v>
+        <v>2.9558799531199026E-2</v>
       </c>
       <c r="C50" s="9">
         <f>_xll.qlBondYield(C25,"actual360","CONTINUOUS","annual",,,C44)</f>
-        <v>2.9558799446356546E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9558799531199026E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>120</v>
       </c>
@@ -4265,20 +4702,20 @@
         <v>欣[test_bonds.xlsx]Bond!R51C3BondPrice,A</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B52" s="9">
         <f>_xll.qlBondYield2(B25,B51,"actual360","CONTINUOUS","annual")</f>
-        <v>3.5251441098982664E-2</v>
+        <v>2.9558799531199026E-2</v>
       </c>
       <c r="C52" s="9">
         <f>_xll.qlBondYield2(C25,C51,"actual360","CONTINUOUS","annual")</f>
-        <v>3.5251441098982664E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9558799531199026E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>54</v>
       </c>
@@ -4289,7 +4726,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>39</v>
       </c>
@@ -4302,30 +4739,30 @@
         <v>1.7166666666664776E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B55" s="9">
         <f>_xll.qlBondSettlementValue(B25,B44)</f>
-        <v>2.9992611209492819</v>
+        <v>2.9982762319550749</v>
       </c>
       <c r="C55" s="9">
         <f>_xll.qlBondSettlementValue(C25,C44)</f>
-        <v>2.9992611209492819</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9982762319550749</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B56" s="9">
         <f>_xll.qlBondSettlementValue2(B25,B45)</f>
-        <v>2.9992611209492823</v>
+        <v>2.9982762319550749</v>
       </c>
       <c r="C56" s="9">
         <f>_xll.qlBondSettlementValue2(C25,C45)</f>
-        <v>2.9992611209492823</v>
+        <v>2.9982762319550749</v>
       </c>
     </row>
   </sheetData>
@@ -4336,33 +4773,33 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0BDDB4-6035-4089-86B1-6246F3228CBC}">
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.88671875" customWidth="1"/>
-    <col min="2" max="2" width="88.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="59.33203125" style="3" customWidth="1"/>
-    <col min="4" max="7" width="11.44140625" style="3"/>
+    <col min="1" max="1" width="42.85546875" customWidth="1"/>
+    <col min="2" max="2" width="88.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" style="3" customWidth="1"/>
+    <col min="4" max="7" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4373,7 +4810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -4386,7 +4823,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4397,7 +4834,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4408,7 +4845,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -4416,7 +4853,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -4424,7 +4861,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -4432,7 +4869,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>62</v>
       </c>
@@ -4445,7 +4882,7 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R11C3ZeroCouponBond,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
@@ -4458,7 +4895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -4471,7 +4908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>22</v>
       </c>
@@ -4484,7 +4921,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -4497,7 +4934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -4510,20 +4947,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="2">
         <f>_xll.qlBondSettlementDate(B11)</f>
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C17" s="2">
         <f>_xll.qlBondSettlementDate(C11)</f>
         <v>45667</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>26</v>
       </c>
@@ -4536,7 +4973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
@@ -4549,7 +4986,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>28</v>
       </c>
@@ -4562,7 +4999,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>29</v>
       </c>
@@ -4575,7 +5012,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>30</v>
       </c>
@@ -4588,7 +5025,7 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R22C3CashFlow,A</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>57</v>
       </c>
@@ -4601,7 +5038,7 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R23C3CashFlow,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>58</v>
       </c>
@@ -4614,7 +5051,7 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R24C3CashFlow,A</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
@@ -4627,7 +5064,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>32</v>
       </c>
@@ -4640,7 +5077,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>59</v>
       </c>
@@ -4653,7 +5090,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>55</v>
       </c>
@@ -4666,9 +5103,9 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R28C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B29" s="3" t="str">
         <f>_xll.qlDiscountingBondEngine(B28)</f>
@@ -4679,9 +5116,9 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R29C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B30" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B11,B29)</f>
@@ -4692,20 +5129,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="9">
         <f>_xll.qlBondCleanPrice(B11,B30)</f>
-        <v>71.916622935265281</v>
+        <v>71.893007155387124</v>
       </c>
       <c r="C31" s="9">
         <f>_xll.qlBondCleanPrice(C11,C30)</f>
-        <v>86.299947522318348</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>86.299947522318362</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>56</v>
       </c>
@@ -4716,46 +5153,46 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B33" s="9">
         <f>_xll.qlBondCleanPrice2(B11,B32,"actual360","continuous")</f>
-        <v>71.916618245755444</v>
+        <v>71.893002462746765</v>
       </c>
       <c r="C33" s="9">
         <f>_xll.qlBondCleanPrice2(C11,C32,"actual360","continuous")</f>
         <v>86.299941894906539</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B34" s="9">
         <f>_xll.qlBondDirtyPrice(B11,B30)</f>
-        <v>71.916622935265281</v>
+        <v>71.893007155387124</v>
       </c>
       <c r="C34" s="9">
         <f>_xll.qlBondDirtyPrice(C11,C30)</f>
-        <v>86.299947522318348</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>86.299947522318362</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="9">
         <f>_xll.qlBondDirtyPrice2(B11,B32,"actual360","CONTINUOUS","annual")</f>
-        <v>71.916618245755444</v>
+        <v>71.893002462746765</v>
       </c>
       <c r="C35" s="9">
         <f>_xll.qlBondDirtyPrice2(C11,C32,"actual360","CONTINUOUS","annual")</f>
         <v>86.299941894906539</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>37</v>
       </c>
@@ -4768,7 +5205,7 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>120</v>
       </c>
@@ -4781,7 +5218,7 @@
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R37C3BondPrice,A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>38</v>
       </c>
@@ -4794,7 +5231,7 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>54</v>
       </c>
@@ -4805,7 +5242,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>39</v>
       </c>
@@ -4818,30 +5255,107 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="9">
         <f>_xll.qlBondSettlementValue(B11,B30)</f>
-        <v>71.916622935265281</v>
+        <v>71.893007155387124</v>
       </c>
       <c r="C41" s="9">
         <f>_xll.qlBondSettlementValue(C11,C30)</f>
-        <v>86.299947522318348</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+        <v>86.299947522318362</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="9">
         <f>_xll.qlBondSettlementValue2(B11,B31)</f>
-        <v>71.916622935265281</v>
+        <v>71.893007155387124</v>
       </c>
       <c r="C42" s="9">
         <f>_xll.qlBondSettlementValue2(C11,C31)</f>
-        <v>86.299947522318348</v>
+        <v>86.299947522318362</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R43C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C43" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R43C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B44" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C44" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B11,B43,B44,B45,B46,B47)</f>
+        <v>68.138537120691339</v>
+      </c>
+      <c r="C49" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C11,C43,C44,C45,C46,C47)</f>
+        <v>81.797469972073358</v>
       </c>
     </row>
   </sheetData>
@@ -4851,32 +5365,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00EB77E5-949B-439C-BFA2-575F2A710E3C}">
-  <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="59.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="126.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="114.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="126.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4887,7 +5401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -4898,7 +5412,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
@@ -4909,7 +5423,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -4920,7 +5434,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
@@ -4931,7 +5445,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -4944,7 +5458,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -4955,7 +5469,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>75</v>
       </c>
@@ -4966,7 +5480,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
@@ -4977,7 +5491,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -4988,7 +5502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -5001,8 +5515,8 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R14C3Schedule,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="3">
@@ -5012,8 +5526,8 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="40"/>
       <c r="B16" s="3">
         <v>0.05</v>
       </c>
@@ -5021,8 +5535,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="40"/>
       <c r="B17" s="3">
         <v>0.06</v>
       </c>
@@ -5030,18 +5544,18 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -5049,7 +5563,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -5057,7 +5571,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -5065,7 +5579,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -5074,7 +5588,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -5082,7 +5596,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -5091,7 +5605,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -5099,7 +5613,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -5107,7 +5621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>80</v>
       </c>
@@ -5120,7 +5634,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R27C3FixedRateBond,A</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>20</v>
       </c>
@@ -5133,7 +5647,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>21</v>
       </c>
@@ -5146,7 +5660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>22</v>
       </c>
@@ -5159,7 +5673,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>23</v>
       </c>
@@ -5172,7 +5686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -5185,20 +5699,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B33" s="2">
         <f>_xll.qlBondSettlementDate(B27)</f>
-        <v>45665</v>
+        <v>45659</v>
       </c>
       <c r="C33" s="2">
         <f>_xll.qlBondSettlementDate(C27)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>26</v>
       </c>
@@ -5211,7 +5725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>27</v>
       </c>
@@ -5224,7 +5738,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>28</v>
       </c>
@@ -5237,7 +5751,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>29</v>
       </c>
@@ -5250,7 +5764,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>30</v>
       </c>
@@ -5263,7 +5777,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R38C3CashFlow,A</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>57</v>
       </c>
@@ -5276,7 +5790,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R39C3CashFlow,A</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>58</v>
       </c>
@@ -5289,20 +5803,20 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R40C3CashFlow,A</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B41" s="3" t="str">
         <f>_xll.qlBondCalendar(B27)</f>
-        <v>Null</v>
+        <v>TARGET</v>
       </c>
       <c r="C41" s="3" t="str">
         <f>_xll.qlBondCalendar(C27)</f>
         <v>TARGET</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>32</v>
       </c>
@@ -5315,7 +5829,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>59</v>
       </c>
@@ -5328,7 +5842,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>55</v>
       </c>
@@ -5341,9 +5855,9 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R44C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B45" s="3" t="str">
         <f>_xll.qlDiscountingBondEngine(B44)</f>
@@ -5354,9 +5868,9 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R45C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B46" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B27,B45)</f>
@@ -5367,20 +5881,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B47" s="9">
         <f>_xll.qlBondCleanPrice(B27,B46)</f>
-        <v>124.40332304252402</v>
+        <v>124.34000059920736</v>
       </c>
       <c r="C47" s="9">
         <f>_xll.qlBondCleanPrice(C27,C46)</f>
-        <v>124.40127138186648</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124.38084443368287</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>56</v>
       </c>
@@ -5391,46 +5905,46 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B49" s="9">
         <f>_xll.qlBondCleanPrice2(B27,B48,"actual360","continuous")</f>
-        <v>124.40331650168764</v>
+        <v>124.33999404914331</v>
       </c>
       <c r="C49" s="9">
         <f>_xll.qlBondCleanPrice2(C27,C48,"actual360","continuous")</f>
-        <v>124.40126484069721</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124.38083788954749</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B50" s="9">
         <f>_xll.qlBondDirtyPrice(B27,B46)</f>
-        <v>124.40332304252402</v>
+        <v>124.34000059920736</v>
       </c>
       <c r="C50" s="9">
         <f>_xll.qlBondDirtyPrice(C27,C46)</f>
-        <v>124.40127138186648</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124.38084443368287</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B51" s="9">
         <f>_xll.qlBondDirtyPrice2(B27,B48,"actual360","CONTINUOUS","annual")</f>
-        <v>124.40331650168764</v>
+        <v>124.33999404914331</v>
       </c>
       <c r="C51" s="9">
         <f>_xll.qlBondDirtyPrice2(C27,C48,"actual360","CONTINUOUS","annual")</f>
-        <v>124.40126484069721</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124.38083788954749</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>37</v>
       </c>
@@ -5443,7 +5957,7 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>120</v>
       </c>
@@ -5456,7 +5970,7 @@
         <v>欣[test_bonds.xlsx]FixedRateBond!R53C3BondPrice,A</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>38</v>
       </c>
@@ -5469,7 +5983,7 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>54</v>
       </c>
@@ -5480,7 +5994,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>39</v>
       </c>
@@ -5493,30 +6007,107 @@
         <v>2.2222222222212373E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B57" s="9">
         <f>_xll.qlBondSettlementValue(B27,B46)</f>
-        <v>124.40332304252402</v>
+        <v>124.34000059920736</v>
       </c>
       <c r="C57" s="9">
         <f>_xll.qlBondSettlementValue(C27,C46)</f>
-        <v>124.40127138186648</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124.38084443368287</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B58" s="9">
         <f>_xll.qlBondSettlementValue2(B27,B47)</f>
-        <v>124.40332304252402</v>
+        <v>124.34000059920736</v>
       </c>
       <c r="C58" s="9">
         <f>_xll.qlBondSettlementValue2(C27,C47)</f>
-        <v>124.40127138186648</v>
+        <v>124.38084443368287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B59" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R59C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C59" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R59C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B60" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C60" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B65" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B27,B59,B60,B61,B62,B63)</f>
+        <v>119.08699120029004</v>
+      </c>
+      <c r="C65" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C27,C59,C60,C61,C62,C63)</f>
+        <v>119.13246891789954</v>
       </c>
     </row>
   </sheetData>
@@ -5529,32 +6120,32 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303A5445-988F-4FD7-9234-8C10A40DEB2F}">
-  <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.44140625" customWidth="1"/>
-    <col min="2" max="2" width="69.44140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="71.109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="2" width="69.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="71.140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -5565,8 +6156,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="3">
@@ -5576,8 +6167,8 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="40"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -5585,8 +6176,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="40"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -5594,7 +6185,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>73</v>
       </c>
@@ -5605,7 +6196,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
@@ -5616,7 +6207,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
@@ -5627,7 +6218,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>60</v>
       </c>
@@ -5640,7 +6231,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
@@ -5651,7 +6242,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>75</v>
       </c>
@@ -5662,7 +6253,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>77</v>
       </c>
@@ -5673,7 +6264,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>78</v>
       </c>
@@ -5684,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -5697,8 +6288,8 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R16C3Schedule,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="36" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="40" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="3">
@@ -5708,8 +6299,8 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="40"/>
       <c r="B18" s="3">
         <v>0.05</v>
       </c>
@@ -5717,8 +6308,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="40"/>
       <c r="B19" s="3">
         <v>0.06</v>
       </c>
@@ -5726,18 +6317,18 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>83</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -5745,7 +6336,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -5753,7 +6344,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -5761,7 +6352,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -5770,7 +6361,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -5778,7 +6369,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -5786,27 +6377,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="40" t="s">
         <v>87</v>
       </c>
       <c r="C27" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="36"/>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="40"/>
       <c r="C28" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="40"/>
       <c r="C29" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>85</v>
       </c>
@@ -5819,7 +6410,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R30C3AmortizingFixedRateBond,A</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>20</v>
       </c>
@@ -5832,7 +6423,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>21</v>
       </c>
@@ -5845,7 +6436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>22</v>
       </c>
@@ -5858,7 +6449,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>23</v>
       </c>
@@ -5871,7 +6462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
@@ -5884,20 +6475,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B36" s="2">
         <f>_xll.qlBondSettlementDate(B30)</f>
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C36" s="2">
         <f>_xll.qlBondSettlementDate(C30)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>26</v>
       </c>
@@ -5910,7 +6501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>27</v>
       </c>
@@ -5923,7 +6514,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>28</v>
       </c>
@@ -5936,7 +6527,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>29</v>
       </c>
@@ -5949,7 +6540,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>30</v>
       </c>
@@ -5962,7 +6553,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R41C3CashFlow,A</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>57</v>
       </c>
@@ -5975,7 +6566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>58</v>
       </c>
@@ -5988,7 +6579,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R43C3CashFlow,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>31</v>
       </c>
@@ -6001,7 +6592,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>32</v>
       </c>
@@ -6014,7 +6605,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>59</v>
       </c>
@@ -6027,7 +6618,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>55</v>
       </c>
@@ -6040,9 +6631,9 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R47C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B48" s="3" t="str">
         <f>_xll.qlDiscountingBondEngine(B47)</f>
@@ -6053,9 +6644,9 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R48C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B49" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B30,B48)</f>
@@ -6066,20 +6657,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B50" s="9">
         <f>_xll.qlBondCleanPrice(B30,B49)</f>
-        <v>116.8815996495765</v>
+        <v>116.86543332111933</v>
       </c>
       <c r="C50" s="9">
         <f>_xll.qlBondCleanPrice(C30,C49)</f>
-        <v>124.86509521653187</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124.84630729008698</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>56</v>
       </c>
@@ -6090,46 +6681,46 @@
         <v>2.9586706781387334E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B52" s="9">
         <f>_xll.qlBondCleanPrice2(B30,B51,"actual360","continuous")</f>
-        <v>116.85937778132163</v>
+        <v>116.84318252273343</v>
       </c>
       <c r="C52" s="9">
         <f>_xll.qlBondCleanPrice2(C30,C51,"actual360","continuous")</f>
-        <v>124.84124844017744</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124.82242964321487</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B53" s="9">
         <f>_xll.qlBondDirtyPrice(B30,B49)</f>
-        <v>116.90382187179871</v>
+        <v>116.86543332111933</v>
       </c>
       <c r="C53" s="9">
         <f>_xll.qlBondDirtyPrice(C30,C49)</f>
-        <v>124.88731743875408</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124.84630729008698</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B54" s="9">
         <f>_xll.qlBondDirtyPrice2(B30,B51,"actual360","CONTINUOUS","annual")</f>
-        <v>116.88160000354384</v>
+        <v>116.84318252273343</v>
       </c>
       <c r="C54" s="9">
         <f>_xll.qlBondDirtyPrice2(C30,C51,"actual360","CONTINUOUS","annual")</f>
-        <v>124.86347066239965</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124.82242964321487</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>37</v>
       </c>
@@ -6142,7 +6733,7 @@
         <v>2.9558808088302614E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
         <v>120</v>
       </c>
@@ -6155,20 +6746,20 @@
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R56C3BondPrice,A</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B57" s="9">
         <f>_xll.qlBondYield2(B30,B56,"actual360","CONTINUOUS","annual")</f>
-        <v>2.9586706781387334E-2</v>
+        <v>2.9558808088302614E-2</v>
       </c>
       <c r="C57" s="9">
         <f>_xll.qlBondYield2(C30,C56,"actual360","CONTINUOUS","annual")</f>
-        <v>2.9584804964065556E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9558808088302614E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>54</v>
       </c>
@@ -6179,7 +6770,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>39</v>
       </c>
@@ -6192,30 +6783,184 @@
         <v>2.2222222222212373E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B60" s="9">
         <f>_xll.qlBondSettlementValue(B30,B49)</f>
-        <v>175.35573280769808</v>
+        <v>175.29814998167899</v>
       </c>
       <c r="C60" s="9">
         <f>_xll.qlBondSettlementValue(C30,C49)</f>
-        <v>187.33097615813111</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+        <v>187.26946093513047</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B61" s="9">
         <f>_xll.qlBondSettlementValue2(B30,B50)</f>
-        <v>175.35573280769808</v>
+        <v>175.29814998167896</v>
       </c>
       <c r="C61" s="9">
         <f>_xll.qlBondSettlementValue2(C30,C50)</f>
-        <v>187.33097615813111</v>
+        <v>187.2694609351305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R62C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C62" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R62C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B63" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C63" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B68" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B30,B62,B63,B64,B65,B66)</f>
+        <v>113.12097995518857</v>
+      </c>
+      <c r="C68" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C30,C62,C63,C64,C65,C66)</f>
+        <v>120.82857387849862</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R69C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C69" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R69C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B70" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C70" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B75" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B30,B69,B70,B71,B72,B73)</f>
+        <v>113.12097995518857</v>
+      </c>
+      <c r="C75" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C30,C69,C70,C71,C72,C73)</f>
+        <v>120.82857387849862</v>
       </c>
     </row>
   </sheetData>
@@ -6230,32 +6975,32 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76F30CA-2F79-453E-B116-2A48310E361D}">
-  <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E72"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.44140625" customWidth="1"/>
-    <col min="2" max="2" width="72.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="73.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="45.42578125" customWidth="1"/>
+    <col min="2" max="2" width="72.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="73.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -6266,8 +7011,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>88</v>
       </c>
       <c r="B5" s="3">
@@ -6277,8 +7022,8 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="40"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -6286,8 +7031,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="40"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -6295,7 +7040,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>73</v>
       </c>
@@ -6306,7 +7051,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
@@ -6317,7 +7062,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
@@ -6328,7 +7073,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>60</v>
       </c>
@@ -6341,7 +7086,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
@@ -6352,7 +7097,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>75</v>
       </c>
@@ -6363,7 +7108,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>77</v>
       </c>
@@ -6374,7 +7119,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>78</v>
       </c>
@@ -6385,7 +7130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -6398,7 +7143,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R16C3Schedule,A</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>55</v>
       </c>
@@ -6411,7 +7156,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -6424,18 +7169,18 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R18C3Euribor,A</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>83</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -6443,7 +7188,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -6451,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>91</v>
       </c>
@@ -6459,7 +7204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>92</v>
       </c>
@@ -6467,18 +7212,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>93</v>
       </c>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>95</v>
       </c>
@@ -6486,7 +7231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>17</v>
       </c>
@@ -6494,7 +7239,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -6502,7 +7247,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -6511,7 +7256,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -6519,7 +7264,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -6527,7 +7272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -6535,7 +7280,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -6543,7 +7288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>97</v>
       </c>
@@ -6556,20 +7301,20 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R34C3AmortizingFloatingRateBond,A</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B35" s="3">
         <f>_xll.qlBondNextCouponRate(B34)</f>
-        <v>3.03480522114358E-2</v>
+        <v>3.0348052211436018E-2</v>
       </c>
       <c r="C35" s="3">
         <f>_xll.qlBondNextCouponRate(C34)</f>
-        <v>3.03480522114358E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3.0348052211436018E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>21</v>
       </c>
@@ -6582,7 +7327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>22</v>
       </c>
@@ -6595,7 +7340,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>23</v>
       </c>
@@ -6608,7 +7353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>24</v>
       </c>
@@ -6621,20 +7366,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B40" s="2">
         <f>_xll.qlBondSettlementDate(B34)</f>
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C40" s="2">
         <f>_xll.qlBondSettlementDate(C34)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>26</v>
       </c>
@@ -6647,7 +7392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>27</v>
       </c>
@@ -6660,7 +7405,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>28</v>
       </c>
@@ -6673,7 +7418,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>29</v>
       </c>
@@ -6686,7 +7431,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>30</v>
       </c>
@@ -6699,7 +7444,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R45C3CashFlow,A</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>57</v>
       </c>
@@ -6712,7 +7457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>58</v>
       </c>
@@ -6725,7 +7470,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R47C3CashFlow,A</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>31</v>
       </c>
@@ -6738,7 +7483,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>32</v>
       </c>
@@ -6751,7 +7496,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>59</v>
       </c>
@@ -6764,7 +7509,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>55</v>
       </c>
@@ -6777,9 +7522,9 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R51C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B52" s="3" t="str">
         <f>_xll.qlDiscountingBondEngine(B51)</f>
@@ -6790,9 +7535,9 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R52C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B53" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B34,B52)</f>
@@ -6803,20 +7548,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B54" s="9">
         <f>_xll.qlBondCleanPrice(B34,B53)</f>
-        <v>99.710822698691345</v>
+        <v>99.694569705127705</v>
       </c>
       <c r="C54" s="9">
         <f>_xll.qlBondCleanPrice(C34,C53)</f>
-        <v>99.710822698691345</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.694569705127705</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>56</v>
       </c>
@@ -6827,46 +7572,46 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B56" s="9">
         <f>_xll.qlBondCleanPrice2(B34,B55,"actual360","continuous")</f>
-        <v>99.710819325044866</v>
+        <v>99.694566327188411</v>
       </c>
       <c r="C56" s="9">
         <f>_xll.qlBondCleanPrice2(C34,C55,"actual360","continuous")</f>
-        <v>99.710819325044866</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.694566327188411</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B57" s="9">
         <f>_xll.qlBondDirtyPrice(B34,B53)</f>
-        <v>99.727682727697697</v>
+        <v>99.694569705127705</v>
       </c>
       <c r="C57" s="9">
         <f>_xll.qlBondDirtyPrice(C34,C53)</f>
-        <v>99.727682727697697</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.694569705127705</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B58" s="9">
         <f>_xll.qlBondDirtyPrice2(B34,B55,"actual360","CONTINUOUS","annual")</f>
-        <v>99.727679354051219</v>
+        <v>99.694566327188411</v>
       </c>
       <c r="C58" s="9">
         <f>_xll.qlBondDirtyPrice2(C34,C55,"actual360","CONTINUOUS","annual")</f>
-        <v>99.727679354051219</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.694566327188411</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>37</v>
       </c>
@@ -6879,7 +7624,7 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>120</v>
       </c>
@@ -6892,20 +7637,20 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R60C3BondPrice,A</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B61" s="9">
         <f>_xll.qlBondYield2(B34,B60,"actual360","CONTINUOUS","annual")</f>
-        <v>2.991248164176942E-2</v>
+        <v>2.9888064241409308E-2</v>
       </c>
       <c r="C61" s="9">
         <f>_xll.qlBondYield2(C34,C60,"actual360","CONTINUOUS","annual")</f>
-        <v>2.991248164176942E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>54</v>
       </c>
@@ -6916,43 +7661,120 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B63" s="9">
         <f>_xll.qlBondAccruedAmount(B34,B62)</f>
-        <v>1.6860029006353222E-2</v>
+        <v>1.6860029006353344E-2</v>
       </c>
       <c r="C63" s="9">
         <f>_xll.qlBondAccruedAmount(C34,C62)</f>
-        <v>1.6860029006353222E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1.6860029006353344E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B64" s="9">
         <f>_xll.qlBondSettlementValue(B34,B53)</f>
-        <v>149.59152409154655</v>
+        <v>149.54185455769155</v>
       </c>
       <c r="C64" s="9">
         <f>_xll.qlBondSettlementValue(C34,C53)</f>
-        <v>149.59152409154655</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+        <v>149.54185455769155</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B65" s="9">
         <f>_xll.qlBondSettlementValue2(B34,B54)</f>
-        <v>149.59152409154655</v>
+        <v>149.54185455769155</v>
       </c>
       <c r="C65" s="9">
         <f>_xll.qlBondSettlementValue2(C34,C54)</f>
-        <v>149.59152409154655</v>
+        <v>149.54185455769155</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B66" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R66C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C66" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R66C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B67" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C67" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B34,B66,B67,B68,B69,B70)</f>
+        <v>96.66855780761604</v>
+      </c>
+      <c r="C72" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C34,C66,C67,C68,C69,C70)</f>
+        <v>96.66855780761604</v>
       </c>
     </row>
   </sheetData>
@@ -6966,32 +7788,32 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05025377-E5EA-48F0-BE68-1C47A2C5C8E6}">
-  <dimension ref="A1:C62"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C69"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.33203125" customWidth="1"/>
-    <col min="2" max="2" width="67.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="73.109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="44.28515625" customWidth="1"/>
+    <col min="2" max="2" width="67.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="73.140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -7002,7 +7824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -7013,7 +7835,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
@@ -7024,7 +7846,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -7035,7 +7857,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
@@ -7046,7 +7868,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -7059,7 +7881,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -7070,7 +7892,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>75</v>
       </c>
@@ -7081,7 +7903,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
@@ -7092,7 +7914,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -7103,7 +7925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -7116,7 +7938,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R14C3Schedule,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>55</v>
       </c>
@@ -7129,7 +7951,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R15C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>89</v>
       </c>
@@ -7142,18 +7964,18 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R16C3Euribor,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -7161,7 +7983,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -7169,7 +7991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -7177,7 +7999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -7185,17 +8007,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>95</v>
       </c>
@@ -7203,7 +8025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -7211,7 +8033,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -7219,7 +8041,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -7227,7 +8049,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -7236,7 +8058,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -7244,7 +8066,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -7252,7 +8074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>98</v>
       </c>
@@ -7265,20 +8087,20 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R31C3FloatingRateBond,A</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B32" s="3">
         <f>_xll.qlBondNextCouponRate(B31)</f>
-        <v>3.03480522114358E-2</v>
+        <v>3.0348052211436018E-2</v>
       </c>
       <c r="C32" s="3">
         <f>_xll.qlBondNextCouponRate(C31)</f>
-        <v>3.03480522114358E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3.0348052211436018E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>21</v>
       </c>
@@ -7291,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>22</v>
       </c>
@@ -7304,7 +8126,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>23</v>
       </c>
@@ -7317,7 +8139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>24</v>
       </c>
@@ -7330,20 +8152,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B37" s="2">
         <f>_xll.qlBondSettlementDate(B31)</f>
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C37" s="2">
         <f>_xll.qlBondSettlementDate(C31)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>26</v>
       </c>
@@ -7356,7 +8178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>27</v>
       </c>
@@ -7369,7 +8191,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>28</v>
       </c>
@@ -7382,7 +8204,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>29</v>
       </c>
@@ -7395,7 +8217,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>30</v>
       </c>
@@ -7408,7 +8230,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R42C3CashFlow,A</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>57</v>
       </c>
@@ -7421,7 +8243,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R43C3CashFlow,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>58</v>
       </c>
@@ -7434,7 +8256,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R44C3CashFlow,A</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>31</v>
       </c>
@@ -7447,7 +8269,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>32</v>
       </c>
@@ -7460,7 +8282,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>59</v>
       </c>
@@ -7473,7 +8295,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>55</v>
       </c>
@@ -7486,9 +8308,9 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R48C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>_xll.qlDiscountingBondEngine(B48)</f>
@@ -7499,9 +8321,9 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R49C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B50" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B31,B49)</f>
@@ -7512,20 +8334,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B51" s="9">
         <f>_xll.qlBondCleanPrice(B31,B50)</f>
-        <v>99.596604611054161</v>
+        <v>99.58038954182615</v>
       </c>
       <c r="C51" s="9">
         <f>_xll.qlBondCleanPrice(C31,C50)</f>
-        <v>99.596604611054161</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.58038954182615</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>56</v>
       </c>
@@ -7536,46 +8358,46 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B53" s="9">
         <f>_xll.qlBondCleanPrice2(B31,B52,"actual360","continuous")</f>
-        <v>99.596599916978249</v>
+        <v>99.580384843902053</v>
       </c>
       <c r="C53" s="9">
         <f>_xll.qlBondCleanPrice2(C31,C52,"actual360","continuous")</f>
-        <v>99.596599916978249</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.580384843902053</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B54" s="9">
         <f>_xll.qlBondDirtyPrice(B31,B50)</f>
-        <v>99.613464640060513</v>
+        <v>99.58038954182615</v>
       </c>
       <c r="C54" s="9">
         <f>_xll.qlBondDirtyPrice(C31,C50)</f>
-        <v>99.613464640060513</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.58038954182615</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B55" s="9">
         <f>_xll.qlBondDirtyPrice2(B31,B52,"actual360","CONTINUOUS","annual")</f>
-        <v>99.613459945984602</v>
+        <v>99.580384843902053</v>
       </c>
       <c r="C55" s="9">
         <f>_xll.qlBondDirtyPrice2(C31,C52,"actual360","CONTINUOUS","annual")</f>
-        <v>99.613459945984602</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.580384843902053</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>37</v>
       </c>
@@ -7588,7 +8410,7 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>120</v>
       </c>
@@ -7601,20 +8423,20 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R57C3BondPrice,A</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B58" s="9">
         <f>_xll.qlBondYield2(B31,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>2.990561575889588E-2</v>
+        <v>2.9888064241409308E-2</v>
       </c>
       <c r="C58" s="9">
         <f>_xll.qlBondYield2(C31,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>2.990561575889588E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>54</v>
       </c>
@@ -7625,43 +8447,120 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B60" s="9">
         <f>_xll.qlBondAccruedAmount(B31,B59)</f>
-        <v>1.6860029006353222E-2</v>
+        <v>1.6860029006353344E-2</v>
       </c>
       <c r="C60" s="9">
         <f>_xll.qlBondAccruedAmount(C31,C59)</f>
-        <v>1.6860029006353222E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1.6860029006353344E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B61" s="9">
         <f>_xll.qlBondSettlementValue(B31,B50)</f>
-        <v>99.613464640060513</v>
+        <v>99.58038954182615</v>
       </c>
       <c r="C61" s="9">
         <f>_xll.qlBondSettlementValue(C31,C50)</f>
-        <v>99.613464640060513</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99.58038954182615</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B62" s="9">
         <f>_xll.qlBondSettlementValue2(B31,B51)</f>
-        <v>99.613464640060513</v>
+        <v>99.58038954182615</v>
       </c>
       <c r="C62" s="9">
         <f>_xll.qlBondSettlementValue2(C31,C51)</f>
-        <v>99.613464640060513</v>
+        <v>99.58038954182615</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B63" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]FloatingRateBond!R63C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C63" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]FloatingRateBond!R63C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B64" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C64" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B69" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B31,B63,B64,B65,B66,B67)</f>
+        <v>95.378021304374883</v>
+      </c>
+      <c r="C69" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C31,C63,C64,C65,C66,C67)</f>
+        <v>95.378021304374883</v>
       </c>
     </row>
   </sheetData>
@@ -7671,32 +8570,32 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27515A30-3B44-433D-8DBF-ACC4ED7765FD}">
-  <dimension ref="A1:C67"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C74"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.109375" customWidth="1"/>
-    <col min="2" max="2" width="58.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="46.140625" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
         <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -7707,7 +8606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -7718,7 +8617,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
@@ -7729,7 +8628,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -7740,7 +8639,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
@@ -7751,7 +8650,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -7764,7 +8663,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -7775,7 +8674,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>75</v>
       </c>
@@ -7786,7 +8685,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
@@ -7797,7 +8696,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -7808,7 +8707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -7821,7 +8720,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R14C3Schedule,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>101</v>
       </c>
@@ -7832,7 +8731,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>46</v>
       </c>
@@ -7843,7 +8742,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>14</v>
       </c>
@@ -7854,7 +8753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>103</v>
       </c>
@@ -7865,7 +8764,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>60</v>
       </c>
@@ -7878,7 +8777,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>105</v>
       </c>
@@ -7889,7 +8788,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>106</v>
       </c>
@@ -7900,7 +8799,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>107</v>
       </c>
@@ -7911,7 +8810,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>109</v>
       </c>
@@ -7924,7 +8823,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R23C3Euribor,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>110</v>
       </c>
@@ -7937,7 +8836,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R24C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>100</v>
       </c>
@@ -7950,18 +8849,18 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R25C3SwapIndex,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>67</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -7972,7 +8871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>90</v>
       </c>
@@ -7983,7 +8882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>91</v>
       </c>
@@ -7994,7 +8893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -8005,7 +8904,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>93</v>
       </c>
@@ -8016,7 +8915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>94</v>
       </c>
@@ -8027,7 +8926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -8035,7 +8934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>63</v>
       </c>
@@ -8043,7 +8942,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -8051,7 +8950,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>99</v>
       </c>
@@ -8064,7 +8963,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R36C3CmsRateBond,A</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>20</v>
       </c>
@@ -8077,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>21</v>
       </c>
@@ -8090,7 +8989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>22</v>
       </c>
@@ -8103,7 +9002,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>23</v>
       </c>
@@ -8116,7 +9015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>24</v>
       </c>
@@ -8129,20 +9028,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B42" s="2">
         <f>_xll.qlBondSettlementDate(B36)</f>
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C42" s="2">
         <f>_xll.qlBondSettlementDate(C36)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>26</v>
       </c>
@@ -8155,7 +9054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>27</v>
       </c>
@@ -8168,7 +9067,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>28</v>
       </c>
@@ -8181,7 +9080,7 @@
         <v>49682</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>29</v>
       </c>
@@ -8194,7 +9093,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>30</v>
       </c>
@@ -8207,7 +9106,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R47C3CashFlow,A</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>57</v>
       </c>
@@ -8220,7 +9119,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R48C3CashFlow,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>58</v>
       </c>
@@ -8233,7 +9132,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R49C3CashFlow,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
@@ -8246,7 +9145,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>32</v>
       </c>
@@ -8259,7 +9158,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>59</v>
       </c>
@@ -8272,7 +9171,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>55</v>
       </c>
@@ -8285,9 +9184,9 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R53C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B54" s="3" t="str">
         <f>_xll.qlDiscountingBondEngine(B53)</f>
@@ -8298,9 +9197,9 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R54C3DiscountingBondEngine,A</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B55" s="3" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B36,B54)</f>
@@ -8311,20 +9210,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B56" s="9">
         <f>_xll.qlBondCleanPrice(B36,B55)</f>
-        <v>71.653019933502407</v>
+        <v>71.629228665106581</v>
       </c>
       <c r="C56" s="9">
         <f>_xll.qlBondCleanPrice(C36,C55)</f>
-        <v>85.983623920202888</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85.955074398127891</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>56</v>
       </c>
@@ -8335,46 +9234,46 @@
         <v>2.9888064241409301E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B58" s="9">
         <f>_xll.qlBondCleanPrice2(B36,B57,"actual360","continuous")</f>
-        <v>71.653016028468784</v>
+        <v>71.629224757480401</v>
       </c>
       <c r="C58" s="9">
         <f>_xll.qlBondCleanPrice2(C36,C57,"actual360","continuous")</f>
-        <v>85.983619234162546</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85.955069708976481</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B59" s="9">
         <f>_xll.qlBondDirtyPrice(B36,B55)</f>
-        <v>71.653019933502407</v>
+        <v>71.629228665106581</v>
       </c>
       <c r="C59" s="9">
         <f>_xll.qlBondDirtyPrice(C36,C55)</f>
-        <v>85.983623920202888</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85.955074398127891</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B60" s="9">
         <f>_xll.qlBondDirtyPrice2(B36,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>71.653016028468784</v>
+        <v>71.629224757480401</v>
       </c>
       <c r="C60" s="9">
         <f>_xll.qlBondDirtyPrice2(C36,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>85.983619234162546</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85.955069708976481</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>37</v>
       </c>
@@ -8387,7 +9286,7 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>120</v>
       </c>
@@ -8400,7 +9299,7 @@
         <v>欣[test_bonds.xlsx]CmsRateBond!R62C3BondPrice,A</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>38</v>
       </c>
@@ -8413,7 +9312,7 @@
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>54</v>
       </c>
@@ -8424,7 +9323,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>39</v>
       </c>
@@ -8437,30 +9336,107 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B66" s="9">
         <f>_xll.qlBondSettlementValue(B36,B55)</f>
-        <v>71.653019933502407</v>
+        <v>71.629228665106581</v>
       </c>
       <c r="C66" s="9">
         <f>_xll.qlBondSettlementValue(C36,C55)</f>
-        <v>85.983623920202888</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85.955074398127891</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B67" s="9">
         <f>_xll.qlBondSettlementValue2(B36,B56)</f>
-        <v>71.653019933502407</v>
+        <v>71.629228665106581</v>
       </c>
       <c r="C67" s="9">
         <f>_xll.qlBondSettlementValue2(C36,C56)</f>
-        <v>85.983623920202888</v>
+        <v>85.955074398127891</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R68C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C68" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R68C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C69" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B74" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B36,B68,B69,B70,B71,B72)</f>
+        <v>68.138537120691339</v>
+      </c>
+      <c r="C74" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C36,C68,C69,C70,C71,C72)</f>
+        <v>81.766244544829618</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooktests/workbooks/test_bonds.xlsx
+++ b/tests/workbooktests/workbooks/test_bonds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210FD972-46B1-4CAB-9F2D-C79A32D0F197}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C765770E-1E17-4A42-BC55-6DEF547373F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="181">
   <si>
     <t>Bond</t>
   </si>
@@ -554,6 +554,36 @@
   </si>
   <si>
     <t>Annual</t>
+  </si>
+  <si>
+    <t>TreeCallableFixedRateBondEngine_Bond</t>
+  </si>
+  <si>
+    <t>termstruture</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>model (qlHullWhite)</t>
+  </si>
+  <si>
+    <t>time_steps</t>
+  </si>
+  <si>
+    <t>qlTreeCallableFixedRateBondEngine</t>
+  </si>
+  <si>
+    <t>TimeGrid_Values</t>
+  </si>
+  <si>
+    <t>TreeCallableFixedRateBondEngine2_Bond</t>
+  </si>
+  <si>
+    <t>time_grid</t>
   </si>
 </sst>
 </file>
@@ -563,7 +593,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -614,6 +644,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -623,7 +661,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -739,11 +777,156 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -794,22 +977,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -819,6 +986,200 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1148,18 +1509,18 @@
       <c r="B2" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="31"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="17"/>
       <c r="C3" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="112" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="19" t="s">
@@ -1267,7 +1628,9 @@
         <v>8</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="21" t="s">
+        <v>112</v>
+      </c>
       <c r="E14" s="22" t="s">
         <v>112</v>
       </c>
@@ -1277,7 +1640,9 @@
         <v>9</v>
       </c>
       <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
+      <c r="D15" s="21" t="s">
+        <v>112</v>
+      </c>
       <c r="E15" s="22" t="s">
         <v>112</v>
       </c>
@@ -1341,7 +1706,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="32" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="3">
@@ -1352,7 +1717,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
@@ -1361,7 +1726,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="3">
         <v>101</v>
       </c>
@@ -2262,12 +2627,11 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0A1FE9-B1FE-4762-AEA9-E4B3F6C519F7}">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.7109375" customWidth="1"/>
-    <col min="2" max="2" width="93.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="75.28515625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="80" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2288,937 +2652,1746 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="34">
         <v>2</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="35">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="37">
         <v>100</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="38">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="47">
         <v>45659</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="48">
         <v>45659</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="49">
         <v>48215</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="50">
         <v>48215</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="52" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="6" t="str">
+      <c r="B9" s="51" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
-      <c r="C9" s="6" t="str">
+      <c r="C9" s="52" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="52" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="52" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="52" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="6" t="b">
+      <c r="B13" s="51" t="b">
         <v>0</v>
       </c>
-      <c r="C13" s="6" t="b">
+      <c r="C13" s="52" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="3" t="str">
+      <c r="B14" s="44" t="str">
         <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R14C2Schedule,A</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="C14" s="45" t="str">
         <f>_xll.qlSchedule(C6,C7,C8,C9,C10,C11,C12,C13)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R14C3Schedule,A</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="37">
         <v>0.06</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="38">
         <v>0.03</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="40"/>
-      <c r="B16" s="3">
+      <c r="A16" s="58"/>
+      <c r="B16" s="37">
         <v>0.06</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="38">
         <v>0.03</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="40"/>
-      <c r="B17" s="3">
+      <c r="A17" s="58"/>
+      <c r="B17" s="37">
         <v>0.06</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="38">
         <v>0.03</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="38" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="38" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="37">
         <v>100</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="38">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="2">
-        <v>45665</v>
-      </c>
-      <c r="C21" s="2">
-        <v>45665</v>
+      <c r="B21" s="56">
+        <v>45659</v>
+      </c>
+      <c r="C21" s="57">
+        <v>45659</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="B22" s="2" t="str">
+      <c r="B22" s="54" t="str">
         <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R22C2BondPrice,A</v>
       </c>
-      <c r="C22" s="2" t="str">
+      <c r="C22" s="55" t="str">
         <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R22C3BondPrice,A</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="57" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="56">
         <v>46754</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="57">
         <v>46754</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="3" t="str">
+      <c r="B25" s="44" t="str">
         <f>_xll.qlCallability(B22,B23,B24)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R25C2Callability,A</v>
       </c>
-      <c r="C25" s="3" t="str">
+      <c r="C25" s="45" t="str">
         <f>_xll.qlCallability(C22,C23,C24)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R25C3Callability,A</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="38" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="3" t="str">
+      <c r="B27" s="37" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
-      <c r="C27" s="3" t="str">
+      <c r="C27" s="38" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="B28" s="37"/>
+      <c r="C28" s="38" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="3" t="b">
+      <c r="B29" s="37"/>
+      <c r="C29" s="38" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="85" t="s">
         <v>136</v>
       </c>
-      <c r="B30" s="3" t="str">
+      <c r="B30" s="83" t="str">
         <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R30C2CallableFixedRateBond,A</v>
       </c>
-      <c r="C30" s="3" t="str">
+      <c r="C30" s="84" t="str">
         <f>_xll.qlCallableFixedRateBond(C4,C5,C14,C15:C17,C18,C19,C20,C21,C25,C26,C27,C28,C29)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R30C3CallableFixedRateBond,A</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="70">
         <f>_xll.qlBondNextCouponRate(B30)</f>
         <v>0.06</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="70">
         <f>_xll.qlBondNextCouponRate(C30)</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="70">
         <f>_xll.qlBondPreviousCouponRate(B30)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="70">
         <f>_xll.qlBondPreviousCouponRate(C30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="72">
         <f>_xll.qlBondNextCashFlowDate(B30)</f>
         <v>45840</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="72">
         <f>_xll.qlBondNextCashFlowDate(C30)</f>
         <v>45840</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="72">
         <f>_xll.qlBondPreviousCashFlowDate(B30)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="72">
         <f>_xll.qlBondPreviousCashFlowDate(C30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="70">
         <f>_xll.qlBondSettlementDays(B30)</f>
         <v>2</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="70">
         <f>_xll.qlBondSettlementDays(C30)</f>
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="72">
         <f>_xll.qlBondSettlementDate(B30)</f>
-        <v>45665</v>
-      </c>
-      <c r="C36" s="2">
+        <v>45663</v>
+      </c>
+      <c r="C36" s="72">
         <f>_xll.qlBondSettlementDate(C30)</f>
-        <v>45665</v>
+        <v>45663</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="3" t="b">
+      <c r="B37" s="70" t="b">
         <f>_xll.qlBondIsTradable(B30)</f>
         <v>1</v>
       </c>
-      <c r="C37" s="3" t="b">
+      <c r="C37" s="70" t="b">
         <f>_xll.qlBondIsTradable(C30)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="72">
         <f>_xll.qlBondStartDate(B30)</f>
         <v>45659</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="72">
         <f>_xll.qlBondStartDate(C30)</f>
         <v>45659</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="72">
         <f>_xll.qlBondMaturityDate(B30)</f>
         <v>48215</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="72">
         <f>_xll.qlBondMaturityDate(C30)</f>
         <v>48215</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="72">
         <f>_xll.qlBondIssueDate(B30)</f>
-        <v>45665</v>
-      </c>
-      <c r="C40" s="2">
+        <v>45659</v>
+      </c>
+      <c r="C40" s="72">
         <f>_xll.qlBondIssueDate(C30)</f>
-        <v>45665</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="B41" s="3" t="str">
+      <c r="B41" s="70" t="str">
         <f>_xll.qlBondCashFlows(B30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R41C2CashFlow,A</v>
       </c>
-      <c r="C41" s="3" t="str">
+      <c r="C41" s="70" t="str">
         <f>_xll.qlBondCashFlows(C30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R41C3CashFlow,A</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="3" t="str">
+      <c r="B42" s="70" t="str">
         <f>_xll.qlBondRedemption(B30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R42C2CashFlow,A</v>
       </c>
-      <c r="C42" s="3" t="str">
+      <c r="C42" s="70" t="str">
         <f>_xll.qlBondRedemption(C30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R42C3CashFlow,A</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="3" t="str">
+      <c r="B43" s="70" t="str">
         <f>_xll.qlBondRedemptions(B30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R43C2CashFlow,A</v>
       </c>
-      <c r="C43" s="3" t="str">
+      <c r="C43" s="70" t="str">
         <f>_xll.qlBondRedemptions(C30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R43C3CashFlow,A</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="3" t="str">
+      <c r="B44" s="70" t="str">
         <f>_xll.qlBondCalendar(B30)</f>
         <v>TARGET</v>
       </c>
-      <c r="C44" s="3" t="str">
+      <c r="C44" s="70" t="str">
         <f>_xll.qlBondCalendar(C30)</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="70">
         <f>_xll.qlBondNotional(B30)</f>
         <v>100</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="70">
         <f>_xll.qlBondNotional(C30)</f>
         <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="70">
         <f>_xll.qlBondNotionals(B30)</f>
         <v>100</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="70">
         <f>_xll.qlBondNotionals(C30)</f>
         <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="34">
         <v>0.2</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="35">
         <v>0.2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="3" t="str">
+      <c r="B48" s="37" t="str">
         <f>_xll.qlFlatForward($B$2,0.03,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C48" s="3" t="str">
+      <c r="C48" s="38" t="str">
         <f>_xll.qlFlatForward($B$2,0.03,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="3" t="str">
+      <c r="B49" s="44" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(B47,B48)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R49C2BlackCallableFixedRateBondEngine,A</v>
       </c>
-      <c r="C49" s="3" t="str">
+      <c r="C49" s="45" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(C47,C48)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R49C3BlackCallableFixedRateBondEngine,A</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="B50" s="3" t="b">
+      <c r="B50" s="37" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B30,B49)</f>
         <v>1</v>
       </c>
-      <c r="C50" s="3" t="b">
+      <c r="C50" s="38" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(C30,C49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B51" s="33">
+      <c r="B51" s="86">
         <f>_xll.qlBondCleanPrice(B30,B50)</f>
-        <v>110.06392336774921</v>
-      </c>
-      <c r="C51" s="33">
+        <v>110.09602977203045</v>
+      </c>
+      <c r="C51" s="87">
         <f>_xll.qlBondCleanPrice(C30,C50)</f>
-        <v>99.445095445011546</v>
+        <v>99.448292731770522</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="62">
         <v>2.8928264971926201E-2</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="63">
         <v>2.8928264971926201E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="64">
         <f>_xll.qlBondCleanPrice2(B30,B52,"actual360","continuous")</f>
-        <v>119.08137817483198</v>
-      </c>
-      <c r="C53" s="9">
+        <v>119.09555910006989</v>
+      </c>
+      <c r="C53" s="65">
         <f>_xll.qlBondCleanPrice2(C30,C52,"actual360","continuous")</f>
-        <v>100.54500989207793</v>
+        <v>100.54551097389133</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="77">
         <f>_xll.qlBondDirtyPrice(B30,B50)</f>
-        <v>110.16392336774921</v>
-      </c>
-      <c r="C54" s="9">
+        <v>110.16269643869711</v>
+      </c>
+      <c r="C54" s="78">
         <f>_xll.qlBondDirtyPrice(C30,C50)</f>
-        <v>99.495095445011543</v>
+        <v>99.481626065103853</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="67">
         <f>_xll.qlBondDirtyPrice2(B30,B52,"actual360","CONTINUOUS","annual")</f>
-        <v>119.18137817483198</v>
-      </c>
-      <c r="C55" s="9">
+        <v>119.16222576673655</v>
+      </c>
+      <c r="C55" s="68">
         <f>_xll.qlBondDirtyPrice2(C30,C52,"actual360","CONTINUOUS","annual")</f>
-        <v>100.59500989207793</v>
+        <v>100.57884430722466</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="77">
         <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual",,,B50)</f>
-        <v>4.2093677997589118E-2</v>
-      </c>
-      <c r="C56" s="9">
+        <v>4.2056273937225358E-2</v>
+      </c>
+      <c r="C56" s="78">
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual",,,C50)</f>
-        <v>3.0637670373916633E-2</v>
+        <v>3.0632255029678354E-2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="9" t="str">
+      <c r="B57" s="62" t="str">
         <f>_xll.qlBondPrice(B51,"clean")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R57C2BondPrice,A</v>
       </c>
-      <c r="C57" s="9" t="str">
+      <c r="C57" s="63" t="str">
         <f>_xll.qlBondPrice(C51,"clean")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R57C3BondPrice,A</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="64">
         <f>_xll.qlBondYield2(B30,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>4.2246308316370287E-2</v>
-      </c>
-      <c r="C58" s="9">
+        <v>4.2157923221588151E-2</v>
+      </c>
+      <c r="C58" s="65">
         <f>_xll.qlBondYield2(C30,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>3.0715854406356817E-2</v>
+        <v>3.0684329366683964E-2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="54">
         <v>45667</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="55">
         <v>45667</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="64">
         <f>_xll.qlBondAccruedAmount(B30,B59)</f>
         <v>0.13333333333334085</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="65">
         <f>_xll.qlBondAccruedAmount(C30,C59)</f>
         <v>6.6666666666659324E-2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="73">
         <f>_xll.qlBondSettlementValue(B30,B50)</f>
-        <v>110.16392336774922</v>
-      </c>
-      <c r="C61" s="9">
+        <v>110.16269643869711</v>
+      </c>
+      <c r="C61" s="73">
         <f>_xll.qlBondSettlementValue(C30,C50)</f>
-        <v>99.495095445011543</v>
+        <v>99.481626065103839</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="73">
         <f>_xll.qlBondSettlementValue2(B30,B51)</f>
-        <v>110.16392336774921</v>
-      </c>
-      <c r="C62" s="9">
+        <v>110.16269643869711</v>
+      </c>
+      <c r="C62" s="73">
         <f>_xll.qlBondSettlementValue2(C30,C51)</f>
-        <v>99.495095445011543</v>
+        <v>99.481626065103853</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="74" t="s">
         <v>139</v>
       </c>
-      <c r="B63" s="3" t="str">
+      <c r="B63" s="75" t="str">
         <f>_xll.qlCallableBondCallability(B30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R63C2Callability,A</v>
       </c>
-      <c r="C63" s="3" t="str">
+      <c r="C63" s="75" t="str">
         <f>_xll.qlCallableBondCallability(C30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R63C3Callability,A</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="B64" s="3" t="str">
+      <c r="B64" s="34" t="str">
         <f>_xll.qlBondPrice(B51,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R64C2BondPrice,A</v>
       </c>
-      <c r="C64" s="3" t="str">
+      <c r="C64" s="35" t="str">
         <f>_xll.qlBondPrice(C51,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R64C3BondPrice,A</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="B65" s="3" t="str">
+      <c r="B65" s="37" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R65C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C65" s="3" t="str">
+      <c r="C65" s="38" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R65C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="B66" s="34">
+      <c r="B66" s="76">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="79">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="37">
         <v>100</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="38">
         <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="37">
         <v>0.01</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="38">
         <v>0.01</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="37">
         <v>0.5</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="38">
         <v>0.5</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="80" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="36">
+      <c r="B70" s="81">
         <f>_xll.qlCallableBondImpliedVolatility(B30,B64,B65,B66,B67,B68,B69)</f>
-        <v>0.3367870577176853</v>
-      </c>
-      <c r="C70" s="36">
+        <v>0.32447524793161092</v>
+      </c>
+      <c r="C70" s="82">
         <f>_xll.qlCallableBondImpliedVolatility(C30,C64,C65,C66,C67,C68,C69)</f>
-        <v>0.25291424428606024</v>
+        <v>0.25030192954114117</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="32" t="s">
+      <c r="A71" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="37">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(B30,105,B48,"Actual/360","Simple","Annual",,,1000,,B50))</f>
         <v>1</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="38">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(C30,105,C48,"Actual/360","Simple","Annual",,,1000,,C50))</f>
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="83">
         <f>_xll.qlCallableBondCleanPriceOAS(B30,0.3,B48,"actual/360","simple","annual",,B50)</f>
-        <v>110.008855174261</v>
-      </c>
-      <c r="C72" s="3">
+        <v>110.05931499268738</v>
+      </c>
+      <c r="C72" s="84">
         <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual",,C50)</f>
-        <v>99.395360332103436</v>
+        <v>99.415137715891774</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="66" t="s">
         <v>143</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="83">
         <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
         <v>0</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="84">
         <f>_xll.qlCallableBondEffectiveDuration(C30,0.3,C48,"actual/360","compounded","annual",,C50)</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="37">
         <f>_xll.qlCallableBondEffectiveConvexity(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
         <v>0</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="38">
         <f>_xll.qlCallableBondEffectiveConvexity(C30,0.3,C48,"actual/360","compounded","annual",,C50)</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="B75" s="9" t="str">
+      <c r="B75" s="62" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R75C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C75" s="9" t="str">
+      <c r="C75" s="63" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R75C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="77">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="78">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="77" t="s">
         <v>168</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="78" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="77" t="s">
         <v>169</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="78" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="77" t="s">
         <v>170</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="78" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
+      <c r="B80" s="77"/>
+      <c r="C80" s="78"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="3">
+      <c r="B81" s="44">
         <f>_xll.qlBondCleanPriceFromZSpread(B30,B75,B76,B77,B78,B79)</f>
-        <v>115.26309756278064</v>
-      </c>
-      <c r="C81" s="3">
+        <v>115.27440939680005</v>
+      </c>
+      <c r="C81" s="45">
         <f>_xll.qlBondCleanPriceFromZSpread(C30,C75,C76,C77,C78,C79)</f>
-        <v>97.091946053546252</v>
+        <v>97.090069430863338</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="34" t="str">
+        <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R83C2CallableFixedRateBond,A</v>
+      </c>
+      <c r="C83" s="35" t="str">
+        <f>_xll.qlCallableFixedRateBond(C4,C5,C14,C15:C17,C18,C19,C20,C21,C25)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R83C3CallableFixedRateBond,A</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="B84" s="37" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R84C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C84" s="38" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R84C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" s="37">
+        <v>0.03</v>
+      </c>
+      <c r="C85" s="38">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B86" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="C86" s="38">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B87" s="37" t="str">
+        <f>_xll.qlHullWhite(B84,B85,B86)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R87C2HullWhite,A</v>
+      </c>
+      <c r="C87" s="38" t="str">
+        <f>_xll.qlHullWhite(C84,C85,C86)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R87C3HullWhite,A</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="37">
+        <v>100</v>
+      </c>
+      <c r="C88" s="38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B89" s="37" t="str">
+        <f>_xll.qlTreeCallableFixedRateBondEngine(B87,B88)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R89C2TreeCallableFixedRateBondEngine,A</v>
+      </c>
+      <c r="C89" s="38" t="str">
+        <f>_xll.qlTreeCallableFixedRateBondEngine(C87,C88)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R89C3TreeCallableFixedRateBondEngine,A</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B90" s="37" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B83,B89)</f>
+        <v>1</v>
+      </c>
+      <c r="C90" s="38" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C83,C89)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B91" s="44">
+        <f>_xll.qlBondCleanPrice(B83,B90)</f>
+        <v>113.36825228071841</v>
+      </c>
+      <c r="C91" s="45">
+        <f>_xll.qlBondCleanPrice(C83,C90)</f>
+        <v>104.15316507210984</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B92" s="34" t="str">
+        <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R92C2CallableFixedRateBond,A</v>
+      </c>
+      <c r="C92" s="35" t="str">
+        <f>_xll.qlCallableFixedRateBond(C4,C5,C14,C15:C17,C18,C19,C20,C21,C25)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R92C3CallableFixedRateBond,A</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="B93" s="37" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R93C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C93" s="38" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R93C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B94" s="37">
+        <v>0.03</v>
+      </c>
+      <c r="C94" s="38">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B95" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="C95" s="38">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B96" s="37" t="str">
+        <f>_xll.qlHullWhite(B93,B94,B95)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R96C2HullWhite,A</v>
+      </c>
+      <c r="C96" s="38" t="str">
+        <f>_xll.qlHullWhite(C93,C94,C95)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R96C3HullWhite,A</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="B97" s="37" t="str">
+        <f>_xll.qlTimeGridFromTimes(B104:B219)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R97C2TimeGrid,A</v>
+      </c>
+      <c r="C97" s="38" t="str">
+        <f>_xll.qlTimeGridFromTimes(B104:B219)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R97C3TimeGrid,A</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B98" s="37" t="str">
+        <f>_xll.qlTreeCallableFixedRateBondEngine2(B96,B97)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R98C2TreeCallableFixedRateBondEngine,A</v>
+      </c>
+      <c r="C98" s="38" t="str">
+        <f>_xll.qlTreeCallableFixedRateBondEngine2(C96,C97)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R98C3TreeCallableFixedRateBondEngine,A</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B99" s="37" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B92,B98)</f>
+        <v>1</v>
+      </c>
+      <c r="C99" s="38" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C92,C98)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100" s="44">
+        <f>_xll.qlBondCleanPrice(B92,B99)</f>
+        <v>113.36581391762972</v>
+      </c>
+      <c r="C100" s="45">
+        <f>_xll.qlBondCleanPrice(C92,C99)</f>
+        <v>104.21047805357765</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>178</v>
+      </c>
+      <c r="B104" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B105" s="3">
+        <v>0.49589041095890402</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B106" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="3">
+        <v>1.4958904109589</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="3">
+        <v>2.0054794520547898</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B109" s="3">
+        <v>2.4958904109589</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B110" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B111" s="3">
+        <v>3.0027397260273898</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B112" s="3">
+        <v>3.5013698630136898</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="3">
+        <v>4.0027397260273903</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="3">
+        <v>4.4986301369863</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="3">
+        <v>5.0027397260273903</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="3">
+        <v>5.4986301369863</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="3">
+        <v>6.0027397260273903</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="3">
+        <v>6.4986301369863</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="3">
+        <v>7.0027397260273903</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="3">
+        <v>7.0077397260273901</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="3">
+        <v>7.01273972602739</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="3">
+        <v>7.0177397260273899</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="3">
+        <v>7.0227397260273898</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="3">
+        <v>7.0277397260273897</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="3">
+        <v>7.0327397260273896</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="3">
+        <v>7.0377397260273904</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="3">
+        <v>7.0427397260273903</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="3">
+        <v>7.0477397260273902</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="3">
+        <v>7.0527397260273901</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="3">
+        <v>7.05773972602739</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="3">
+        <v>7.0627397260273899</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="3">
+        <v>7.0677397260273898</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="3">
+        <v>7.0727397260273897</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="3">
+        <v>7.0777397260273904</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="3">
+        <v>7.0827397260273903</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="3">
+        <v>7.0877397260273902</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="3">
+        <v>7.0927397260273901</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="3">
+        <v>7.09773972602739</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="3">
+        <v>7.1027397260273899</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="3">
+        <v>7.1077397260273898</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="3">
+        <v>7.1127397260273897</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="3">
+        <v>7.1177397260273896</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="3">
+        <v>7.1227397260273904</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="3">
+        <v>7.1277397260273903</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="3">
+        <v>7.1327397260273901</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="3">
+        <v>7.13773972602739</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="3">
+        <v>7.1427397260273899</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="3">
+        <v>7.1477397260273898</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="3">
+        <v>7.1527397260273897</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="3">
+        <v>7.1577397260273896</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="3">
+        <v>7.1627397260273904</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" s="3">
+        <v>7.1677397260273903</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B153" s="3">
+        <v>7.1727397260273902</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="3">
+        <v>7.1777397260273901</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155" s="3">
+        <v>7.18273972602739</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="3">
+        <v>7.1877397260273899</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="3">
+        <v>7.1927397260273898</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" s="3">
+        <v>7.1977397260273897</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="3">
+        <v>7.2027397260273904</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" s="3">
+        <v>7.2077397260273903</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="3">
+        <v>7.2127397260273902</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="3">
+        <v>7.2177397260273901</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" s="3">
+        <v>7.22273972602739</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="3">
+        <v>7.2277397260273899</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="3">
+        <v>7.2327397260273898</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="3">
+        <v>7.2377397260273897</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="3">
+        <v>7.2427397260273896</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="3">
+        <v>7.2477397260273904</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="3">
+        <v>7.2527397260273903</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" s="3">
+        <v>7.2577397260273901</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="3">
+        <v>7.26273972602739</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="3">
+        <v>7.2677397260273899</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" s="3">
+        <v>7.2727397260273898</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B174" s="3">
+        <v>7.2777397260273897</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B175" s="3">
+        <v>7.2827397260273896</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B176" s="3">
+        <v>7.2877397260273904</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B177" s="3">
+        <v>7.2927397260273903</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B178" s="3">
+        <v>7.2977397260273902</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B179" s="3">
+        <v>7.3027397260273901</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" s="3">
+        <v>7.30773972602739</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B181" s="3">
+        <v>7.3127397260273899</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B182" s="3">
+        <v>7.3177397260273898</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B183" s="3">
+        <v>7.3227397260273897</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B184" s="3">
+        <v>7.3277397260273904</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B185" s="3">
+        <v>7.3327397260273903</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B186" s="3">
+        <v>7.3377397260273902</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B187" s="3">
+        <v>7.3427397260273901</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B188" s="3">
+        <v>7.34773972602739</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B189" s="3">
+        <v>7.3527397260273899</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B190" s="3">
+        <v>7.3577397260273898</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" s="3">
+        <v>7.3627397260273897</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" s="3">
+        <v>7.3677397260273896</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="3">
+        <v>7.3727397260273904</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B194" s="3">
+        <v>7.3777397260273903</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="3">
+        <v>7.3827397260273901</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="3">
+        <v>7.38773972602739</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" s="3">
+        <v>7.3927397260273899</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" s="3">
+        <v>7.3977397260273898</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B199" s="3">
+        <v>7.4027397260273897</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" s="3">
+        <v>7.4077397260273896</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B201" s="3">
+        <v>7.4127397260273904</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="3">
+        <v>7.4177397260273903</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B203" s="3">
+        <v>7.4227397260273902</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B204" s="3">
+        <v>0.42773972602739702</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B205" s="3">
+        <v>7.43273972602739</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B206" s="3">
+        <v>7.4377397260273899</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B207" s="3">
+        <v>7.4427397260273898</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B208" s="3">
+        <v>7.4477397260273897</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B209" s="3">
+        <v>7.4527397260273904</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B210" s="3">
+        <v>7.4577397260273903</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B211" s="3">
+        <v>7.4627397260273902</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B212" s="3">
+        <v>7.4677397260273901</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B213" s="3">
+        <v>7.47273972602739</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B214" s="3">
+        <v>7.4777397260273899</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B215" s="3">
+        <v>7.4827397260273898</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B216" s="3">
+        <v>7.4877397260273897</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B217" s="3">
+        <v>7.4927397260273896</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B218" s="3">
+        <v>7.4977397260273904</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B219" s="3">
+        <v>7.5027397260273903</v>
       </c>
     </row>
   </sheetData>
@@ -3232,12 +4405,11 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4EF9C2-FD4D-4E7F-8154-C8E782972C6B}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.140625" customWidth="1"/>
-    <col min="2" max="2" width="89.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="73.28515625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="82" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3258,793 +4430,1603 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="94">
         <v>2</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="95">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="96">
         <v>100</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="97">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="3" t="str">
+      <c r="B6" s="96" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
-      <c r="C6" s="3" t="str">
+      <c r="C6" s="97" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2">
-        <v>49682</v>
-      </c>
-      <c r="C7" s="2">
-        <v>49682</v>
+      <c r="B7" s="98">
+        <v>48215</v>
+      </c>
+      <c r="C7" s="99">
+        <v>48215</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="96" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="97" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="96"/>
+      <c r="C9" s="97" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="3">
+      <c r="B10" s="96"/>
+      <c r="C10" s="97">
         <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="2">
-        <v>45665</v>
+      <c r="B11" s="96"/>
+      <c r="C11" s="99">
+        <v>45659</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="B12" s="2" t="str">
+      <c r="B12" s="100" t="str">
         <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C2BondPrice,A</v>
       </c>
-      <c r="C12" s="2" t="str">
+      <c r="C12" s="101" t="str">
         <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C3BondPrice,A</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="98" t="s">
         <v>161</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="99" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="98">
         <v>46754</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="99">
         <v>46754</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="93" t="s">
         <v>133</v>
       </c>
-      <c r="B15" s="3" t="str">
+      <c r="B15" s="102" t="str">
         <f>_xll.qlCallability(B12,B13,B14)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C2Callability,A</v>
       </c>
-      <c r="C15" s="3" t="str">
+      <c r="C15" s="103" t="str">
         <f>_xll.qlCallability(C12,C13,C14)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C3Callability,A</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="69" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="3" t="str">
+      <c r="B16" s="104" t="str">
         <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C2CallableZeroCouponBond,A</v>
       </c>
-      <c r="C16" s="3" t="str">
+      <c r="C16" s="104" t="str">
         <f>_xll.qlCallableZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,C11,C15)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C3CallableZeroCouponBond,A</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3">
-        <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036",_xll.qlBondNextCouponRate(B16))</f>
+      <c r="B17" s="105">
+        <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 2nd, 2032",_xll.qlBondNextCouponRate(B16))</f>
         <v>1</v>
       </c>
-      <c r="C17" s="3">
-        <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036",_xll.qlBondNextCouponRate(C16))</f>
+      <c r="C17" s="35">
+        <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 2nd, 2032",_xll.qlBondNextCouponRate(C16))</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="109">
         <f>_xll.qlBondPreviousCouponRate(B16)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="84">
         <f>_xll.qlBondPreviousCouponRate(C16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="107">
         <f>_xll.qlBondNextCashFlowDate(B16)</f>
-        <v>49682</v>
-      </c>
-      <c r="C19" s="2">
+        <v>48215</v>
+      </c>
+      <c r="C19" s="57">
         <f>_xll.qlBondNextCashFlowDate(C16)</f>
-        <v>49682</v>
+        <v>48215</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="110">
         <f>_xll.qlBondPreviousCashFlowDate(B16)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="111">
         <f>_xll.qlBondPreviousCashFlowDate(C16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="106">
         <f>_xll.qlBondSettlementDays(B16)</f>
         <v>2</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="38">
         <f>_xll.qlBondSettlementDays(C16)</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="110">
         <f>_xll.qlBondSettlementDate(B16)</f>
         <v>45663</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="111">
         <f>_xll.qlBondSettlementDate(C16)</f>
-        <v>45665</v>
+        <v>45663</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3" t="b">
+      <c r="B23" s="106" t="b">
         <f>_xll.qlBondIsTradable(B16)</f>
         <v>1</v>
       </c>
-      <c r="C23" s="3" t="b">
+      <c r="C23" s="38" t="b">
         <f>_xll.qlBondIsTradable(C16)</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="110">
         <f>_xll.qlBondStartDate(B16)</f>
-        <v>49682</v>
-      </c>
-      <c r="C24" s="2">
+        <v>48215</v>
+      </c>
+      <c r="C24" s="111">
         <f>_xll.qlBondStartDate(C16)</f>
-        <v>49682</v>
+        <v>48215</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="107">
         <f>_xll.qlBondMaturityDate(B16)</f>
-        <v>49682</v>
-      </c>
-      <c r="C25" s="2">
+        <v>48215</v>
+      </c>
+      <c r="C25" s="57">
         <f>_xll.qlBondMaturityDate(C16)</f>
-        <v>49682</v>
+        <v>48215</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="110">
         <f>_xll.qlBondIssueDate(B16)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="111">
         <f>_xll.qlBondIssueDate(C16)</f>
-        <v>45665</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3" t="str">
+      <c r="B27" s="106" t="str">
         <f>_xll.qlBondCashFlows(B16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C2CashFlow,A</v>
       </c>
-      <c r="C27" s="3" t="str">
+      <c r="C27" s="38" t="str">
         <f>_xll.qlBondCashFlows(C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C3CashFlow,A</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="3" t="str">
+      <c r="B28" s="109" t="str">
         <f>_xll.qlBondRedemption(B16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C2CashFlow,A</v>
       </c>
-      <c r="C28" s="3" t="str">
+      <c r="C28" s="84" t="str">
         <f>_xll.qlBondRedemption(C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C3CashFlow,A</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="3" t="str">
+      <c r="B29" s="106" t="str">
         <f>_xll.qlBondRedemptions(B16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C2CashFlow,A</v>
       </c>
-      <c r="C29" s="3" t="str">
+      <c r="C29" s="38" t="str">
         <f>_xll.qlBondRedemptions(C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C3CashFlow,A</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="3" t="str">
+      <c r="B30" s="109" t="str">
         <f>_xll.qlBondCalendar(B16)</f>
         <v>TARGET</v>
       </c>
-      <c r="C30" s="3" t="str">
+      <c r="C30" s="84" t="str">
         <f>_xll.qlBondCalendar(C16)</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="109">
         <f>_xll.qlBondNotional(B16)</f>
         <v>100</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="84">
         <f>_xll.qlBondNotional(C16)</f>
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="108">
         <f>_xll.qlBondNotionals(B16)</f>
         <v>100</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="45">
         <f>_xll.qlBondNotionals(C16)</f>
         <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="37">
         <v>0.15</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="38">
         <v>0.15</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="3" t="str">
+      <c r="B34" s="37" t="str">
         <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C34" s="3" t="str">
+      <c r="C34" s="38" t="str">
         <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="3" t="str">
+      <c r="B35" s="44" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(B33,B34)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R35C2BlackCallableFixedRateBondEngine,A</v>
       </c>
-      <c r="C35" s="3" t="str">
+      <c r="C35" s="45" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(C33,C34)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R35C3BlackCallableFixedRateBondEngine,A</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="3" t="b">
+      <c r="B36" s="37" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B16,B35)</f>
         <v>1</v>
       </c>
-      <c r="C36" s="3" t="b">
+      <c r="C36" s="38" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(C16,C35)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="77">
         <f>_xll.qlBondCleanPrice(B16,B36)</f>
-        <v>71.629227252608828</v>
-      </c>
-      <c r="C37" s="9">
+        <v>80.906733580822063</v>
+      </c>
+      <c r="C37" s="78">
         <f>_xll.qlBondCleanPrice(C16,C36)</f>
-        <v>71.641121879613067</v>
+        <v>80.906733580822063</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="62">
         <v>2.9888064241409308E-2</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="63">
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="64">
         <f>_xll.qlBondCleanPrice2(B16,B38,"actual360","continuous")</f>
-        <v>71.629224757480401</v>
-      </c>
-      <c r="C39" s="9">
+        <v>80.906730788838317</v>
+      </c>
+      <c r="C39" s="65">
         <f>_xll.qlBondCleanPrice2(C16,C38,"actual360","continuous")</f>
-        <v>71.641119405370375</v>
+        <v>80.906730788838317</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="77">
         <f>_xll.qlBondDirtyPrice(B16,B36)</f>
-        <v>71.629227252608828</v>
-      </c>
-      <c r="C40" s="9">
+        <v>80.906733580822063</v>
+      </c>
+      <c r="C40" s="78">
         <f>_xll.qlBondDirtyPrice(C16,C36)</f>
-        <v>71.641121879613067</v>
+        <v>80.906733580822063</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="67">
         <f>_xll.qlBondDirtyPrice2(B16,B38,"actual360","CONTINUOUS","annual")</f>
-        <v>71.629224757480401</v>
-      </c>
-      <c r="C41" s="9">
+        <v>80.906730788838317</v>
+      </c>
+      <c r="C41" s="68">
         <f>_xll.qlBondDirtyPrice2(C16,C38,"actual360","CONTINUOUS","annual")</f>
-        <v>71.641119405370375</v>
+        <v>80.906730788838317</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="77">
         <f>_xll.qlBondYield(B16,"actual360","CONTINUOUS","annual",,,B36)</f>
         <v>2.9888064241409308E-2</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="78">
         <f>_xll.qlBondYield(C16,"actual360","CONTINUOUS","annual",,,C36)</f>
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="B43" s="9" t="str">
+      <c r="B43" s="62" t="str">
         <f>_xll.qlBondPrice(B37,"clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C2BondPrice,A</v>
       </c>
-      <c r="C43" s="9" t="str">
+      <c r="C43" s="63" t="str">
         <f>_xll.qlBondPrice(C37,"clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C3BondPrice,A</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="64">
         <f>_xll.qlBondYield2(B16,B43,"actual360","CONTINUOUS","annual")</f>
         <v>2.9888064241409308E-2</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="65">
         <f>_xll.qlBondYield2(C16,C43,"actual360","CONTINUOUS","annual")</f>
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="54">
         <v>45667</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="55">
         <v>45667</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="64">
         <f>_xll.qlBondAccruedAmount(B16,B45)</f>
         <v>0</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="65">
         <f>_xll.qlBondAccruedAmount(C16,C45)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="67">
         <f>_xll.qlBondSettlementValue(B16,B36)</f>
-        <v>71.629227252608828</v>
-      </c>
-      <c r="C47" s="9">
+        <v>80.906733580822063</v>
+      </c>
+      <c r="C47" s="68">
         <f>_xll.qlBondSettlementValue(C16,C36)</f>
-        <v>71.641121879613067</v>
+        <v>80.906733580822063</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="77">
         <f>_xll.qlBondSettlementValue2(B16,B37)</f>
-        <v>71.629227252608828</v>
-      </c>
-      <c r="C48" s="9">
+        <v>80.906733580822063</v>
+      </c>
+      <c r="C48" s="78">
         <f>_xll.qlBondSettlementValue2(C16,C37)</f>
-        <v>71.641121879613067</v>
+        <v>80.906733580822063</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="B49" s="3" t="str">
+      <c r="B49" s="37" t="str">
         <f>_xll.qlCallableBondCallability(B16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C2Callability,A</v>
       </c>
-      <c r="C49" s="3" t="str">
+      <c r="C49" s="38" t="str">
         <f>_xll.qlCallableBondCallability(C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C3Callability,A</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="B50" s="3" t="str">
+      <c r="B50" s="34" t="str">
         <f>_xll.qlBondPrice(B37,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R50C2BondPrice,A</v>
       </c>
-      <c r="C50" s="3" t="str">
+      <c r="C50" s="35" t="str">
         <f>_xll.qlBondPrice(C37,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R50C3BondPrice,A</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="B51" s="3" t="str">
+      <c r="B51" s="37" t="str">
         <f>_xll.qlBondPrice(B37,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R51C2BondPrice,A</v>
       </c>
-      <c r="C51" s="3" t="str">
+      <c r="C51" s="38" t="str">
         <f>_xll.qlBondPrice(C37,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R51C3BondPrice,A</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="B52" s="3" t="str">
+      <c r="B52" s="37" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R52C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C52" s="3" t="str">
+      <c r="C52" s="38" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R52C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="B53" s="34">
+      <c r="B53" s="76">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="79">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="37">
         <v>100</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="38">
         <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="37">
         <v>0.01</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="38">
         <v>0.01</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="37">
         <v>0.5</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="38">
         <v>0.5</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="80" t="s">
         <v>140</v>
       </c>
-      <c r="B57" s="37">
+      <c r="B57" s="90">
         <f>_xll.qlCallableBondImpliedVolatility(B16,B51,B52,B53,B54,B55,B56)</f>
-        <v>0.40836303474006003</v>
-      </c>
-      <c r="C57" s="37">
+        <v>0.49070370787832679</v>
+      </c>
+      <c r="C57" s="91">
         <f>_xll.qlCallableBondImpliedVolatility(C16,C51,C52,C53,C54,C55,C56)</f>
-        <v>0.40812981234542117</v>
+        <v>0.49070370787832679</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="32" t="s">
+      <c r="A58" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="37">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(B16,105,B34,"Actual/360","Simple","Annual",,,1000,,B36))</f>
         <v>1</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="38">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(C16,105,C34,"Actual/360","Simple","Annual",,,1000,,C36))</f>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="32" t="s">
+      <c r="A59" s="92" t="s">
         <v>142</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="83">
         <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual",,B36)</f>
-        <v>71.605443884201833</v>
-      </c>
-      <c r="C59" s="3">
+        <v>80.879869761049534</v>
+      </c>
+      <c r="C59" s="84">
         <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual",,C36)</f>
-        <v>71.605443864856298</v>
+        <v>80.879869761049534</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="37">
         <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
         <v>0</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="38">
         <f>_xll.qlCallableBondEffectiveDuration(C16,0.3,C34,"actual/360","simple","quarterly",,C36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="66" t="s">
         <v>144</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="83">
         <f>_xll.qlCallableBondEffectiveConvexity(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
         <v>0</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="84">
         <f>_xll.qlCallableBondEffectiveConvexity(C16,0.3,C34,"actual/360","simple","quarterly",,C36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="B62" s="9" t="str">
+      <c r="B62" s="62" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R62C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C62" s="9" t="str">
+      <c r="C62" s="63" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R62C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="77">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C63" s="78">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="77" t="s">
         <v>168</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="78" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="77" t="s">
         <v>169</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="78" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="77" t="s">
         <v>170</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="78" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
+      <c r="B67" s="77"/>
+      <c r="C67" s="78"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="44">
         <f>_xll.qlBondCleanPriceFromZSpread(B16,B62,B63,B64,B65,B66)</f>
-        <v>68.138537120691339</v>
-      </c>
-      <c r="C68" s="3">
+        <v>78.380336922103126</v>
+      </c>
+      <c r="C68" s="45">
         <f>_xll.qlBondCleanPriceFromZSpread(C16,C62,C63,C64,C65,C66)</f>
-        <v>68.151546473470646</v>
+        <v>78.380336922103126</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B70" s="34" t="str">
+        <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R70C2CallableZeroCouponBond,A</v>
+      </c>
+      <c r="C70" s="35" t="str">
+        <f>_xll.qlCallableZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,C11,C15)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R70C3CallableZeroCouponBond,A</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="B71" s="37" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R71C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C71" s="38" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R71C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B72" s="37">
+        <v>0.03</v>
+      </c>
+      <c r="C72" s="38">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B73" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="C73" s="38">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B74" s="37" t="str">
+        <f>_xll.qlHullWhite(B71,B72,B73)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R74C2HullWhite,A</v>
+      </c>
+      <c r="C74" s="38" t="str">
+        <f>_xll.qlHullWhite(C71,C72,C73)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R74C3HullWhite,A</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" s="37">
+        <v>100</v>
+      </c>
+      <c r="C75" s="38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B76" s="37" t="str">
+        <f>_xll.qlTreeCallableFixedRateBondEngine(B74,B75)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R76C2TreeCallableFixedRateBondEngine,A</v>
+      </c>
+      <c r="C76" s="38" t="str">
+        <f>_xll.qlTreeCallableFixedRateBondEngine(C74,C75)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R76C3TreeCallableFixedRateBondEngine,A</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" s="37" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B70,B76)</f>
+        <v>1</v>
+      </c>
+      <c r="C77" s="38" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C70,C76)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B78" s="44">
+        <f>_xll.qlBondCleanPrice(B70,B77)</f>
+        <v>86.90746669939648</v>
+      </c>
+      <c r="C78" s="45">
+        <f>_xll.qlBondCleanPrice(C70,C77)</f>
+        <v>86.90746669939648</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" s="34" t="str">
+        <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R79C2CallableZeroCouponBond,A</v>
+      </c>
+      <c r="C79" s="35" t="str">
+        <f>_xll.qlCallableZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,C11,C15)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R79C3CallableZeroCouponBond,A</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="B80" s="37" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R80C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C80" s="38" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R80C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B81" s="37">
+        <v>0.03</v>
+      </c>
+      <c r="C81" s="38">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B82" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="C82" s="38">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B83" s="37" t="str">
+        <f>_xll.qlHullWhite(B80,B81,B82)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R83C2HullWhite,A</v>
+      </c>
+      <c r="C83" s="38" t="str">
+        <f>_xll.qlHullWhite(C80,C81,C82)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R83C3HullWhite,A</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="B84" s="37" t="str">
+        <f>_xll.qlTimeGridFromTimes(B91:B206)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R84C2TimeGrid,A</v>
+      </c>
+      <c r="C84" s="38" t="str">
+        <f>_xll.qlTimeGridFromTimes(B91:B206)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R84C3TimeGrid,A</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B85" s="37" t="str">
+        <f>_xll.qlTreeCallableFixedRateBondEngine2(B83,B84)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R85C2TreeCallableFixedRateBondEngine,A</v>
+      </c>
+      <c r="C85" s="38" t="str">
+        <f>_xll.qlTreeCallableFixedRateBondEngine2(C83,C84)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R85C3TreeCallableFixedRateBondEngine,A</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B86" s="37" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B79,B85)</f>
+        <v>1</v>
+      </c>
+      <c r="C86" s="38" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C79,C85)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B87" s="44">
+        <f>_xll.qlBondCleanPrice(B79,B86)</f>
+        <v>86.905812107181106</v>
+      </c>
+      <c r="C87" s="45">
+        <f>_xll.qlBondCleanPrice(C79,C86)</f>
+        <v>86.905812107181106</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>178</v>
+      </c>
+      <c r="B91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B92" s="3">
+        <v>0.49589041095890402</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B94" s="3">
+        <v>1.4958904109589</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B95" s="3">
+        <v>2.0054794520547898</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B96" s="3">
+        <v>2.4958904109589</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="3">
+        <v>3.0027397260273898</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="3">
+        <v>3.5013698630136898</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="3">
+        <v>4.0027397260273903</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="3">
+        <v>4.4986301369863</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="3">
+        <v>5.0027397260273903</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="3">
+        <v>5.4986301369863</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="3">
+        <v>6.0027397260273903</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="3">
+        <v>6.4986301369863</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="3">
+        <v>7.0027397260273903</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="3">
+        <v>7.0077397260273901</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="3">
+        <v>7.01273972602739</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="3">
+        <v>7.0177397260273899</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="3">
+        <v>7.0227397260273898</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="3">
+        <v>7.0277397260273897</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="3">
+        <v>7.0327397260273896</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="3">
+        <v>7.0377397260273904</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="3">
+        <v>7.0427397260273903</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="3">
+        <v>7.0477397260273902</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="3">
+        <v>7.0527397260273901</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="3">
+        <v>7.05773972602739</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="3">
+        <v>7.0627397260273899</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="3">
+        <v>7.0677397260273898</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="3">
+        <v>7.0727397260273897</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="3">
+        <v>7.0777397260273904</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="3">
+        <v>7.0827397260273903</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="3">
+        <v>7.0877397260273902</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="3">
+        <v>7.0927397260273901</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="3">
+        <v>7.09773972602739</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="3">
+        <v>7.1027397260273899</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="3">
+        <v>7.1077397260273898</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="3">
+        <v>7.1127397260273897</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="3">
+        <v>7.1177397260273896</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="3">
+        <v>7.1227397260273904</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="3">
+        <v>7.1277397260273903</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="3">
+        <v>7.1327397260273901</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="3">
+        <v>7.13773972602739</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="3">
+        <v>7.1427397260273899</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="3">
+        <v>7.1477397260273898</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="3">
+        <v>7.1527397260273897</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="3">
+        <v>7.1577397260273896</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="3">
+        <v>7.1627397260273904</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="3">
+        <v>7.1677397260273903</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="3">
+        <v>7.1727397260273902</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="3">
+        <v>7.1777397260273901</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="3">
+        <v>7.18273972602739</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="3">
+        <v>7.1877397260273899</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="3">
+        <v>7.1927397260273898</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="3">
+        <v>7.1977397260273897</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="3">
+        <v>7.2027397260273904</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="3">
+        <v>7.2077397260273903</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="3">
+        <v>7.2127397260273902</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="3">
+        <v>7.2177397260273901</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="3">
+        <v>7.22273972602739</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="3">
+        <v>7.2277397260273899</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" s="3">
+        <v>7.2327397260273898</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B153" s="3">
+        <v>7.2377397260273897</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="3">
+        <v>7.2427397260273896</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155" s="3">
+        <v>7.2477397260273904</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="3">
+        <v>7.2527397260273903</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="3">
+        <v>7.2577397260273901</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" s="3">
+        <v>7.26273972602739</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="3">
+        <v>7.2677397260273899</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" s="3">
+        <v>7.2727397260273898</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="3">
+        <v>7.2777397260273897</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="3">
+        <v>7.2827397260273896</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" s="3">
+        <v>7.2877397260273904</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="3">
+        <v>7.2927397260273903</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="3">
+        <v>7.2977397260273902</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="3">
+        <v>7.3027397260273901</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="3">
+        <v>7.30773972602739</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="3">
+        <v>7.3127397260273899</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="3">
+        <v>7.3177397260273898</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" s="3">
+        <v>7.3227397260273897</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="3">
+        <v>7.3277397260273904</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="3">
+        <v>7.3327397260273903</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" s="3">
+        <v>7.3377397260273902</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B174" s="3">
+        <v>7.3427397260273901</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B175" s="3">
+        <v>7.34773972602739</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B176" s="3">
+        <v>7.3527397260273899</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B177" s="3">
+        <v>7.3577397260273898</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B178" s="3">
+        <v>7.3627397260273897</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B179" s="3">
+        <v>7.3677397260273896</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" s="3">
+        <v>7.3727397260273904</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B181" s="3">
+        <v>7.3777397260273903</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B182" s="3">
+        <v>7.3827397260273901</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B183" s="3">
+        <v>7.38773972602739</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B184" s="3">
+        <v>7.3927397260273899</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B185" s="3">
+        <v>7.3977397260273898</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B186" s="3">
+        <v>7.4027397260273897</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B187" s="3">
+        <v>7.4077397260273896</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B188" s="3">
+        <v>7.4127397260273904</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B189" s="3">
+        <v>7.4177397260273903</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B190" s="3">
+        <v>7.4227397260273902</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" s="3">
+        <v>0.42773972602739702</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" s="3">
+        <v>7.43273972602739</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="3">
+        <v>7.4377397260273899</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B194" s="3">
+        <v>7.4427397260273898</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="3">
+        <v>7.4477397260273897</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="3">
+        <v>7.4527397260273904</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" s="3">
+        <v>7.4577397260273903</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" s="3">
+        <v>7.4627397260273902</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B199" s="3">
+        <v>7.4677397260273901</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" s="3">
+        <v>7.47273972602739</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B201" s="3">
+        <v>7.4777397260273899</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="3">
+        <v>7.4827397260273898</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B203" s="3">
+        <v>7.4877397260273897</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B204" s="3">
+        <v>7.4927397260273896</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B205" s="3">
+        <v>7.4977397260273904</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B206" s="3">
+        <v>7.5027397260273903</v>
       </c>
     </row>
   </sheetData>
@@ -5516,7 +7498,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="32" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="3">
@@ -5527,7 +7509,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="40"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="3">
         <v>0.05</v>
       </c>
@@ -5536,7 +7518,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="40"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="3">
         <v>0.06</v>
       </c>
@@ -6157,7 +8139,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="32" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="3">
@@ -6168,7 +8150,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -6177,7 +8159,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -6289,7 +8271,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="32" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="3">
@@ -6300,7 +8282,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="40"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="3">
         <v>0.05</v>
       </c>
@@ -6309,7 +8291,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="40"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="3">
         <v>0.06</v>
       </c>
@@ -6378,7 +8360,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="40" t="s">
+      <c r="A27" s="32" t="s">
         <v>87</v>
       </c>
       <c r="C27" s="3">
@@ -6386,13 +8368,13 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="40"/>
+      <c r="A28" s="32"/>
       <c r="C28" s="3">
         <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="40"/>
+      <c r="A29" s="32"/>
       <c r="C29" s="3">
         <v>110</v>
       </c>
@@ -7012,7 +8994,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="32" t="s">
         <v>88</v>
       </c>
       <c r="B5" s="3">
@@ -7023,7 +9005,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -7032,7 +9014,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>

--- a/tests/workbooktests/workbooks/test_bonds.xlsx
+++ b/tests/workbooktests/workbooks/test_bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C765770E-1E17-4A42-BC55-6DEF547373F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB21C28-8590-48C0-AC89-070A617FEADF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <sheet name="Callability" sheetId="21" r:id="rId11"/>
     <sheet name="CallableFixedRateBond" sheetId="13" r:id="rId12"/>
     <sheet name="CallableZeroCouponBond" sheetId="14" r:id="rId13"/>
-    <sheet name="CPIBond" sheetId="17" r:id="rId14"/>
+    <sheet name="CPIBond" sheetId="22" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="200">
   <si>
     <t>Bond</t>
   </si>
@@ -584,6 +584,63 @@
   </si>
   <si>
     <t>time_grid</t>
+  </si>
+  <si>
+    <t>growth_only</t>
+  </si>
+  <si>
+    <t>base_cpi</t>
+  </si>
+  <si>
+    <t>observation_lag</t>
+  </si>
+  <si>
+    <t>cpi_index</t>
+  </si>
+  <si>
+    <t>observation_interpolation</t>
+  </si>
+  <si>
+    <t>familiy_name</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>revised</t>
+  </si>
+  <si>
+    <t>frequency</t>
+  </si>
+  <si>
+    <t>avaibility_lag</t>
+  </si>
+  <si>
+    <t>zero_inflation_trem_structure</t>
+  </si>
+  <si>
+    <t>TEST_CPI</t>
+  </si>
+  <si>
+    <t>dates</t>
+  </si>
+  <si>
+    <t>rates</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>qlIndexAddFixing</t>
+  </si>
+  <si>
+    <t>Linear</t>
+  </si>
+  <si>
+    <t>TARGET</t>
+  </si>
+  <si>
+    <t>qlCPIBond</t>
   </si>
 </sst>
 </file>
@@ -926,7 +983,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -972,20 +1029,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1042,9 +1089,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1180,6 +1224,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1509,18 +1574,18 @@
       <c r="B2" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="115" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="31"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="116"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="17"/>
       <c r="C3" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="112" t="s">
+      <c r="D3" s="107" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="19" t="s">
@@ -1528,12 +1593,12 @@
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
@@ -1606,7 +1671,7 @@
       <c r="E11" s="22"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="21" t="s">
@@ -1616,7 +1681,7 @@
       <c r="E12" s="22"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="25" t="s">
         <v>124</v>
       </c>
       <c r="C13" s="21"/>
@@ -1624,7 +1689,7 @@
       <c r="E13" s="22"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="25" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="21"/>
@@ -1636,7 +1701,7 @@
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="21"/>
@@ -1648,10 +1713,12 @@
       </c>
     </row>
     <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23"/>
+      <c r="C16" s="23" t="s">
+        <v>112</v>
+      </c>
       <c r="D16" s="23"/>
       <c r="E16" s="24"/>
     </row>
@@ -1706,7 +1773,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="117" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="3">
@@ -1717,7 +1784,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
+      <c r="A6" s="117"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
@@ -1726,7 +1793,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
+      <c r="A7" s="117"/>
       <c r="B7" s="3">
         <v>101</v>
       </c>
@@ -2652,1161 +2719,1161 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="30">
         <v>2</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="31">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="33">
         <v>100</v>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="34">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="43">
         <v>45659</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="44">
         <v>45659</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="49">
+      <c r="B7" s="45">
         <v>48215</v>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="46">
         <v>48215</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="47" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="48" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="51" t="str">
+      <c r="B9" s="47" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
-      <c r="C9" s="52" t="str">
+      <c r="C9" s="48" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="48" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="48" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="48" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="51" t="b">
+      <c r="B13" s="47" t="b">
         <v>0</v>
       </c>
-      <c r="C13" s="52" t="b">
+      <c r="C13" s="48" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="44" t="str">
+      <c r="B14" s="40" t="str">
         <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R14C2Schedule,A</v>
       </c>
-      <c r="C14" s="45" t="str">
+      <c r="C14" s="41" t="str">
         <f>_xll.qlSchedule(C6,C7,C8,C9,C10,C11,C12,C13)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R14C3Schedule,A</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="33">
         <v>0.06</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="34">
         <v>0.03</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
-      <c r="B16" s="37">
+      <c r="A16" s="118"/>
+      <c r="B16" s="33">
         <v>0.06</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="34">
         <v>0.03</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="58"/>
-      <c r="B17" s="37">
+      <c r="A17" s="118"/>
+      <c r="B17" s="33">
         <v>0.06</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="34">
         <v>0.03</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="34" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="34" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="33">
         <v>100</v>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="34">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="56">
+      <c r="B21" s="52">
         <v>45659</v>
       </c>
-      <c r="C21" s="57">
+      <c r="C21" s="53">
         <v>45659</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="B22" s="54" t="str">
+      <c r="B22" s="50" t="str">
         <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R22C2BondPrice,A</v>
       </c>
-      <c r="C22" s="55" t="str">
+      <c r="C22" s="51" t="str">
         <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R22C3BondPrice,A</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="56" t="s">
+      <c r="B23" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="53" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="56">
+      <c r="B24" s="52">
         <v>46754</v>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="53">
         <v>46754</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="44" t="str">
+      <c r="B25" s="40" t="str">
         <f>_xll.qlCallability(B22,B23,B24)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R25C2Callability,A</v>
       </c>
-      <c r="C25" s="45" t="str">
+      <c r="C25" s="41" t="str">
         <f>_xll.qlCallability(C22,C23,C24)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R25C3Callability,A</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="34" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="37" t="str">
+      <c r="B27" s="33" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
-      <c r="C27" s="38" t="str">
+      <c r="C27" s="34" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="38" t="s">
+      <c r="B28" s="33"/>
+      <c r="C28" s="34" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="38" t="b">
+      <c r="B29" s="33"/>
+      <c r="C29" s="34" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="85" t="s">
+      <c r="A30" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="B30" s="83" t="str">
+      <c r="B30" s="78" t="str">
         <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R30C2CallableFixedRateBond,A</v>
       </c>
-      <c r="C30" s="84" t="str">
+      <c r="C30" s="79" t="str">
         <f>_xll.qlCallableFixedRateBond(C4,C5,C14,C15:C17,C18,C19,C20,C21,C25,C26,C27,C28,C29)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R30C3CallableFixedRateBond,A</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="69" t="s">
+      <c r="A31" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="70">
+      <c r="B31" s="65">
         <f>_xll.qlBondNextCouponRate(B30)</f>
         <v>0.06</v>
       </c>
-      <c r="C31" s="70">
+      <c r="C31" s="65">
         <f>_xll.qlBondNextCouponRate(C30)</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="69" t="s">
+      <c r="A32" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="70">
+      <c r="B32" s="65">
         <f>_xll.qlBondPreviousCouponRate(B30)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="70">
+      <c r="C32" s="65">
         <f>_xll.qlBondPreviousCouponRate(C30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="71" t="s">
+      <c r="A33" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="72">
+      <c r="B33" s="67">
         <f>_xll.qlBondNextCashFlowDate(B30)</f>
         <v>45840</v>
       </c>
-      <c r="C33" s="72">
+      <c r="C33" s="67">
         <f>_xll.qlBondNextCashFlowDate(C30)</f>
         <v>45840</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="69" t="s">
+      <c r="A34" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="72">
+      <c r="B34" s="67">
         <f>_xll.qlBondPreviousCashFlowDate(B30)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="72">
+      <c r="C34" s="67">
         <f>_xll.qlBondPreviousCashFlowDate(C30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="69" t="s">
+      <c r="A35" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="70">
+      <c r="B35" s="65">
         <f>_xll.qlBondSettlementDays(B30)</f>
         <v>2</v>
       </c>
-      <c r="C35" s="70">
+      <c r="C35" s="65">
         <f>_xll.qlBondSettlementDays(C30)</f>
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="69" t="s">
+      <c r="A36" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="72">
+      <c r="B36" s="67">
         <f>_xll.qlBondSettlementDate(B30)</f>
         <v>45663</v>
       </c>
-      <c r="C36" s="72">
+      <c r="C36" s="67">
         <f>_xll.qlBondSettlementDate(C30)</f>
         <v>45663</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="71" t="s">
+      <c r="A37" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="70" t="b">
+      <c r="B37" s="65" t="b">
         <f>_xll.qlBondIsTradable(B30)</f>
         <v>1</v>
       </c>
-      <c r="C37" s="70" t="b">
+      <c r="C37" s="65" t="b">
         <f>_xll.qlBondIsTradable(C30)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="69" t="s">
+      <c r="A38" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="72">
+      <c r="B38" s="67">
         <f>_xll.qlBondStartDate(B30)</f>
         <v>45659</v>
       </c>
-      <c r="C38" s="72">
+      <c r="C38" s="67">
         <f>_xll.qlBondStartDate(C30)</f>
         <v>45659</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="72">
+      <c r="B39" s="67">
         <f>_xll.qlBondMaturityDate(B30)</f>
         <v>48215</v>
       </c>
-      <c r="C39" s="72">
+      <c r="C39" s="67">
         <f>_xll.qlBondMaturityDate(C30)</f>
         <v>48215</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="69" t="s">
+      <c r="A40" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="72">
+      <c r="B40" s="67">
         <f>_xll.qlBondIssueDate(B30)</f>
         <v>45659</v>
       </c>
-      <c r="C40" s="72">
+      <c r="C40" s="67">
         <f>_xll.qlBondIssueDate(C30)</f>
         <v>45659</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="71" t="s">
+      <c r="A41" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="B41" s="70" t="str">
+      <c r="B41" s="65" t="str">
         <f>_xll.qlBondCashFlows(B30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R41C2CashFlow,A</v>
       </c>
-      <c r="C41" s="70" t="str">
+      <c r="C41" s="65" t="str">
         <f>_xll.qlBondCashFlows(C30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R41C3CashFlow,A</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="69" t="s">
+      <c r="A42" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="70" t="str">
+      <c r="B42" s="65" t="str">
         <f>_xll.qlBondRedemption(B30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R42C2CashFlow,A</v>
       </c>
-      <c r="C42" s="70" t="str">
+      <c r="C42" s="65" t="str">
         <f>_xll.qlBondRedemption(C30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R42C3CashFlow,A</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="69" t="s">
+      <c r="A43" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="70" t="str">
+      <c r="B43" s="65" t="str">
         <f>_xll.qlBondRedemptions(B30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R43C2CashFlow,A</v>
       </c>
-      <c r="C43" s="70" t="str">
+      <c r="C43" s="65" t="str">
         <f>_xll.qlBondRedemptions(C30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R43C3CashFlow,A</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="69" t="s">
+      <c r="A44" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="70" t="str">
+      <c r="B44" s="65" t="str">
         <f>_xll.qlBondCalendar(B30)</f>
         <v>TARGET</v>
       </c>
-      <c r="C44" s="70" t="str">
+      <c r="C44" s="65" t="str">
         <f>_xll.qlBondCalendar(C30)</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="71" t="s">
+      <c r="A45" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="70">
+      <c r="B45" s="65">
         <f>_xll.qlBondNotional(B30)</f>
         <v>100</v>
       </c>
-      <c r="C45" s="70">
+      <c r="C45" s="65">
         <f>_xll.qlBondNotional(C30)</f>
         <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="70">
+      <c r="B46" s="65">
         <f>_xll.qlBondNotionals(B30)</f>
         <v>100</v>
       </c>
-      <c r="C46" s="70">
+      <c r="C46" s="65">
         <f>_xll.qlBondNotionals(C30)</f>
         <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="60" t="s">
+      <c r="A47" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="B47" s="34">
+      <c r="B47" s="30">
         <v>0.2</v>
       </c>
-      <c r="C47" s="35">
+      <c r="C47" s="31">
         <v>0.2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="42" t="s">
+      <c r="A48" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="37" t="str">
+      <c r="B48" s="33" t="str">
         <f>_xll.qlFlatForward($B$2,0.03,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C48" s="38" t="str">
+      <c r="C48" s="34" t="str">
         <f>_xll.qlFlatForward($B$2,0.03,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="59" t="s">
+      <c r="A49" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="44" t="str">
+      <c r="B49" s="40" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(B47,B48)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R49C2BlackCallableFixedRateBondEngine,A</v>
       </c>
-      <c r="C49" s="45" t="str">
+      <c r="C49" s="41" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(C47,C48)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R49C3BlackCallableFixedRateBondEngine,A</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="42" t="s">
+      <c r="A50" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="B50" s="37" t="b">
+      <c r="B50" s="33" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B30,B49)</f>
         <v>1</v>
       </c>
-      <c r="C50" s="38" t="b">
+      <c r="C50" s="34" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(C30,C49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="41" t="s">
+      <c r="A51" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B51" s="86">
+      <c r="B51" s="81">
         <f>_xll.qlBondCleanPrice(B30,B50)</f>
         <v>110.09602977203045</v>
       </c>
-      <c r="C51" s="87">
+      <c r="C51" s="82">
         <f>_xll.qlBondCleanPrice(C30,C50)</f>
         <v>99.448292731770522</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="61" t="s">
+      <c r="A52" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="62">
+      <c r="B52" s="57">
         <v>2.8928264971926201E-2</v>
       </c>
-      <c r="C52" s="63">
+      <c r="C52" s="58">
         <v>2.8928264971926201E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="43" t="s">
+      <c r="A53" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B53" s="64">
+      <c r="B53" s="59">
         <f>_xll.qlBondCleanPrice2(B30,B52,"actual360","continuous")</f>
         <v>119.09555910006989</v>
       </c>
-      <c r="C53" s="65">
+      <c r="C53" s="60">
         <f>_xll.qlBondCleanPrice2(C30,C52,"actual360","continuous")</f>
         <v>100.54551097389133</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="41" t="s">
+      <c r="A54" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B54" s="77">
+      <c r="B54" s="72">
         <f>_xll.qlBondDirtyPrice(B30,B50)</f>
         <v>110.16269643869711</v>
       </c>
-      <c r="C54" s="78">
+      <c r="C54" s="73">
         <f>_xll.qlBondDirtyPrice(C30,C50)</f>
         <v>99.481626065103853</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="66" t="s">
+      <c r="A55" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="B55" s="67">
+      <c r="B55" s="62">
         <f>_xll.qlBondDirtyPrice2(B30,B52,"actual360","CONTINUOUS","annual")</f>
         <v>119.16222576673655</v>
       </c>
-      <c r="C55" s="68">
+      <c r="C55" s="63">
         <f>_xll.qlBondDirtyPrice2(C30,C52,"actual360","CONTINUOUS","annual")</f>
         <v>100.57884430722466</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="41" t="s">
+      <c r="A56" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="77">
+      <c r="B56" s="72">
         <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual",,,B50)</f>
         <v>4.2056273937225358E-2</v>
       </c>
-      <c r="C56" s="78">
+      <c r="C56" s="73">
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual",,,C50)</f>
         <v>3.0632255029678354E-2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="61" t="s">
+      <c r="A57" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="62" t="str">
+      <c r="B57" s="57" t="str">
         <f>_xll.qlBondPrice(B51,"clean")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R57C2BondPrice,A</v>
       </c>
-      <c r="C57" s="63" t="str">
+      <c r="C57" s="58" t="str">
         <f>_xll.qlBondPrice(C51,"clean")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R57C3BondPrice,A</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="43" t="s">
+      <c r="A58" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="64">
+      <c r="B58" s="59">
         <f>_xll.qlBondYield2(B30,B57,"actual360","CONTINUOUS","annual")</f>
         <v>4.2157923221588151E-2</v>
       </c>
-      <c r="C58" s="65">
+      <c r="C58" s="60">
         <f>_xll.qlBondYield2(C30,C57,"actual360","CONTINUOUS","annual")</f>
         <v>3.0684329366683964E-2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="61" t="s">
+      <c r="A59" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B59" s="54">
+      <c r="B59" s="50">
         <v>45667</v>
       </c>
-      <c r="C59" s="55">
+      <c r="C59" s="51">
         <v>45667</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="43" t="s">
+      <c r="A60" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B60" s="64">
+      <c r="B60" s="59">
         <f>_xll.qlBondAccruedAmount(B30,B59)</f>
         <v>0.13333333333334085</v>
       </c>
-      <c r="C60" s="65">
+      <c r="C60" s="60">
         <f>_xll.qlBondAccruedAmount(C30,C59)</f>
         <v>6.6666666666659324E-2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="B61" s="73">
+      <c r="B61" s="68">
         <f>_xll.qlBondSettlementValue(B30,B50)</f>
         <v>110.16269643869711</v>
       </c>
-      <c r="C61" s="73">
+      <c r="C61" s="68">
         <f>_xll.qlBondSettlementValue(C30,C50)</f>
         <v>99.481626065103839</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="71" t="s">
+      <c r="A62" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="B62" s="73">
+      <c r="B62" s="68">
         <f>_xll.qlBondSettlementValue2(B30,B51)</f>
         <v>110.16269643869711</v>
       </c>
-      <c r="C62" s="73">
+      <c r="C62" s="68">
         <f>_xll.qlBondSettlementValue2(C30,C51)</f>
         <v>99.481626065103853</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="74" t="s">
+      <c r="A63" s="69" t="s">
         <v>139</v>
       </c>
-      <c r="B63" s="75" t="str">
+      <c r="B63" s="70" t="str">
         <f>_xll.qlCallableBondCallability(B30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R63C2Callability,A</v>
       </c>
-      <c r="C63" s="75" t="str">
+      <c r="C63" s="70" t="str">
         <f>_xll.qlCallableBondCallability(C30)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R63C3Callability,A</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="61" t="s">
+      <c r="A64" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="B64" s="34" t="str">
+      <c r="B64" s="30" t="str">
         <f>_xll.qlBondPrice(B51,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R64C2BondPrice,A</v>
       </c>
-      <c r="C64" s="35" t="str">
+      <c r="C64" s="31" t="str">
         <f>_xll.qlBondPrice(C51,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R64C3BondPrice,A</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="40" t="s">
+      <c r="A65" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="B65" s="37" t="str">
+      <c r="B65" s="33" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R65C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C65" s="38" t="str">
+      <c r="C65" s="34" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R65C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="40" t="s">
+      <c r="A66" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="B66" s="76">
+      <c r="B66" s="71">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C66" s="79">
+      <c r="C66" s="74">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="40" t="s">
+      <c r="A67" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="37">
+      <c r="B67" s="33">
         <v>100</v>
       </c>
-      <c r="C67" s="38">
+      <c r="C67" s="34">
         <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="40" t="s">
+      <c r="A68" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="37">
+      <c r="B68" s="33">
         <v>0.01</v>
       </c>
-      <c r="C68" s="38">
+      <c r="C68" s="34">
         <v>0.01</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="40" t="s">
+      <c r="A69" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="B69" s="37">
+      <c r="B69" s="33">
         <v>0.5</v>
       </c>
-      <c r="C69" s="38">
+      <c r="C69" s="34">
         <v>0.5</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="80" t="s">
+      <c r="A70" s="75" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="81">
+      <c r="B70" s="76">
         <f>_xll.qlCallableBondImpliedVolatility(B30,B64,B65,B66,B67,B68,B69)</f>
         <v>0.32447524793161092</v>
       </c>
-      <c r="C70" s="82">
+      <c r="C70" s="77">
         <f>_xll.qlCallableBondImpliedVolatility(C30,C64,C65,C66,C67,C68,C69)</f>
         <v>0.25030192954114117</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="88" t="s">
+      <c r="A71" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="37">
+      <c r="B71" s="33">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(B30,105,B48,"Actual/360","Simple","Annual",,,1000,,B50))</f>
         <v>1</v>
       </c>
-      <c r="C71" s="38">
+      <c r="C71" s="34">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(C30,105,C48,"Actual/360","Simple","Annual",,,1000,,C50))</f>
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="66" t="s">
+      <c r="A72" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="83">
+      <c r="B72" s="78">
         <f>_xll.qlCallableBondCleanPriceOAS(B30,0.3,B48,"actual/360","simple","annual",,B50)</f>
         <v>110.05931499268738</v>
       </c>
-      <c r="C72" s="84">
+      <c r="C72" s="79">
         <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual",,C50)</f>
         <v>99.415137715891774</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="66" t="s">
+      <c r="A73" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="B73" s="83">
+      <c r="B73" s="78">
         <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
         <v>0</v>
       </c>
-      <c r="C73" s="84">
+      <c r="C73" s="79">
         <f>_xll.qlCallableBondEffectiveDuration(C30,0.3,C48,"actual/360","compounded","annual",,C50)</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="41" t="s">
+      <c r="A74" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B74" s="37">
+      <c r="B74" s="33">
         <f>_xll.qlCallableBondEffectiveConvexity(B30,0.3,B48,"actual/360","compounded","annual",,B50)</f>
         <v>0</v>
       </c>
-      <c r="C74" s="38">
+      <c r="C74" s="34">
         <f>_xll.qlCallableBondEffectiveConvexity(C30,0.3,C48,"actual/360","compounded","annual",,C50)</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="61" t="s">
+      <c r="A75" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="B75" s="62" t="str">
+      <c r="B75" s="57" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R75C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C75" s="63" t="str">
+      <c r="C75" s="58" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R75C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="40" t="s">
+      <c r="A76" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="B76" s="77">
+      <c r="B76" s="72">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C76" s="78">
+      <c r="C76" s="73">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="40" t="s">
+      <c r="A77" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="B77" s="77" t="s">
+      <c r="B77" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="C77" s="78" t="s">
+      <c r="C77" s="73" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="40" t="s">
+      <c r="A78" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="B78" s="77" t="s">
+      <c r="B78" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="C78" s="78" t="s">
+      <c r="C78" s="73" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="40" t="s">
+      <c r="A79" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="B79" s="77" t="s">
+      <c r="B79" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="C79" s="78" t="s">
+      <c r="C79" s="73" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="40" t="s">
+      <c r="A80" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="B80" s="77"/>
-      <c r="C80" s="78"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="73"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="43" t="s">
+      <c r="A81" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="44">
+      <c r="B81" s="40">
         <f>_xll.qlBondCleanPriceFromZSpread(B30,B75,B76,B77,B78,B79)</f>
         <v>115.27440939680005</v>
       </c>
-      <c r="C81" s="45">
+      <c r="C81" s="41">
         <f>_xll.qlBondCleanPriceFromZSpread(C30,C75,C76,C77,C78,C79)</f>
         <v>97.090069430863338</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="33" t="s">
+      <c r="A83" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="B83" s="34" t="str">
+      <c r="B83" s="30" t="str">
         <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R83C2CallableFixedRateBond,A</v>
       </c>
-      <c r="C83" s="35" t="str">
+      <c r="C83" s="31" t="str">
         <f>_xll.qlCallableFixedRateBond(C4,C5,C14,C15:C17,C18,C19,C20,C21,C25)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R83C3CallableFixedRateBond,A</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="36" t="s">
+      <c r="A84" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="B84" s="37" t="str">
+      <c r="B84" s="33" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R84C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C84" s="38" t="str">
+      <c r="C84" s="34" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R84C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="36" t="s">
+      <c r="A85" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="B85" s="37">
+      <c r="B85" s="33">
         <v>0.03</v>
       </c>
-      <c r="C85" s="38">
+      <c r="C85" s="34">
         <v>0.03</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="36" t="s">
+      <c r="A86" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="B86" s="37">
+      <c r="B86" s="33">
         <v>0.01</v>
       </c>
-      <c r="C86" s="38">
+      <c r="C86" s="34">
         <v>0.01</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="39" t="s">
+      <c r="A87" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="B87" s="37" t="str">
+      <c r="B87" s="33" t="str">
         <f>_xll.qlHullWhite(B84,B85,B86)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R87C2HullWhite,A</v>
       </c>
-      <c r="C87" s="38" t="str">
+      <c r="C87" s="34" t="str">
         <f>_xll.qlHullWhite(C84,C85,C86)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R87C3HullWhite,A</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="40" t="s">
+      <c r="A88" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="37">
+      <c r="B88" s="33">
         <v>100</v>
       </c>
-      <c r="C88" s="38">
+      <c r="C88" s="34">
         <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="41" t="s">
+      <c r="A89" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="B89" s="37" t="str">
+      <c r="B89" s="33" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine(B87,B88)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R89C2TreeCallableFixedRateBondEngine,A</v>
       </c>
-      <c r="C89" s="38" t="str">
+      <c r="C89" s="34" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine(C87,C88)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R89C3TreeCallableFixedRateBondEngine,A</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="42" t="s">
+      <c r="A90" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="B90" s="37" t="b">
+      <c r="B90" s="33" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B83,B89)</f>
         <v>1</v>
       </c>
-      <c r="C90" s="38" t="b">
+      <c r="C90" s="34" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(C83,C89)</f>
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="43" t="s">
+      <c r="A91" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B91" s="44">
+      <c r="B91" s="40">
         <f>_xll.qlBondCleanPrice(B83,B90)</f>
         <v>113.36825228071841</v>
       </c>
-      <c r="C91" s="45">
+      <c r="C91" s="41">
         <f>_xll.qlBondCleanPrice(C83,C90)</f>
         <v>104.15316507210984</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="33" t="s">
+      <c r="A92" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="B92" s="34" t="str">
+      <c r="B92" s="30" t="str">
         <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R92C2CallableFixedRateBond,A</v>
       </c>
-      <c r="C92" s="35" t="str">
+      <c r="C92" s="31" t="str">
         <f>_xll.qlCallableFixedRateBond(C4,C5,C14,C15:C17,C18,C19,C20,C21,C25)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R92C3CallableFixedRateBond,A</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="36" t="s">
+      <c r="A93" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="B93" s="37" t="str">
+      <c r="B93" s="33" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R93C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C93" s="38" t="str">
+      <c r="C93" s="34" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R93C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="36" t="s">
+      <c r="A94" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="B94" s="37">
+      <c r="B94" s="33">
         <v>0.03</v>
       </c>
-      <c r="C94" s="38">
+      <c r="C94" s="34">
         <v>0.03</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="36" t="s">
+      <c r="A95" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="B95" s="37">
+      <c r="B95" s="33">
         <v>0.01</v>
       </c>
-      <c r="C95" s="38">
+      <c r="C95" s="34">
         <v>0.01</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="39" t="s">
+      <c r="A96" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="B96" s="37" t="str">
+      <c r="B96" s="33" t="str">
         <f>_xll.qlHullWhite(B93,B94,B95)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R96C2HullWhite,A</v>
       </c>
-      <c r="C96" s="38" t="str">
+      <c r="C96" s="34" t="str">
         <f>_xll.qlHullWhite(C93,C94,C95)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R96C3HullWhite,A</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="40" t="s">
+      <c r="A97" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="B97" s="37" t="str">
+      <c r="B97" s="33" t="str">
         <f>_xll.qlTimeGridFromTimes(B104:B219)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R97C2TimeGrid,A</v>
       </c>
-      <c r="C97" s="38" t="str">
+      <c r="C97" s="34" t="str">
         <f>_xll.qlTimeGridFromTimes(B104:B219)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R97C3TimeGrid,A</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="41" t="s">
+      <c r="A98" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="B98" s="37" t="str">
+      <c r="B98" s="33" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine2(B96,B97)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R98C2TreeCallableFixedRateBondEngine,A</v>
       </c>
-      <c r="C98" s="38" t="str">
+      <c r="C98" s="34" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine2(C96,C97)</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R98C3TreeCallableFixedRateBondEngine,A</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="42" t="s">
+      <c r="A99" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="B99" s="37" t="b">
+      <c r="B99" s="33" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B92,B98)</f>
         <v>1</v>
       </c>
-      <c r="C99" s="38" t="b">
+      <c r="C99" s="34" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(C92,C98)</f>
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="43" t="s">
+      <c r="A100" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B100" s="44">
+      <c r="B100" s="40">
         <f>_xll.qlBondCleanPrice(B92,B99)</f>
         <v>113.36581391762972</v>
       </c>
-      <c r="C100" s="45">
+      <c r="C100" s="41">
         <f>_xll.qlBondCleanPrice(C92,C99)</f>
         <v>104.21047805357765</v>
       </c>
@@ -4430,1018 +4497,1018 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="94">
+      <c r="B4" s="89">
         <v>2</v>
       </c>
-      <c r="C4" s="95">
+      <c r="C4" s="90">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="96">
+      <c r="B5" s="91">
         <v>100</v>
       </c>
-      <c r="C5" s="97">
+      <c r="C5" s="92">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="96" t="str">
+      <c r="B6" s="91" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
-      <c r="C6" s="97" t="str">
+      <c r="C6" s="92" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="98">
+      <c r="B7" s="93">
         <v>48215</v>
       </c>
-      <c r="C7" s="99">
+      <c r="C7" s="94">
         <v>48215</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="91" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="97" t="s">
+      <c r="C8" s="92" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="97" t="s">
+      <c r="B9" s="91"/>
+      <c r="C9" s="92" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="97">
+      <c r="B10" s="91"/>
+      <c r="C10" s="92">
         <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="99">
+      <c r="B11" s="91"/>
+      <c r="C11" s="94">
         <v>45659</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B12" s="100" t="str">
+      <c r="B12" s="95" t="str">
         <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C2BondPrice,A</v>
       </c>
-      <c r="C12" s="101" t="str">
+      <c r="C12" s="96" t="str">
         <f>_xll.qlBondPrice(105,"CLEAN")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C3BondPrice,A</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="C13" s="99" t="s">
+      <c r="C13" s="94" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="98">
+      <c r="B14" s="93">
         <v>46754</v>
       </c>
-      <c r="C14" s="99">
+      <c r="C14" s="94">
         <v>46754</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="93" t="s">
+      <c r="A15" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="B15" s="102" t="str">
+      <c r="B15" s="97" t="str">
         <f>_xll.qlCallability(B12,B13,B14)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C2Callability,A</v>
       </c>
-      <c r="C15" s="103" t="str">
+      <c r="C15" s="98" t="str">
         <f>_xll.qlCallability(C12,C13,C14)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C3Callability,A</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="69" t="s">
+      <c r="A16" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="104" t="str">
+      <c r="B16" s="99" t="str">
         <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C2CallableZeroCouponBond,A</v>
       </c>
-      <c r="C16" s="104" t="str">
+      <c r="C16" s="99" t="str">
         <f>_xll.qlCallableZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,C11,C15)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C3CallableZeroCouponBond,A</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="85" t="s">
+      <c r="A17" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="105">
+      <c r="B17" s="100">
         <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 2nd, 2032",_xll.qlBondNextCouponRate(B16))</f>
         <v>1</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="31">
         <f>FIND("RuntimeError: RuntimeError: no coupon paid at cashflow date January 2nd, 2032",_xll.qlBondNextCouponRate(C16))</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="109">
+      <c r="B18" s="104">
         <f>_xll.qlBondPreviousCouponRate(B16)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="84">
+      <c r="C18" s="79">
         <f>_xll.qlBondPreviousCouponRate(C16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="107">
+      <c r="B19" s="102">
         <f>_xll.qlBondNextCashFlowDate(B16)</f>
         <v>48215</v>
       </c>
-      <c r="C19" s="57">
+      <c r="C19" s="53">
         <f>_xll.qlBondNextCashFlowDate(C16)</f>
         <v>48215</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="85" t="s">
+      <c r="A20" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="110">
+      <c r="B20" s="105">
         <f>_xll.qlBondPreviousCashFlowDate(B16)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="111">
+      <c r="C20" s="106">
         <f>_xll.qlBondPreviousCashFlowDate(C16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="106">
+      <c r="B21" s="101">
         <f>_xll.qlBondSettlementDays(B16)</f>
         <v>2</v>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="34">
         <f>_xll.qlBondSettlementDays(C16)</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="110">
+      <c r="B22" s="105">
         <f>_xll.qlBondSettlementDate(B16)</f>
         <v>45663</v>
       </c>
-      <c r="C22" s="111">
+      <c r="C22" s="106">
         <f>_xll.qlBondSettlementDate(C16)</f>
         <v>45663</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="106" t="b">
+      <c r="B23" s="101" t="b">
         <f>_xll.qlBondIsTradable(B16)</f>
         <v>1</v>
       </c>
-      <c r="C23" s="38" t="b">
+      <c r="C23" s="34" t="b">
         <f>_xll.qlBondIsTradable(C16)</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="85" t="s">
+      <c r="A24" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="110">
+      <c r="B24" s="105">
         <f>_xll.qlBondStartDate(B16)</f>
         <v>48215</v>
       </c>
-      <c r="C24" s="111">
+      <c r="C24" s="106">
         <f>_xll.qlBondStartDate(C16)</f>
         <v>48215</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="85" t="s">
+      <c r="A25" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="107">
+      <c r="B25" s="102">
         <f>_xll.qlBondMaturityDate(B16)</f>
         <v>48215</v>
       </c>
-      <c r="C25" s="57">
+      <c r="C25" s="53">
         <f>_xll.qlBondMaturityDate(C16)</f>
         <v>48215</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="85" t="s">
+      <c r="A26" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="110">
+      <c r="B26" s="105">
         <f>_xll.qlBondIssueDate(B16)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="111">
+      <c r="C26" s="106">
         <f>_xll.qlBondIssueDate(C16)</f>
         <v>45659</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="106" t="str">
+      <c r="B27" s="101" t="str">
         <f>_xll.qlBondCashFlows(B16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C2CashFlow,A</v>
       </c>
-      <c r="C27" s="38" t="str">
+      <c r="C27" s="34" t="str">
         <f>_xll.qlBondCashFlows(C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C3CashFlow,A</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="85" t="s">
+      <c r="A28" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="109" t="str">
+      <c r="B28" s="104" t="str">
         <f>_xll.qlBondRedemption(B16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C2CashFlow,A</v>
       </c>
-      <c r="C28" s="84" t="str">
+      <c r="C28" s="79" t="str">
         <f>_xll.qlBondRedemption(C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C3CashFlow,A</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="85" t="s">
+      <c r="A29" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="106" t="str">
+      <c r="B29" s="101" t="str">
         <f>_xll.qlBondRedemptions(B16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C2CashFlow,A</v>
       </c>
-      <c r="C29" s="38" t="str">
+      <c r="C29" s="34" t="str">
         <f>_xll.qlBondRedemptions(C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C3CashFlow,A</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="85" t="s">
+      <c r="A30" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="109" t="str">
+      <c r="B30" s="104" t="str">
         <f>_xll.qlBondCalendar(B16)</f>
         <v>TARGET</v>
       </c>
-      <c r="C30" s="84" t="str">
+      <c r="C30" s="79" t="str">
         <f>_xll.qlBondCalendar(C16)</f>
         <v>TARGET</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="109">
+      <c r="B31" s="104">
         <f>_xll.qlBondNotional(B16)</f>
         <v>100</v>
       </c>
-      <c r="C31" s="84">
+      <c r="C31" s="79">
         <f>_xll.qlBondNotional(C16)</f>
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="108">
+      <c r="B32" s="103">
         <f>_xll.qlBondNotionals(B16)</f>
         <v>100</v>
       </c>
-      <c r="C32" s="45">
+      <c r="C32" s="41">
         <f>_xll.qlBondNotionals(C16)</f>
         <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="37">
+      <c r="B33" s="33">
         <v>0.15</v>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="34">
         <v>0.15</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="37" t="str">
+      <c r="B34" s="33" t="str">
         <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C34" s="38" t="str">
+      <c r="C34" s="34" t="str">
         <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="59" t="s">
+      <c r="A35" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="44" t="str">
+      <c r="B35" s="40" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(B33,B34)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R35C2BlackCallableFixedRateBondEngine,A</v>
       </c>
-      <c r="C35" s="45" t="str">
+      <c r="C35" s="41" t="str">
         <f>_xll.qlBlackCallableFixedRateBondEngine(C33,C34)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R35C3BlackCallableFixedRateBondEngine,A</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="42" t="s">
+      <c r="A36" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="37" t="b">
+      <c r="B36" s="33" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B16,B35)</f>
         <v>1</v>
       </c>
-      <c r="C36" s="38" t="b">
+      <c r="C36" s="34" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(C16,C35)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="41" t="s">
+      <c r="A37" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="77">
+      <c r="B37" s="72">
         <f>_xll.qlBondCleanPrice(B16,B36)</f>
         <v>80.906733580822063</v>
       </c>
-      <c r="C37" s="78">
+      <c r="C37" s="73">
         <f>_xll.qlBondCleanPrice(C16,C36)</f>
         <v>80.906733580822063</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="61" t="s">
+      <c r="A38" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="62">
+      <c r="B38" s="57">
         <v>2.9888064241409308E-2</v>
       </c>
-      <c r="C38" s="63">
+      <c r="C38" s="58">
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="64">
+      <c r="B39" s="59">
         <f>_xll.qlBondCleanPrice2(B16,B38,"actual360","continuous")</f>
         <v>80.906730788838317</v>
       </c>
-      <c r="C39" s="65">
+      <c r="C39" s="60">
         <f>_xll.qlBondCleanPrice2(C16,C38,"actual360","continuous")</f>
         <v>80.906730788838317</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="41" t="s">
+      <c r="A40" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="77">
+      <c r="B40" s="72">
         <f>_xll.qlBondDirtyPrice(B16,B36)</f>
         <v>80.906733580822063</v>
       </c>
-      <c r="C40" s="78">
+      <c r="C40" s="73">
         <f>_xll.qlBondDirtyPrice(C16,C36)</f>
         <v>80.906733580822063</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="67">
+      <c r="B41" s="62">
         <f>_xll.qlBondDirtyPrice2(B16,B38,"actual360","CONTINUOUS","annual")</f>
         <v>80.906730788838317</v>
       </c>
-      <c r="C41" s="68">
+      <c r="C41" s="63">
         <f>_xll.qlBondDirtyPrice2(C16,C38,"actual360","CONTINUOUS","annual")</f>
         <v>80.906730788838317</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="41" t="s">
+      <c r="A42" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="77">
+      <c r="B42" s="72">
         <f>_xll.qlBondYield(B16,"actual360","CONTINUOUS","annual",,,B36)</f>
         <v>2.9888064241409308E-2</v>
       </c>
-      <c r="C42" s="78">
+      <c r="C42" s="73">
         <f>_xll.qlBondYield(C16,"actual360","CONTINUOUS","annual",,,C36)</f>
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="61" t="s">
+      <c r="A43" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="B43" s="62" t="str">
+      <c r="B43" s="57" t="str">
         <f>_xll.qlBondPrice(B37,"clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C2BondPrice,A</v>
       </c>
-      <c r="C43" s="63" t="str">
+      <c r="C43" s="58" t="str">
         <f>_xll.qlBondPrice(C37,"clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C3BondPrice,A</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="43" t="s">
+      <c r="A44" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="64">
+      <c r="B44" s="59">
         <f>_xll.qlBondYield2(B16,B43,"actual360","CONTINUOUS","annual")</f>
         <v>2.9888064241409308E-2</v>
       </c>
-      <c r="C44" s="65">
+      <c r="C44" s="60">
         <f>_xll.qlBondYield2(C16,C43,"actual360","CONTINUOUS","annual")</f>
         <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="61" t="s">
+      <c r="A45" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B45" s="54">
+      <c r="B45" s="50">
         <v>45667</v>
       </c>
-      <c r="C45" s="55">
+      <c r="C45" s="51">
         <v>45667</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="43" t="s">
+      <c r="A46" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="64">
+      <c r="B46" s="59">
         <f>_xll.qlBondAccruedAmount(B16,B45)</f>
         <v>0</v>
       </c>
-      <c r="C46" s="65">
+      <c r="C46" s="60">
         <f>_xll.qlBondAccruedAmount(C16,C45)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="66" t="s">
+      <c r="A47" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="67">
+      <c r="B47" s="62">
         <f>_xll.qlBondSettlementValue(B16,B36)</f>
         <v>80.906733580822063</v>
       </c>
-      <c r="C47" s="68">
+      <c r="C47" s="63">
         <f>_xll.qlBondSettlementValue(C16,C36)</f>
         <v>80.906733580822063</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="41" t="s">
+      <c r="A48" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="77">
+      <c r="B48" s="72">
         <f>_xll.qlBondSettlementValue2(B16,B37)</f>
         <v>80.906733580822063</v>
       </c>
-      <c r="C48" s="78">
+      <c r="C48" s="73">
         <f>_xll.qlBondSettlementValue2(C16,C37)</f>
         <v>80.906733580822063</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="41" t="s">
+      <c r="A49" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="B49" s="37" t="str">
+      <c r="B49" s="33" t="str">
         <f>_xll.qlCallableBondCallability(B16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C2Callability,A</v>
       </c>
-      <c r="C49" s="38" t="str">
+      <c r="C49" s="34" t="str">
         <f>_xll.qlCallableBondCallability(C16)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C3Callability,A</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="61" t="s">
+      <c r="A50" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="B50" s="34" t="str">
+      <c r="B50" s="30" t="str">
         <f>_xll.qlBondPrice(B37,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R50C2BondPrice,A</v>
       </c>
-      <c r="C50" s="35" t="str">
+      <c r="C50" s="31" t="str">
         <f>_xll.qlBondPrice(C37,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R50C3BondPrice,A</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="40" t="s">
+      <c r="A51" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="B51" s="37" t="str">
+      <c r="B51" s="33" t="str">
         <f>_xll.qlBondPrice(B37,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R51C2BondPrice,A</v>
       </c>
-      <c r="C51" s="38" t="str">
+      <c r="C51" s="34" t="str">
         <f>_xll.qlBondPrice(C37,"Clean")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R51C3BondPrice,A</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="40" t="s">
+      <c r="A52" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="B52" s="37" t="str">
+      <c r="B52" s="33" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R52C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C52" s="38" t="str">
+      <c r="C52" s="34" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R52C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="B53" s="76">
+      <c r="B53" s="71">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C53" s="79">
+      <c r="C53" s="74">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="B54" s="37">
+      <c r="B54" s="33">
         <v>100</v>
       </c>
-      <c r="C54" s="38">
+      <c r="C54" s="34">
         <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="40" t="s">
+      <c r="A55" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="B55" s="37">
+      <c r="B55" s="33">
         <v>0.01</v>
       </c>
-      <c r="C55" s="38">
+      <c r="C55" s="34">
         <v>0.01</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="40" t="s">
+      <c r="A56" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="B56" s="37">
+      <c r="B56" s="33">
         <v>0.5</v>
       </c>
-      <c r="C56" s="38">
+      <c r="C56" s="34">
         <v>0.5</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="80" t="s">
+      <c r="A57" s="75" t="s">
         <v>140</v>
       </c>
-      <c r="B57" s="90">
+      <c r="B57" s="85">
         <f>_xll.qlCallableBondImpliedVolatility(B16,B51,B52,B53,B54,B55,B56)</f>
         <v>0.49070370787832679</v>
       </c>
-      <c r="C57" s="91">
+      <c r="C57" s="86">
         <f>_xll.qlCallableBondImpliedVolatility(C16,C51,C52,C53,C54,C55,C56)</f>
         <v>0.49070370787832679</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="88" t="s">
+      <c r="A58" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="37">
+      <c r="B58" s="33">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(B16,105,B34,"Actual/360","Simple","Annual",,,1000,,B36))</f>
         <v>1</v>
       </c>
-      <c r="C58" s="38">
+      <c r="C58" s="34">
         <f>FIND("RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations",_xll.qlCallableBondOAS(C16,105,C34,"Actual/360","Simple","Annual",,,1000,,C36))</f>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="92" t="s">
+      <c r="A59" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="B59" s="83">
+      <c r="B59" s="78">
         <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual",,B36)</f>
         <v>80.879869761049534</v>
       </c>
-      <c r="C59" s="84">
+      <c r="C59" s="79">
         <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual",,C36)</f>
         <v>80.879869761049534</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="41" t="s">
+      <c r="A60" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="37">
+      <c r="B60" s="33">
         <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
         <v>0</v>
       </c>
-      <c r="C60" s="38">
+      <c r="C60" s="34">
         <f>_xll.qlCallableBondEffectiveDuration(C16,0.3,C34,"actual/360","simple","quarterly",,C36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="66" t="s">
+      <c r="A61" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="B61" s="83">
+      <c r="B61" s="78">
         <f>_xll.qlCallableBondEffectiveConvexity(B16,0.3,B34,"actual/360","simple","quarterly",,B36)</f>
         <v>0</v>
       </c>
-      <c r="C61" s="84">
+      <c r="C61" s="79">
         <f>_xll.qlCallableBondEffectiveConvexity(C16,0.3,C34,"actual/360","simple","quarterly",,C36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="61" t="s">
+      <c r="A62" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="B62" s="62" t="str">
+      <c r="B62" s="57" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R62C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C62" s="63" t="str">
+      <c r="C62" s="58" t="str">
         <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R62C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="40" t="s">
+      <c r="A63" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="B63" s="77">
+      <c r="B63" s="72">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C63" s="78">
+      <c r="C63" s="73">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="40" t="s">
+      <c r="A64" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="B64" s="77" t="s">
+      <c r="B64" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="C64" s="78" t="s">
+      <c r="C64" s="73" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="40" t="s">
+      <c r="A65" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="B65" s="77" t="s">
+      <c r="B65" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="C65" s="78" t="s">
+      <c r="C65" s="73" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="40" t="s">
+      <c r="A66" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="B66" s="77" t="s">
+      <c r="B66" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="C66" s="78" t="s">
+      <c r="C66" s="73" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="40" t="s">
+      <c r="A67" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="B67" s="77"/>
-      <c r="C67" s="78"/>
+      <c r="B67" s="72"/>
+      <c r="C67" s="73"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="43" t="s">
+      <c r="A68" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="B68" s="44">
+      <c r="B68" s="40">
         <f>_xll.qlBondCleanPriceFromZSpread(B16,B62,B63,B64,B65,B66)</f>
         <v>78.380336922103126</v>
       </c>
-      <c r="C68" s="45">
+      <c r="C68" s="41">
         <f>_xll.qlBondCleanPriceFromZSpread(C16,C62,C63,C64,C65,C66)</f>
         <v>78.380336922103126</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="33" t="s">
+      <c r="A70" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="B70" s="34" t="str">
+      <c r="B70" s="30" t="str">
         <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R70C2CallableZeroCouponBond,A</v>
       </c>
-      <c r="C70" s="35" t="str">
+      <c r="C70" s="31" t="str">
         <f>_xll.qlCallableZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,C11,C15)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R70C3CallableZeroCouponBond,A</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="36" t="s">
+      <c r="A71" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="B71" s="37" t="str">
+      <c r="B71" s="33" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R71C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C71" s="38" t="str">
+      <c r="C71" s="34" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R71C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="36" t="s">
+      <c r="A72" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="B72" s="37">
+      <c r="B72" s="33">
         <v>0.03</v>
       </c>
-      <c r="C72" s="38">
+      <c r="C72" s="34">
         <v>0.03</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="36" t="s">
+      <c r="A73" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="B73" s="37">
+      <c r="B73" s="33">
         <v>0.01</v>
       </c>
-      <c r="C73" s="38">
+      <c r="C73" s="34">
         <v>0.01</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="39" t="s">
+      <c r="A74" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="B74" s="37" t="str">
+      <c r="B74" s="33" t="str">
         <f>_xll.qlHullWhite(B71,B72,B73)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R74C2HullWhite,A</v>
       </c>
-      <c r="C74" s="38" t="str">
+      <c r="C74" s="34" t="str">
         <f>_xll.qlHullWhite(C71,C72,C73)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R74C3HullWhite,A</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="40" t="s">
+      <c r="A75" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="B75" s="37">
+      <c r="B75" s="33">
         <v>100</v>
       </c>
-      <c r="C75" s="38">
+      <c r="C75" s="34">
         <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="41" t="s">
+      <c r="A76" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="B76" s="37" t="str">
+      <c r="B76" s="33" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine(B74,B75)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R76C2TreeCallableFixedRateBondEngine,A</v>
       </c>
-      <c r="C76" s="38" t="str">
+      <c r="C76" s="34" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine(C74,C75)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R76C3TreeCallableFixedRateBondEngine,A</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="42" t="s">
+      <c r="A77" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="B77" s="37" t="b">
+      <c r="B77" s="33" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B70,B76)</f>
         <v>1</v>
       </c>
-      <c r="C77" s="38" t="b">
+      <c r="C77" s="34" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(C70,C76)</f>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="43" t="s">
+      <c r="A78" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B78" s="44">
+      <c r="B78" s="40">
         <f>_xll.qlBondCleanPrice(B70,B77)</f>
         <v>86.90746669939648</v>
       </c>
-      <c r="C78" s="45">
+      <c r="C78" s="41">
         <f>_xll.qlBondCleanPrice(C70,C77)</f>
         <v>86.90746669939648</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="33" t="s">
+      <c r="A79" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="B79" s="34" t="str">
+      <c r="B79" s="30" t="str">
         <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8,,,,B15)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R79C2CallableZeroCouponBond,A</v>
       </c>
-      <c r="C79" s="35" t="str">
+      <c r="C79" s="31" t="str">
         <f>_xll.qlCallableZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,C11,C15)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R79C3CallableZeroCouponBond,A</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="36" t="s">
+      <c r="A80" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="B80" s="37" t="str">
+      <c r="B80" s="33" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R80C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C80" s="38" t="str">
+      <c r="C80" s="34" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R80C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="36" t="s">
+      <c r="A81" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="B81" s="37">
+      <c r="B81" s="33">
         <v>0.03</v>
       </c>
-      <c r="C81" s="38">
+      <c r="C81" s="34">
         <v>0.03</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="36" t="s">
+      <c r="A82" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="B82" s="37">
+      <c r="B82" s="33">
         <v>0.01</v>
       </c>
-      <c r="C82" s="38">
+      <c r="C82" s="34">
         <v>0.01</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="39" t="s">
+      <c r="A83" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="B83" s="37" t="str">
+      <c r="B83" s="33" t="str">
         <f>_xll.qlHullWhite(B80,B81,B82)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R83C2HullWhite,A</v>
       </c>
-      <c r="C83" s="38" t="str">
+      <c r="C83" s="34" t="str">
         <f>_xll.qlHullWhite(C80,C81,C82)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R83C3HullWhite,A</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="40" t="s">
+      <c r="A84" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="B84" s="37" t="str">
+      <c r="B84" s="33" t="str">
         <f>_xll.qlTimeGridFromTimes(B91:B206)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R84C2TimeGrid,A</v>
       </c>
-      <c r="C84" s="38" t="str">
+      <c r="C84" s="34" t="str">
         <f>_xll.qlTimeGridFromTimes(B91:B206)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R84C3TimeGrid,A</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="41" t="s">
+      <c r="A85" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="B85" s="37" t="str">
+      <c r="B85" s="33" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine2(B83,B84)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R85C2TreeCallableFixedRateBondEngine,A</v>
       </c>
-      <c r="C85" s="38" t="str">
+      <c r="C85" s="34" t="str">
         <f>_xll.qlTreeCallableFixedRateBondEngine2(C83,C84)</f>
         <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R85C3TreeCallableFixedRateBondEngine,A</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="42" t="s">
+      <c r="A86" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="B86" s="37" t="b">
+      <c r="B86" s="33" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(B79,B85)</f>
         <v>1</v>
       </c>
-      <c r="C86" s="38" t="b">
+      <c r="C86" s="34" t="b">
         <f>_xll.qlInstrumentSetPricingEngine(C79,C85)</f>
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="43" t="s">
+      <c r="A87" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B87" s="44">
+      <c r="B87" s="40">
         <f>_xll.qlBondCleanPrice(B79,B86)</f>
         <v>86.905812107181106</v>
       </c>
-      <c r="C87" s="45">
+      <c r="C87" s="41">
         <f>_xll.qlBondCleanPrice(C79,C86)</f>
         <v>86.905812107181106</v>
       </c>
@@ -6036,11 +6103,954 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE8D14D-DD7E-4024-86F3-1C5FBF784E5F}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA5B778A-9E41-4D83-BBAD-BAE5A92DD1A2}">
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="44.140625" customWidth="1"/>
+    <col min="2" max="3" width="82" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="30">
+        <v>2</v>
+      </c>
+      <c r="C4" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="33">
+        <v>100</v>
+      </c>
+      <c r="C5" s="34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="33">
+        <v>100</v>
+      </c>
+      <c r="C7" s="34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="33" t="str">
+        <f>_xll.qlCustomRegion("TestRegion","TR")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R10C2CustomRegion,A</v>
+      </c>
+      <c r="C10" s="34" t="str">
+        <f>_xll.qlCustomRegion("TestRegion","TR")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R10C3CustomRegion,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="50">
+        <v>45293</v>
+      </c>
+      <c r="C15" s="51">
+        <v>45293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="B16" s="52">
+        <v>47485</v>
+      </c>
+      <c r="C16" s="53">
+        <v>47485</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" s="33">
+        <v>0.02</v>
+      </c>
+      <c r="C17" s="34">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="33">
+        <v>0.02</v>
+      </c>
+      <c r="C18" s="34">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="109" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="40" t="str">
+        <f>_xll.qlZeroInflationCurve($B$1,B15:B16,B17:B18,"Annual","Actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R19C2ZeroInflationTermStructureHandle,A</v>
+      </c>
+      <c r="C19" s="41" t="str">
+        <f>_xll.qlZeroInflationCurve($B$1,C15:C16,C17:C18,"Annual","Actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R19C3ZeroInflationTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="108" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" s="40" t="str">
+        <f>_xll.qlZeroInflationIndex(B9,B10,B11,B12,B13,B14,B19)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R20C2ZeroInflationIndex,A</v>
+      </c>
+      <c r="C20" s="41" t="str">
+        <f>_xll.qlZeroInflationIndex(C9,C10,C11,C12,C13,C14,C19)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R20C3ZeroInflationIndex,A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" s="50">
+        <v>45293</v>
+      </c>
+      <c r="C21" s="51">
+        <v>45293</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" s="33">
+        <v>100</v>
+      </c>
+      <c r="C22" s="34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="109" t="s">
+        <v>196</v>
+      </c>
+      <c r="B23" s="40" t="b">
+        <f>_xll.qlIndexAddFixing(B20,B21,B22,TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="C23" s="41" t="b">
+        <f>_xll.qlIndexAddFixing(C20,C21,C22,TRUE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="50">
+        <v>45659</v>
+      </c>
+      <c r="C25" s="51">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="52">
+        <v>47485</v>
+      </c>
+      <c r="C26" s="53">
+        <v>47485</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="C32" s="34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="40" t="str">
+        <f>_xll.qlSchedule(B25,B26,B27,B28,B29,B30,B31,B32)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R33C2Schedule,A</v>
+      </c>
+      <c r="C33" s="41" t="str">
+        <f>_xll.qlSchedule(C25,C26,C27,C28,C29,C30,C31,C32)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R33C3Schedule,A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="33">
+        <v>0.03</v>
+      </c>
+      <c r="C34" s="34">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="52">
+        <v>45689</v>
+      </c>
+      <c r="C37" s="53">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="33"/>
+      <c r="C38" s="34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="33"/>
+      <c r="C39" s="34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="33"/>
+      <c r="C40" s="34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" s="33"/>
+      <c r="C41" s="34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="33"/>
+      <c r="C42" s="34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="54" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" s="40" t="str">
+        <f>_xll.qlCPIBond(B4,B5,B6,B7,B8,B20,B24,B33,B34,B35,B36,B37)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R43C2CPIBond,A</v>
+      </c>
+      <c r="C43" s="41" t="str">
+        <f>_xll.qlCPIBond(C4,C5,C6,C7,C8,C20,C24,C33,C34,C35,C36,C37,C38,C39,C40,C41,C42)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R43C3CPIBond,A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="111" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" s="30">
+        <f>_xll.qlBondNextCouponRate(B43)</f>
+        <v>3.0906838410957833E-2</v>
+      </c>
+      <c r="C44" s="31">
+        <f>_xll.qlBondNextCouponRate(C43)</f>
+        <v>3.0906838410957833E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="80" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="78">
+        <f>_xll.qlBondPreviousCouponRate(B43)</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="79">
+        <f>_xll.qlBondPreviousCouponRate(C43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="52">
+        <f>_xll.qlBondNextCashFlowDate(B43)</f>
+        <v>45840</v>
+      </c>
+      <c r="C46" s="53">
+        <f>_xll.qlBondNextCashFlowDate(C43)</f>
+        <v>45840</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" s="113">
+        <f>_xll.qlBondPreviousCashFlowDate(B43)</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="106">
+        <f>_xll.qlBondPreviousCashFlowDate(C43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="112" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="33">
+        <f>_xll.qlBondSettlementDays(B43)</f>
+        <v>2</v>
+      </c>
+      <c r="C48" s="34">
+        <f>_xll.qlBondSettlementDays(C43)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="113">
+        <f>_xll.qlBondSettlementDate(B43)</f>
+        <v>45689</v>
+      </c>
+      <c r="C49" s="106">
+        <f>_xll.qlBondSettlementDate(C43)</f>
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="33" t="b">
+        <f>_xll.qlBondIsTradable(B43)</f>
+        <v>1</v>
+      </c>
+      <c r="C50" s="34" t="b">
+        <f>_xll.qlBondIsTradable(C43)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" s="113">
+        <f>_xll.qlBondStartDate(B43)</f>
+        <v>45659</v>
+      </c>
+      <c r="C51" s="106">
+        <f>_xll.qlBondStartDate(C43)</f>
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" s="52">
+        <f>_xll.qlBondMaturityDate(B43)</f>
+        <v>47485</v>
+      </c>
+      <c r="C52" s="53">
+        <f>_xll.qlBondMaturityDate(C43)</f>
+        <v>47485</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="114" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" s="113">
+        <f>_xll.qlBondIssueDate(B43)</f>
+        <v>45689</v>
+      </c>
+      <c r="C53" s="106">
+        <f>_xll.qlBondIssueDate(C43)</f>
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" s="33" t="str">
+        <f>_xll.qlBondCashFlows(B43)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R54C2CashFlow,A</v>
+      </c>
+      <c r="C54" s="34" t="str">
+        <f>_xll.qlBondCashFlows(C43)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R54C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="78" t="str">
+        <f>_xll.qlBondRedemption(B43)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R55C2CashFlow,A</v>
+      </c>
+      <c r="C55" s="79" t="str">
+        <f>_xll.qlBondRedemption(C43)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R55C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="112" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="33" t="str">
+        <f>_xll.qlBondRedemptions(B43)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R56C2CashFlow,A</v>
+      </c>
+      <c r="C56" s="34" t="str">
+        <f>_xll.qlBondRedemptions(C43)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R56C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="78" t="str">
+        <f>_xll.qlBondCalendar(B43)</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C57" s="79" t="str">
+        <f>_xll.qlBondCalendar(C43)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" s="33">
+        <f>_xll.qlBondNotional(B43)</f>
+        <v>100</v>
+      </c>
+      <c r="C58" s="34">
+        <f>_xll.qlBondNotional(C43)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="78">
+        <f>_xll.qlBondNotionals(B43)</f>
+        <v>100</v>
+      </c>
+      <c r="C59" s="79">
+        <f>_xll.qlBondNotionals(C43)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" s="30" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"actual360","compounded","Annual")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R60C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C60" s="31" t="str">
+        <f>_xll.qlFlatForward(C1,0.03,"actual360","compounded","Annual")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R60C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B61" s="40" t="str">
+        <f>_xll.qlDiscountingBondEngine(B60)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R61C2DiscountingBondEngine,A</v>
+      </c>
+      <c r="C61" s="41" t="str">
+        <f>_xll.qlDiscountingBondEngine(C60)</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R61C3DiscountingBondEngine,A</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" s="33" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B43,B61)</f>
+        <v>1</v>
+      </c>
+      <c r="C62" s="34" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C43,C61)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" s="72">
+        <f>_xll.qlBondCleanPrice(B43,B62)</f>
+        <v>109.81755839471742</v>
+      </c>
+      <c r="C63" s="73">
+        <f>_xll.qlBondCleanPrice(C43,C62)</f>
+        <v>109.81755839471738</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" s="57">
+        <v>2.9558808088302614E-2</v>
+      </c>
+      <c r="C64" s="58">
+        <v>2.9558808088302614E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B65" s="59">
+        <f>_xll.qlBondCleanPrice2(B43,B64,"actual360","continuous")</f>
+        <v>109.81755538345057</v>
+      </c>
+      <c r="C65" s="60">
+        <f>_xll.qlBondCleanPrice2(C43,C64,"actual360","continuous")</f>
+        <v>109.81755538345057</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="72">
+        <f>_xll.qlBondDirtyPrice(B43,B62)</f>
+        <v>110.06455373642939</v>
+      </c>
+      <c r="C66" s="73">
+        <f>_xll.qlBondDirtyPrice(C43,C62)</f>
+        <v>110.06455373642935</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="B67" s="62">
+        <f>_xll.qlBondDirtyPrice2(B43,B64,"actual360","CONTINUOUS","annual")</f>
+        <v>110.06455072516253</v>
+      </c>
+      <c r="C67" s="63">
+        <f>_xll.qlBondDirtyPrice2(C43,C64,"actual360","CONTINUOUS","annual")</f>
+        <v>110.06455072516253</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="72">
+        <f>_xll.qlBondYield(B43,"actual360","CONTINUOUS","annual",,,B62)</f>
+        <v>2.9558808088302614E-2</v>
+      </c>
+      <c r="C68" s="73">
+        <f>_xll.qlBondYield(C43,"actual360","CONTINUOUS","annual",,,C62)</f>
+        <v>2.9558808088302614E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="57" t="str">
+        <f>_xll.qlBondPrice(B63,"clean")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R69C2BondPrice,A</v>
+      </c>
+      <c r="C69" s="58" t="str">
+        <f>_xll.qlBondPrice(C63,"clean")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R69C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" s="59">
+        <f>_xll.qlBondYield2(B43,B69,"actual360","CONTINUOUS","annual")</f>
+        <v>3.0038936376571658E-2</v>
+      </c>
+      <c r="C70" s="60">
+        <f>_xll.qlBondYield2(C43,C69,"actual360","CONTINUOUS","annual")</f>
+        <v>3.0038936376571658E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B71" s="50">
+        <v>45667</v>
+      </c>
+      <c r="C71" s="51">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" s="59">
+        <f>_xll.qlBondAccruedAmount(B43,B71)</f>
+        <v>6.57859407282088E-2</v>
+      </c>
+      <c r="C72" s="60">
+        <f>_xll.qlBondAccruedAmount(C43,C71)</f>
+        <v>6.57859407282088E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" s="72">
+        <f>_xll.qlBondSettlementValue(B43,B62)</f>
+        <v>110.06455373642939</v>
+      </c>
+      <c r="C73" s="73">
+        <f>_xll.qlBondSettlementValue(C43,C62)</f>
+        <v>110.06455373642936</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74" s="62">
+        <f>_xll.qlBondSettlementValue2(B43,B63)</f>
+        <v>110.06455373642939</v>
+      </c>
+      <c r="C74" s="63">
+        <f>_xll.qlBondSettlementValue2(C43,C63)</f>
+        <v>110.06455373642933</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="57" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R75C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C75" s="58" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CPIBond!R75C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="B76" s="72">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C76" s="73">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="B77" s="72" t="s">
+        <v>168</v>
+      </c>
+      <c r="C77" s="73" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="B78" s="72" t="s">
+        <v>169</v>
+      </c>
+      <c r="C78" s="73" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B79" s="72" t="s">
+        <v>170</v>
+      </c>
+      <c r="C79" s="73" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" s="72"/>
+      <c r="C80" s="53">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" s="40">
+        <f>_xll.qlBondCleanPriceFromZSpread(B43,B75,B76,B77,B78,B79)</f>
+        <v>107.37186093315256</v>
+      </c>
+      <c r="C81" s="41">
+        <f>_xll.qlBondCleanPriceFromZSpread(C43,C75,C76,C77,C78,C79,C80)</f>
+        <v>107.31111950834615</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7498,7 +8508,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="117" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="3">
@@ -7509,7 +8519,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="A16" s="117"/>
       <c r="B16" s="3">
         <v>0.05</v>
       </c>
@@ -7518,7 +8528,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
+      <c r="A17" s="117"/>
       <c r="B17" s="3">
         <v>0.06</v>
       </c>
@@ -8139,7 +9149,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="117" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="3">
@@ -8150,7 +9160,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
+      <c r="A6" s="117"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -8159,7 +9169,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
+      <c r="A7" s="117"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -8271,7 +9281,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="117" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="3">
@@ -8282,7 +9292,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="32"/>
+      <c r="A18" s="117"/>
       <c r="B18" s="3">
         <v>0.05</v>
       </c>
@@ -8291,7 +9301,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="32"/>
+      <c r="A19" s="117"/>
       <c r="B19" s="3">
         <v>0.06</v>
       </c>
@@ -8360,7 +9370,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="117" t="s">
         <v>87</v>
       </c>
       <c r="C27" s="3">
@@ -8368,13 +9378,13 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="32"/>
+      <c r="A28" s="117"/>
       <c r="C28" s="3">
         <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="32"/>
+      <c r="A29" s="117"/>
       <c r="C29" s="3">
         <v>110</v>
       </c>
@@ -8994,7 +10004,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="117" t="s">
         <v>88</v>
       </c>
       <c r="B5" s="3">
@@ -9005,7 +10015,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
+      <c r="A6" s="117"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -9014,7 +10024,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
+      <c r="A7" s="117"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>

--- a/tests/workbooktests/workbooks/test_bonds.xlsx
+++ b/tests/workbooktests/workbooks/test_bonds.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB21C28-8590-48C0-AC89-070A617FEADF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D39693-9253-47C1-BCEF-B226CC19D9BD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
     <sheet name="BondPrice" sheetId="18" r:id="rId2"/>
-    <sheet name="Bond" sheetId="3" r:id="rId3"/>
-    <sheet name="ZeroCouponBond" sheetId="4" r:id="rId4"/>
-    <sheet name="FixedRateBond" sheetId="5" r:id="rId5"/>
-    <sheet name="AmortizingFixedRateBond" sheetId="6" r:id="rId6"/>
-    <sheet name="AmortizingFloatingRateBond" sheetId="7" r:id="rId7"/>
-    <sheet name="FloatingRateBond" sheetId="8" r:id="rId8"/>
-    <sheet name="CmsRateBond" sheetId="9" r:id="rId9"/>
-    <sheet name="AmortizingCmsRateBond" sheetId="10" r:id="rId10"/>
-    <sheet name="Callability" sheetId="21" r:id="rId11"/>
-    <sheet name="CallableFixedRateBond" sheetId="13" r:id="rId12"/>
-    <sheet name="CallableZeroCouponBond" sheetId="14" r:id="rId13"/>
-    <sheet name="CPIBond" sheetId="22" r:id="rId14"/>
+    <sheet name="BondSinkingSchedule_Notionals" sheetId="23" r:id="rId3"/>
+    <sheet name="Bond" sheetId="3" r:id="rId4"/>
+    <sheet name="ZeroCouponBond" sheetId="4" r:id="rId5"/>
+    <sheet name="FixedRateBond" sheetId="5" r:id="rId6"/>
+    <sheet name="AmortizingFixedRateBond" sheetId="6" r:id="rId7"/>
+    <sheet name="AmortizingFloatingRateBond" sheetId="7" r:id="rId8"/>
+    <sheet name="FloatingRateBond" sheetId="8" r:id="rId9"/>
+    <sheet name="CmsRateBond" sheetId="9" r:id="rId10"/>
+    <sheet name="AmortizingCmsRateBond" sheetId="10" r:id="rId11"/>
+    <sheet name="Callability" sheetId="21" r:id="rId12"/>
+    <sheet name="CallableFixedRateBond" sheetId="13" r:id="rId13"/>
+    <sheet name="CallableZeroCouponBond" sheetId="14" r:id="rId14"/>
+    <sheet name="CPIBond" sheetId="22" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="209">
   <si>
     <t>Bond</t>
   </si>
@@ -641,6 +642,33 @@
   </si>
   <si>
     <t>qlCPIBond</t>
+  </si>
+  <si>
+    <t>BondSinkingSchedule_Notionals</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>bond_length</t>
+  </si>
+  <si>
+    <t>5Y</t>
+  </si>
+  <si>
+    <t>qlBondSinkingSchedule</t>
+  </si>
+  <si>
+    <t>coupon_rate</t>
+  </si>
+  <si>
+    <t>initial_amount</t>
+  </si>
+  <si>
+    <t>qlBondSinkingNotionals</t>
+  </si>
+  <si>
+    <t>{=qlBondSinkingNotionals(B10;B11;B12;B13)}</t>
   </si>
 </sst>
 </file>
@@ -983,7 +1011,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1244,6 +1272,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1559,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F1B31AC-6B78-4845-B599-86FA814CB2D7}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="15"/>
@@ -1602,17 +1634,15 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22"/>
+        <v>200</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="27"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>112</v>
@@ -1622,7 +1652,7 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>112</v>
@@ -1632,7 +1662,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>112</v>
@@ -1642,7 +1672,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>112</v>
@@ -1652,7 +1682,7 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>112</v>
@@ -1662,7 +1692,7 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>112</v>
@@ -1671,8 +1701,8 @@
       <c r="E11" s="22"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
-        <v>7</v>
+      <c r="B12" s="20" t="s">
+        <v>6</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>112</v>
@@ -1682,27 +1712,25 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="21"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>112</v>
+      </c>
       <c r="D13" s="21"/>
       <c r="E13" s="22"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="25" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>112</v>
-      </c>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21" t="s">
@@ -1712,15 +1740,27 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="110" t="s">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C17" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1732,6 +1772,883 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27515A30-3B44-433D-8DBF-ACC4ED7765FD}">
+  <dimension ref="A1:C74"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46.140625" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="11">
+        <v>45665</v>
+      </c>
+      <c r="C6" s="11">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="11">
+        <v>49682</v>
+      </c>
+      <c r="C7" s="11">
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C9" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="6">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="3" t="str">
+        <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R14C2Schedule,A</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <f>_xll.qlSchedule(C6,C7,C8,C9,C10,C11,C12,C13)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R14C3Schedule,A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C19" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="6" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R23C2Euribor,A</v>
+      </c>
+      <c r="C23" s="6" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R23C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="6" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R24C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C24" s="6" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R24C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="3" t="str">
+        <f>_xll.qlSwapIndex(B15,B16,B17,B18,B19,B20,B21,B22,B23,B24)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R25C2SwapIndex,A</v>
+      </c>
+      <c r="C25" s="3" t="str">
+        <f>_xll.qlSwapIndex(C15,C16,C17,C18,C19,C20,C21,C22,C23,C24)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R25C3SwapIndex,A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C30" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="2">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="3" t="str">
+        <f>_xll.qlCmsRateBond(B4,B5,B14,B25,B26,B27,B28,B29,B30,B31,B32)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R36C2CmsRateBond,A</v>
+      </c>
+      <c r="C36" s="3" t="str">
+        <f>_xll.qlCmsRateBond(C4,C5,C14,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34,C35)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R36C3CmsRateBond,A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="3">
+        <f>_xll.qlBondNextCouponRate(B36)</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="3">
+        <f>_xll.qlBondNextCouponRate(C36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="3">
+        <f>_xll.qlBondPreviousCouponRate(B36)</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="3">
+        <f>_xll.qlBondPreviousCouponRate(C36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="2">
+        <f>_xll.qlBondNextCashFlowDate(B36)</f>
+        <v>46030</v>
+      </c>
+      <c r="C39" s="2">
+        <f>_xll.qlBondNextCashFlowDate(C36)</f>
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(B36)</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(C36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="3">
+        <f>_xll.qlBondSettlementDays(B36)</f>
+        <v>2</v>
+      </c>
+      <c r="C41" s="3">
+        <f>_xll.qlBondSettlementDays(C36)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="2">
+        <f>_xll.qlBondSettlementDate(B36)</f>
+        <v>45663</v>
+      </c>
+      <c r="C42" s="2">
+        <f>_xll.qlBondSettlementDate(C36)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" s="3" t="b">
+        <f>_xll.qlBondIsTradable(B36)</f>
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="b">
+        <f>_xll.qlBondIsTradable(C36)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" s="2">
+        <f>_xll.qlBondStartDate(B36)</f>
+        <v>45665</v>
+      </c>
+      <c r="C44" s="2">
+        <f>_xll.qlBondStartDate(C36)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="2">
+        <f>_xll.qlBondMaturityDate(B36)</f>
+        <v>49682</v>
+      </c>
+      <c r="C45" s="2">
+        <f>_xll.qlBondMaturityDate(C36)</f>
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" s="3">
+        <f>_xll.qlBondIssueDate(B36)</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="2">
+        <f>_xll.qlBondIssueDate(C36)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="3" t="str">
+        <f>_xll.qlBondCashFlows(B36)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R47C2CashFlow,A</v>
+      </c>
+      <c r="C47" s="3" t="str">
+        <f>_xll.qlBondCashFlows(C36)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R47C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="3" t="str">
+        <f>_xll.qlBondRedemption(B36)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R48C2CashFlow,A</v>
+      </c>
+      <c r="C48" s="3" t="str">
+        <f>_xll.qlBondRedemption(C36)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R48C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="3" t="str">
+        <f>_xll.qlBondRedemptions(B36)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R49C2CashFlow,A</v>
+      </c>
+      <c r="C49" s="3" t="str">
+        <f>_xll.qlBondRedemptions(C36)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R49C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" s="3" t="str">
+        <f>_xll.qlBondCalendar(B36)</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C50" s="3" t="str">
+        <f>_xll.qlBondCalendar(C36)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="3">
+        <f>_xll.qlBondNotional(B36)</f>
+        <v>100</v>
+      </c>
+      <c r="C51" s="3">
+        <f>_xll.qlBondNotional(C36)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="3">
+        <f>_xll.qlBondNotionals(B36)</f>
+        <v>100</v>
+      </c>
+      <c r="C52" s="3">
+        <f>_xll.qlBondNotionals(C36)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="3" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R53C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C53" s="3" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R53C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54" s="3" t="str">
+        <f>_xll.qlDiscountingBondEngine(B53)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R54C2DiscountingBondEngine,A</v>
+      </c>
+      <c r="C54" s="3" t="str">
+        <f>_xll.qlDiscountingBondEngine(C53)</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R54C3DiscountingBondEngine,A</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B55" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B36,B54)</f>
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C36,C54)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" s="9">
+        <f>_xll.qlBondCleanPrice(B36,B55)</f>
+        <v>71.629228665106581</v>
+      </c>
+      <c r="C56" s="9">
+        <f>_xll.qlBondCleanPrice(C36,C55)</f>
+        <v>85.955074398127891</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="9">
+        <v>2.9888064241409301E-2</v>
+      </c>
+      <c r="C57" s="9">
+        <v>2.9888064241409301E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" s="9">
+        <f>_xll.qlBondCleanPrice2(B36,B57,"actual360","continuous")</f>
+        <v>71.629224757480401</v>
+      </c>
+      <c r="C58" s="9">
+        <f>_xll.qlBondCleanPrice2(C36,C57,"actual360","continuous")</f>
+        <v>85.955069708976481</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="9">
+        <f>_xll.qlBondDirtyPrice(B36,B55)</f>
+        <v>71.629228665106581</v>
+      </c>
+      <c r="C59" s="9">
+        <f>_xll.qlBondDirtyPrice(C36,C55)</f>
+        <v>85.955074398127891</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="9">
+        <f>_xll.qlBondDirtyPrice2(B36,B57,"actual360","CONTINUOUS","annual")</f>
+        <v>71.629224757480401</v>
+      </c>
+      <c r="C60" s="9">
+        <f>_xll.qlBondDirtyPrice2(C36,C57,"actual360","CONTINUOUS","annual")</f>
+        <v>85.955069708976481</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="9">
+        <f>_xll.qlBondYield(B36,"actual360","CONTINUOUS","annual",,,B55)</f>
+        <v>2.9888064241409308E-2</v>
+      </c>
+      <c r="C61" s="9">
+        <f>_xll.qlBondYield(C36,"actual360","CONTINUOUS","annual",,,C55)</f>
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B62" s="9" t="str">
+        <f>_xll.qlBondPrice(B56,"clean")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R62C2BondPrice,A</v>
+      </c>
+      <c r="C62" s="9" t="str">
+        <f>_xll.qlBondPrice(C56,"clean")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R62C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="9">
+        <f>_xll.qlBondYield2(B36,B62,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9888064241409308E-2</v>
+      </c>
+      <c r="C63" s="9">
+        <f>_xll.qlBondYield2(C36,C62,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C64" s="2">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="9">
+        <f>_xll.qlBondAccruedAmount(B36,B64)</f>
+        <v>0</v>
+      </c>
+      <c r="C65" s="9">
+        <f>_xll.qlBondAccruedAmount(C36,C64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="9">
+        <f>_xll.qlBondSettlementValue(B36,B55)</f>
+        <v>71.629228665106581</v>
+      </c>
+      <c r="C66" s="9">
+        <f>_xll.qlBondSettlementValue(C36,C55)</f>
+        <v>85.955074398127891</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="9">
+        <f>_xll.qlBondSettlementValue2(B36,B56)</f>
+        <v>71.629228665106581</v>
+      </c>
+      <c r="C67" s="9">
+        <f>_xll.qlBondSettlementValue2(C36,C56)</f>
+        <v>85.955074398127891</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R68C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C68" s="9" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R68C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C69" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B74" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(B36,B68,B69,B70,B71,B72)</f>
+        <v>68.138537120691339</v>
+      </c>
+      <c r="C74" s="3">
+        <f>_xll.qlBondCleanPriceFromZSpread(C36,C68,C69,C70,C71,C72)</f>
+        <v>81.766244544829618</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ABD84F-1436-4AE1-BC17-091C65B56114}">
   <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2613,7 +3530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F09BC366-53EA-43EA-8BCB-0489C1B271E0}">
   <dimension ref="A3:B12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2692,7 +3609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0A1FE9-B1FE-4762-AEA9-E4B3F6C519F7}">
   <dimension ref="A1:C219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4470,7 +5387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4EF9C2-FD4D-4E7F-8154-C8E782972C6B}">
   <dimension ref="A1:C206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6102,7 +7019,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA5B778A-9E41-4D83-BBAD-BAE5A92DD1A2}">
   <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7122,6 +8039,128 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2242D3EA-26F0-4B90-9FC1-2485363E0315}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.7109375" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="119" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="119" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="119" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="119" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <f>_xll.qlBondSinkingSchedule(B4,B5,B6,B7)</f>
+        <v>欣[test_bonds.xlsx]BondSinkingSchedule_Notionals!R8C2Schedule,A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="119" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="119" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="119" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="119" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="3">
+        <f>_xll.qlBondSinkingNotionals(B10,B11,B12,B13)</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="120" t="s">
+        <v>208</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8683113-FD1C-4D88-8D42-F7763B404E4F}">
   <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7763,7 +8802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0BDDB4-6035-4089-86B1-6246F3228CBC}">
   <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8355,7 +9394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00EB77E5-949B-439C-BFA2-575F2A710E3C}">
   <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9110,7 +10149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303A5445-988F-4FD7-9234-8C10A40DEB2F}">
   <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9965,7 +11004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76F30CA-2F79-453E-B116-2A48310E361D}">
   <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10778,7 +11817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05025377-E5EA-48F0-BE68-1C47A2C5C8E6}">
   <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11558,881 +12597,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27515A30-3B44-433D-8DBF-ACC4ED7765FD}">
-  <dimension ref="A1:C74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="46.140625" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="2">
-        <v>45659</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2">
-        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45659</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3">
-        <v>100</v>
-      </c>
-      <c r="C5" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="11">
-        <v>45665</v>
-      </c>
-      <c r="C6" s="11">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="11">
-        <v>49682</v>
-      </c>
-      <c r="C7" s="11">
-        <v>49682</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="6" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-      <c r="C9" s="6" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="6">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="3" t="str">
-        <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R14C2Schedule,A</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>_xll.qlSchedule(C6,C7,C8,C9,C10,C11,C12,C13)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R14C3Schedule,A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="6">
-        <v>2</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="6" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-      <c r="C19" s="6" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B23" s="6" t="str">
-        <f>_xll.qlEuribor("3M")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R23C2Euribor,A</v>
-      </c>
-      <c r="C23" s="6" t="str">
-        <f>_xll.qlEuribor("3M")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R23C3Euribor,A</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B24" s="6" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R24C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C24" s="6" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R24C3YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>100</v>
-      </c>
-      <c r="B25" s="3" t="str">
-        <f>_xll.qlSwapIndex(B15,B16,B17,B18,B19,B20,B21,B22,B23,B24)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R25C2SwapIndex,A</v>
-      </c>
-      <c r="C25" s="3" t="str">
-        <f>_xll.qlSwapIndex(C15,C16,C17,C18,C19,C20,C21,C22,C23,C24)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R25C3SwapIndex,A</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>90</v>
-      </c>
-      <c r="B28" s="3">
-        <v>2</v>
-      </c>
-      <c r="C28" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="3">
-        <v>0</v>
-      </c>
-      <c r="C29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" s="3">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C30" s="3">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="3">
-        <v>0</v>
-      </c>
-      <c r="C31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="3">
-        <v>0</v>
-      </c>
-      <c r="C32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="2">
-        <v>45663</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B36" s="3" t="str">
-        <f>_xll.qlCmsRateBond(B4,B5,B14,B25,B26,B27,B28,B29,B30,B31,B32)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R36C2CmsRateBond,A</v>
-      </c>
-      <c r="C36" s="3" t="str">
-        <f>_xll.qlCmsRateBond(C4,C5,C14,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34,C35)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R36C3CmsRateBond,A</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B37" s="3">
-        <f>_xll.qlBondNextCouponRate(B36)</f>
-        <v>0</v>
-      </c>
-      <c r="C37" s="3">
-        <f>_xll.qlBondNextCouponRate(C36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="3">
-        <f>_xll.qlBondPreviousCouponRate(B36)</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="3">
-        <f>_xll.qlBondPreviousCouponRate(C36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B39" s="2">
-        <f>_xll.qlBondNextCashFlowDate(B36)</f>
-        <v>46030</v>
-      </c>
-      <c r="C39" s="2">
-        <f>_xll.qlBondNextCashFlowDate(C36)</f>
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" s="2">
-        <f>_xll.qlBondPreviousCashFlowDate(B36)</f>
-        <v>0</v>
-      </c>
-      <c r="C40" s="2">
-        <f>_xll.qlBondPreviousCashFlowDate(C36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B41" s="3">
-        <f>_xll.qlBondSettlementDays(B36)</f>
-        <v>2</v>
-      </c>
-      <c r="C41" s="3">
-        <f>_xll.qlBondSettlementDays(C36)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B42" s="2">
-        <f>_xll.qlBondSettlementDate(B36)</f>
-        <v>45663</v>
-      </c>
-      <c r="C42" s="2">
-        <f>_xll.qlBondSettlementDate(C36)</f>
-        <v>45663</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B43" s="3" t="b">
-        <f>_xll.qlBondIsTradable(B36)</f>
-        <v>1</v>
-      </c>
-      <c r="C43" s="3" t="b">
-        <f>_xll.qlBondIsTradable(C36)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="2">
-        <f>_xll.qlBondStartDate(B36)</f>
-        <v>45665</v>
-      </c>
-      <c r="C44" s="2">
-        <f>_xll.qlBondStartDate(C36)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" s="2">
-        <f>_xll.qlBondMaturityDate(B36)</f>
-        <v>49682</v>
-      </c>
-      <c r="C45" s="2">
-        <f>_xll.qlBondMaturityDate(C36)</f>
-        <v>49682</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" s="3">
-        <f>_xll.qlBondIssueDate(B36)</f>
-        <v>0</v>
-      </c>
-      <c r="C46" s="2">
-        <f>_xll.qlBondIssueDate(C36)</f>
-        <v>45663</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="3" t="str">
-        <f>_xll.qlBondCashFlows(B36)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R47C2CashFlow,A</v>
-      </c>
-      <c r="C47" s="3" t="str">
-        <f>_xll.qlBondCashFlows(C36)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R47C3CashFlow,A</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="3" t="str">
-        <f>_xll.qlBondRedemption(B36)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R48C2CashFlow,A</v>
-      </c>
-      <c r="C48" s="3" t="str">
-        <f>_xll.qlBondRedemption(C36)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R48C3CashFlow,A</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="3" t="str">
-        <f>_xll.qlBondRedemptions(B36)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R49C2CashFlow,A</v>
-      </c>
-      <c r="C49" s="3" t="str">
-        <f>_xll.qlBondRedemptions(C36)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R49C3CashFlow,A</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B50" s="3" t="str">
-        <f>_xll.qlBondCalendar(B36)</f>
-        <v>TARGET</v>
-      </c>
-      <c r="C50" s="3" t="str">
-        <f>_xll.qlBondCalendar(C36)</f>
-        <v>TARGET</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B51" s="3">
-        <f>_xll.qlBondNotional(B36)</f>
-        <v>100</v>
-      </c>
-      <c r="C51" s="3">
-        <f>_xll.qlBondNotional(C36)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="3">
-        <f>_xll.qlBondNotionals(B36)</f>
-        <v>100</v>
-      </c>
-      <c r="C52" s="3">
-        <f>_xll.qlBondNotionals(C36)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53" s="3" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R53C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C53" s="3" t="str">
-        <f>_xll.qlFlatForward(B2,0.03,"actual360","compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R53C3YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B54" s="3" t="str">
-        <f>_xll.qlDiscountingBondEngine(B53)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R54C2DiscountingBondEngine,A</v>
-      </c>
-      <c r="C54" s="3" t="str">
-        <f>_xll.qlDiscountingBondEngine(C53)</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R54C3DiscountingBondEngine,A</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B55" s="3" t="b">
-        <f>_xll.qlInstrumentSetPricingEngine(B36,B54)</f>
-        <v>1</v>
-      </c>
-      <c r="C55" s="3" t="b">
-        <f>_xll.qlInstrumentSetPricingEngine(C36,C54)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B56" s="9">
-        <f>_xll.qlBondCleanPrice(B36,B55)</f>
-        <v>71.629228665106581</v>
-      </c>
-      <c r="C56" s="9">
-        <f>_xll.qlBondCleanPrice(C36,C55)</f>
-        <v>85.955074398127891</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="9">
-        <v>2.9888064241409301E-2</v>
-      </c>
-      <c r="C57" s="9">
-        <v>2.9888064241409301E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B58" s="9">
-        <f>_xll.qlBondCleanPrice2(B36,B57,"actual360","continuous")</f>
-        <v>71.629224757480401</v>
-      </c>
-      <c r="C58" s="9">
-        <f>_xll.qlBondCleanPrice2(C36,C57,"actual360","continuous")</f>
-        <v>85.955069708976481</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B59" s="9">
-        <f>_xll.qlBondDirtyPrice(B36,B55)</f>
-        <v>71.629228665106581</v>
-      </c>
-      <c r="C59" s="9">
-        <f>_xll.qlBondDirtyPrice(C36,C55)</f>
-        <v>85.955074398127891</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" s="9">
-        <f>_xll.qlBondDirtyPrice2(B36,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>71.629224757480401</v>
-      </c>
-      <c r="C60" s="9">
-        <f>_xll.qlBondDirtyPrice2(C36,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>85.955069708976481</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="9">
-        <f>_xll.qlBondYield(B36,"actual360","CONTINUOUS","annual",,,B55)</f>
-        <v>2.9888064241409308E-2</v>
-      </c>
-      <c r="C61" s="9">
-        <f>_xll.qlBondYield(C36,"actual360","CONTINUOUS","annual",,,C55)</f>
-        <v>2.9888064241409308E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B62" s="9" t="str">
-        <f>_xll.qlBondPrice(B56,"clean")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R62C2BondPrice,A</v>
-      </c>
-      <c r="C62" s="9" t="str">
-        <f>_xll.qlBondPrice(C56,"clean")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R62C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="9">
-        <f>_xll.qlBondYield2(B36,B62,"actual360","CONTINUOUS","annual")</f>
-        <v>2.9888064241409308E-2</v>
-      </c>
-      <c r="C63" s="9">
-        <f>_xll.qlBondYield2(C36,C62,"actual360","CONTINUOUS","annual")</f>
-        <v>2.9888064241409308E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" s="2">
-        <v>45667</v>
-      </c>
-      <c r="C64" s="2">
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="9">
-        <f>_xll.qlBondAccruedAmount(B36,B64)</f>
-        <v>0</v>
-      </c>
-      <c r="C65" s="9">
-        <f>_xll.qlBondAccruedAmount(C36,C64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="9">
-        <f>_xll.qlBondSettlementValue(B36,B55)</f>
-        <v>71.629228665106581</v>
-      </c>
-      <c r="C66" s="9">
-        <f>_xll.qlBondSettlementValue(C36,C55)</f>
-        <v>85.955074398127891</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="9">
-        <f>_xll.qlBondSettlementValue2(B36,B56)</f>
-        <v>71.629228665106581</v>
-      </c>
-      <c r="C67" s="9">
-        <f>_xll.qlBondSettlementValue2(C36,C56)</f>
-        <v>85.955074398127891</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B68" s="9" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R68C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C68" s="9" t="str">
-        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R68C3YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B69" s="9">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C69" s="9">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B74" s="3">
-        <f>_xll.qlBondCleanPriceFromZSpread(B36,B68,B69,B70,B71,B72)</f>
-        <v>68.138537120691339</v>
-      </c>
-      <c r="C74" s="3">
-        <f>_xll.qlBondCleanPriceFromZSpread(C36,C68,C69,C70,C71,C72)</f>
-        <v>81.766244544829618</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>